--- a/verified_email-verification_minimal.xlsx
+++ b/verified_email-verification_minimal.xlsx
@@ -18122,7 +18122,7 @@
       <c r="B47" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="3" t="s">
         <v>327</v>
       </c>
       <c r="D47" s="2"/>
@@ -18156,7 +18156,7 @@
       <c r="B48" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>333</v>
       </c>
       <c r="D48" s="2"/>
@@ -18187,7 +18187,7 @@
       <c r="A49" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>338</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -18221,7 +18221,7 @@
       <c r="A50" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -18255,10 +18255,10 @@
       <c r="A51" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="3" t="s">
         <v>351</v>
       </c>
       <c r="D51" s="2"/>
@@ -18326,7 +18326,7 @@
       <c r="B53" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="3" t="s">
         <v>363</v>
       </c>
       <c r="D53" s="2"/>
@@ -18360,7 +18360,7 @@
       <c r="B54" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="3" t="s">
         <v>369</v>
       </c>
       <c r="D54" s="2"/>
@@ -18425,7 +18425,7 @@
       <c r="A56" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>380</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -18459,7 +18459,7 @@
       <c r="A57" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>386</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -18493,7 +18493,7 @@
       <c r="A58" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="3" t="s">
         <v>392</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -18527,10 +18527,10 @@
       <c r="A59" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="3" t="s">
         <v>399</v>
       </c>
       <c r="D59" s="2"/>
@@ -18564,7 +18564,7 @@
       <c r="B60" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="3" t="s">
         <v>405</v>
       </c>
       <c r="D60" s="2"/>
@@ -18595,7 +18595,7 @@
       <c r="A61" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="3" t="s">
         <v>411</v>
       </c>
       <c r="C61" s="3" t="s">
@@ -18632,7 +18632,7 @@
       <c r="B62" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="3" t="s">
         <v>418</v>
       </c>
       <c r="D62" s="2"/>
@@ -18663,7 +18663,7 @@
       <c r="A63" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="3" t="s">
         <v>423</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -18697,7 +18697,7 @@
       <c r="A64" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="3" t="s">
         <v>430</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -18734,7 +18734,7 @@
       <c r="B65" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>437</v>
       </c>
       <c r="D65" s="2"/>
@@ -18768,7 +18768,7 @@
       <c r="B66" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="3" t="s">
         <v>443</v>
       </c>
       <c r="D66" s="2"/>
@@ -18802,7 +18802,7 @@
       <c r="B67" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="3" t="s">
         <v>449</v>
       </c>
       <c r="D67" s="2"/>
@@ -18836,7 +18836,7 @@
       <c r="B68" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="3" t="s">
         <v>455</v>
       </c>
       <c r="D68" s="2"/>
@@ -18870,7 +18870,7 @@
       <c r="B69" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="3" t="s">
         <v>461</v>
       </c>
       <c r="D69" s="2"/>
@@ -18904,7 +18904,7 @@
       <c r="B70" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="3" t="s">
         <v>468</v>
       </c>
       <c r="D70" s="2"/>
@@ -18938,7 +18938,7 @@
       <c r="B71" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="3" t="s">
         <v>474</v>
       </c>
       <c r="D71" s="2"/>
@@ -18969,10 +18969,10 @@
       <c r="A72" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="3" t="s">
         <v>480</v>
       </c>
       <c r="D72" s="2"/>
@@ -19006,7 +19006,7 @@
       <c r="B73" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="3" t="s">
         <v>486</v>
       </c>
       <c r="D73" s="2"/>
@@ -19040,7 +19040,7 @@
       <c r="B74" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="3" t="s">
         <v>492</v>
       </c>
       <c r="D74" s="2"/>
@@ -19071,7 +19071,7 @@
       <c r="A75" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="3" t="s">
         <v>497</v>
       </c>
       <c r="C75" s="3" t="s">
@@ -19108,7 +19108,7 @@
       <c r="B76" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="3" t="s">
         <v>504</v>
       </c>
       <c r="D76" s="2"/>
@@ -19139,7 +19139,7 @@
       <c r="A77" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="3" t="s">
         <v>509</v>
       </c>
       <c r="C77" s="3" t="s">
@@ -19176,7 +19176,7 @@
       <c r="B78" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="3" t="s">
         <v>516</v>
       </c>
       <c r="D78" s="2"/>
@@ -19244,7 +19244,7 @@
       <c r="B80" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>528</v>
       </c>
       <c r="D80" s="2"/>
@@ -19278,7 +19278,7 @@
       <c r="B81" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="3" t="s">
         <v>534</v>
       </c>
       <c r="D81" s="2"/>
@@ -19309,7 +19309,7 @@
       <c r="A82" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="3" t="s">
         <v>539</v>
       </c>
       <c r="C82" s="3" t="s">
@@ -19346,7 +19346,7 @@
       <c r="B83" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="3" t="s">
         <v>546</v>
       </c>
       <c r="D83" s="2"/>
@@ -19377,7 +19377,7 @@
       <c r="A84" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="3" t="s">
         <v>551</v>
       </c>
       <c r="C84" s="3" t="s">
@@ -19411,7 +19411,7 @@
       <c r="A85" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="3" t="s">
         <v>557</v>
       </c>
       <c r="C85" s="3" t="s">
@@ -19445,10 +19445,10 @@
       <c r="A86" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="3" t="s">
         <v>564</v>
       </c>
       <c r="D86" s="2"/>
@@ -19482,7 +19482,7 @@
       <c r="B87" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="3" t="s">
         <v>570</v>
       </c>
       <c r="D87" s="2"/>
@@ -19516,7 +19516,7 @@
       <c r="B88" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="3" t="s">
         <v>576</v>
       </c>
       <c r="D88" s="2"/>
@@ -19547,10 +19547,10 @@
       <c r="A89" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="3" t="s">
         <v>582</v>
       </c>
       <c r="D89" s="2"/>
@@ -19581,7 +19581,7 @@
       <c r="A90" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="3" t="s">
         <v>587</v>
       </c>
       <c r="C90" s="3" t="s">
@@ -19615,10 +19615,10 @@
       <c r="A91" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="3" t="s">
         <v>594</v>
       </c>
       <c r="D91" s="2"/>
@@ -19652,7 +19652,7 @@
       <c r="B92" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="3" t="s">
         <v>601</v>
       </c>
       <c r="D92" s="2"/>
@@ -19683,7 +19683,7 @@
       <c r="A93" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="3" t="s">
         <v>606</v>
       </c>
       <c r="C93" s="3" t="s">
@@ -19720,7 +19720,7 @@
       <c r="B94" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="3" t="s">
         <v>613</v>
       </c>
       <c r="D94" s="2"/>
@@ -19754,7 +19754,7 @@
       <c r="B95" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="3" t="s">
         <v>619</v>
       </c>
       <c r="D95" s="2"/>
@@ -19785,7 +19785,7 @@
       <c r="A96" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="3" t="s">
         <v>624</v>
       </c>
       <c r="C96" s="3" t="s">
@@ -19819,10 +19819,10 @@
       <c r="A97" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="3" t="s">
         <v>632</v>
       </c>
       <c r="D97" s="2"/>
@@ -19890,7 +19890,7 @@
       <c r="B99" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="3" t="s">
         <v>644</v>
       </c>
       <c r="D99" s="2"/>
@@ -19924,7 +19924,7 @@
       <c r="B100" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="3" t="s">
         <v>650</v>
       </c>
       <c r="D100" s="2"/>
@@ -19958,7 +19958,7 @@
       <c r="B101" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="3" t="s">
         <v>656</v>
       </c>
       <c r="D101" s="2"/>
@@ -19989,10 +19989,10 @@
       <c r="A102" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="3" t="s">
         <v>662</v>
       </c>
       <c r="D102" s="2"/>
@@ -20060,7 +20060,7 @@
       <c r="B104" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="3" t="s">
         <v>674</v>
       </c>
       <c r="D104" s="2"/>
@@ -20091,7 +20091,7 @@
       <c r="A105" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="3" t="s">
         <v>679</v>
       </c>
       <c r="C105" s="3" t="s">
@@ -20128,7 +20128,7 @@
       <c r="B106" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="3" t="s">
         <v>686</v>
       </c>
       <c r="D106" s="2"/>
@@ -20162,7 +20162,7 @@
       <c r="B107" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="3" t="s">
         <v>693</v>
       </c>
       <c r="D107" s="2"/>
@@ -20193,7 +20193,7 @@
       <c r="A108" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="3" t="s">
         <v>698</v>
       </c>
       <c r="C108" s="3" t="s">
@@ -20227,10 +20227,10 @@
       <c r="A109" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="3" t="s">
         <v>705</v>
       </c>
       <c r="D109" s="2"/>
@@ -20261,10 +20261,10 @@
       <c r="A110" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="3" t="s">
         <v>711</v>
       </c>
       <c r="D110" s="2"/>
@@ -20295,10 +20295,10 @@
       <c r="A111" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="3" t="s">
         <v>717</v>
       </c>
       <c r="D111" s="2"/>
@@ -20329,10 +20329,10 @@
       <c r="A112" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="3" t="s">
         <v>723</v>
       </c>
       <c r="D112" s="2"/>
@@ -20363,10 +20363,10 @@
       <c r="A113" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="3" t="s">
         <v>729</v>
       </c>
       <c r="D113" s="2"/>
@@ -20400,7 +20400,7 @@
       <c r="B114" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="3" t="s">
         <v>735</v>
       </c>
       <c r="D114" s="2"/>
@@ -20431,10 +20431,10 @@
       <c r="A115" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="3" t="s">
         <v>741</v>
       </c>
       <c r="D115" s="2"/>
@@ -20465,10 +20465,10 @@
       <c r="A116" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="3" t="s">
         <v>747</v>
       </c>
       <c r="D116" s="2"/>
@@ -20499,10 +20499,10 @@
       <c r="A117" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="3" t="s">
         <v>753</v>
       </c>
       <c r="D117" s="2"/>
@@ -20533,10 +20533,10 @@
       <c r="A118" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="3" t="s">
         <v>759</v>
       </c>
       <c r="D118" s="2"/>
@@ -20567,10 +20567,10 @@
       <c r="A119" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="3" t="s">
         <v>765</v>
       </c>
       <c r="D119" s="2"/>
@@ -20601,7 +20601,7 @@
       <c r="A120" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="3" t="s">
         <v>770</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -20635,10 +20635,10 @@
       <c r="A121" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="3" t="s">
         <v>777</v>
       </c>
       <c r="D121" s="2"/>
@@ -20669,10 +20669,10 @@
       <c r="A122" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="3" t="s">
         <v>783</v>
       </c>
       <c r="D122" s="2"/>
@@ -20703,7 +20703,7 @@
       <c r="A123" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="3" t="s">
         <v>788</v>
       </c>
       <c r="C123" s="3" t="s">
@@ -20737,10 +20737,10 @@
       <c r="A124" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="3" t="s">
         <v>795</v>
       </c>
       <c r="D124" s="2"/>
@@ -20771,10 +20771,10 @@
       <c r="A125" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="3" t="s">
         <v>801</v>
       </c>
       <c r="D125" s="2"/>
@@ -20805,10 +20805,10 @@
       <c r="A126" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="3" t="s">
         <v>807</v>
       </c>
       <c r="D126" s="2"/>
@@ -20839,10 +20839,10 @@
       <c r="A127" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="3" t="s">
         <v>813</v>
       </c>
       <c r="D127" s="2"/>
@@ -20873,10 +20873,10 @@
       <c r="A128" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="3" t="s">
         <v>820</v>
       </c>
       <c r="D128" s="2"/>
@@ -20907,10 +20907,10 @@
       <c r="A129" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="3" t="s">
         <v>826</v>
       </c>
       <c r="D129" s="2"/>
@@ -20941,10 +20941,10 @@
       <c r="A130" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="3" t="s">
         <v>832</v>
       </c>
       <c r="D130" s="2"/>
@@ -20975,10 +20975,10 @@
       <c r="A131" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="3" t="s">
         <v>838</v>
       </c>
       <c r="D131" s="2"/>
@@ -21009,10 +21009,10 @@
       <c r="A132" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="3" t="s">
         <v>844</v>
       </c>
       <c r="D132" s="2"/>
@@ -21043,10 +21043,10 @@
       <c r="A133" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="3" t="s">
         <v>850</v>
       </c>
       <c r="D133" s="2"/>
@@ -21077,10 +21077,10 @@
       <c r="A134" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="3" t="s">
         <v>856</v>
       </c>
       <c r="D134" s="2"/>
@@ -21111,10 +21111,10 @@
       <c r="A135" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="3" t="s">
         <v>862</v>
       </c>
       <c r="D135" s="2"/>
@@ -21145,7 +21145,7 @@
       <c r="A136" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="3" t="s">
         <v>867</v>
       </c>
       <c r="C136" s="2" t="s">
@@ -21179,10 +21179,10 @@
       <c r="A137" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D137" s="2"/>
@@ -21213,10 +21213,10 @@
       <c r="A138" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="3" t="s">
         <v>879</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="3" t="s">
         <v>880</v>
       </c>
       <c r="D138" s="2"/>
@@ -21247,10 +21247,10 @@
       <c r="A139" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="3" t="s">
         <v>886</v>
       </c>
       <c r="D139" s="2"/>
@@ -21281,10 +21281,10 @@
       <c r="A140" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="3" t="s">
         <v>892</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="3" t="s">
         <v>893</v>
       </c>
       <c r="D140" s="2"/>
@@ -21315,10 +21315,10 @@
       <c r="A141" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="3" t="s">
         <v>899</v>
       </c>
       <c r="D141" s="2"/>
@@ -21349,10 +21349,10 @@
       <c r="A142" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="3" t="s">
         <v>905</v>
       </c>
       <c r="D142" s="2"/>
@@ -21383,10 +21383,10 @@
       <c r="A143" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="3" t="s">
         <v>910</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="3" t="s">
         <v>911</v>
       </c>
       <c r="D143" s="2"/>
@@ -21417,10 +21417,10 @@
       <c r="A144" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="3" t="s">
         <v>916</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="3" t="s">
         <v>917</v>
       </c>
       <c r="D144" s="2"/>
@@ -21451,10 +21451,10 @@
       <c r="A145" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="3" t="s">
         <v>922</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="3" t="s">
         <v>923</v>
       </c>
       <c r="D145" s="2"/>
@@ -21485,10 +21485,10 @@
       <c r="A146" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="3" t="s">
         <v>929</v>
       </c>
       <c r="D146" s="2"/>
@@ -21519,10 +21519,10 @@
       <c r="A147" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="3" t="s">
         <v>935</v>
       </c>
       <c r="D147" s="2"/>
@@ -21553,10 +21553,10 @@
       <c r="A148" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B148" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="3" t="s">
         <v>941</v>
       </c>
       <c r="D148" s="2"/>
@@ -21587,10 +21587,10 @@
       <c r="A149" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="3" t="s">
         <v>947</v>
       </c>
       <c r="D149" s="2"/>
@@ -21621,10 +21621,10 @@
       <c r="A150" s="2" t="s">
         <v>951</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="3" t="s">
         <v>953</v>
       </c>
       <c r="D150" s="2"/>
@@ -21655,10 +21655,10 @@
       <c r="A151" s="2" t="s">
         <v>957</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="3" t="s">
         <v>958</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="3" t="s">
         <v>959</v>
       </c>
       <c r="D151" s="2"/>
@@ -21689,10 +21689,10 @@
       <c r="A152" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B152" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="3" t="s">
         <v>965</v>
       </c>
       <c r="D152" s="2"/>
@@ -21723,10 +21723,10 @@
       <c r="A153" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="B153" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="3" t="s">
         <v>971</v>
       </c>
       <c r="D153" s="2"/>
@@ -21757,10 +21757,10 @@
       <c r="A154" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B154" s="3" t="s">
         <v>976</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="3" t="s">
         <v>977</v>
       </c>
       <c r="D154" s="2"/>
@@ -21791,10 +21791,10 @@
       <c r="A155" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="B155" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="3" t="s">
         <v>983</v>
       </c>
       <c r="D155" s="2"/>
@@ -21825,10 +21825,10 @@
       <c r="A156" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B156" s="3" t="s">
         <v>988</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="3" t="s">
         <v>989</v>
       </c>
       <c r="D156" s="2"/>
@@ -21859,10 +21859,10 @@
       <c r="A157" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="B157" s="3" t="s">
         <v>994</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="3" t="s">
         <v>995</v>
       </c>
       <c r="D157" s="2"/>
@@ -21893,7 +21893,7 @@
       <c r="A158" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="B158" s="3" t="s">
         <v>1000</v>
       </c>
       <c r="C158" s="3" t="s">
@@ -21927,10 +21927,10 @@
       <c r="A159" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B159" s="3" t="s">
         <v>1006</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="3" t="s">
         <v>1007</v>
       </c>
       <c r="D159" s="2"/>
@@ -21964,7 +21964,7 @@
       <c r="B160" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="3" t="s">
         <v>1013</v>
       </c>
       <c r="D160" s="2"/>
@@ -21995,10 +21995,10 @@
       <c r="A161" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="B161" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="3" t="s">
         <v>1019</v>
       </c>
       <c r="D161" s="2"/>
@@ -22032,7 +22032,7 @@
       <c r="B162" s="3" t="s">
         <v>1024</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="3" t="s">
         <v>1025</v>
       </c>
       <c r="D162" s="2"/>
@@ -22063,10 +22063,10 @@
       <c r="A163" s="2" t="s">
         <v>1029</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B163" s="3" t="s">
         <v>1030</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C163" s="3" t="s">
         <v>1031</v>
       </c>
       <c r="D163" s="2"/>
@@ -22097,10 +22097,10 @@
       <c r="A164" s="2" t="s">
         <v>1035</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="B164" s="3" t="s">
         <v>1036</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C164" s="3" t="s">
         <v>1037</v>
       </c>
       <c r="D164" s="2"/>
@@ -22131,10 +22131,10 @@
       <c r="A165" s="2" t="s">
         <v>1041</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B165" s="3" t="s">
         <v>1042</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C165" s="3" t="s">
         <v>1043</v>
       </c>
       <c r="D165" s="2"/>
@@ -22165,10 +22165,10 @@
       <c r="A166" s="2" t="s">
         <v>1047</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B166" s="3" t="s">
         <v>1048</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C166" s="3" t="s">
         <v>1049</v>
       </c>
       <c r="D166" s="2"/>
@@ -22199,10 +22199,10 @@
       <c r="A167" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B167" s="3" t="s">
         <v>1054</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C167" s="3" t="s">
         <v>1055</v>
       </c>
       <c r="D167" s="2"/>
@@ -22233,10 +22233,10 @@
       <c r="A168" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="3" t="s">
         <v>1060</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="C168" s="3" t="s">
         <v>1061</v>
       </c>
       <c r="D168" s="2"/>
@@ -22267,10 +22267,10 @@
       <c r="A169" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="3" t="s">
         <v>1066</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="C169" s="3" t="s">
         <v>1067</v>
       </c>
       <c r="D169" s="2"/>
@@ -22301,7 +22301,7 @@
       <c r="A170" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="B170" s="3" t="s">
         <v>1072</v>
       </c>
       <c r="C170" s="3" t="s">
@@ -22335,10 +22335,10 @@
       <c r="A171" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="B171" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="C171" s="2" t="s">
+      <c r="C171" s="3" t="s">
         <v>1079</v>
       </c>
       <c r="D171" s="2"/>
@@ -22369,7 +22369,7 @@
       <c r="A172" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="B172" s="3" t="s">
         <v>1084</v>
       </c>
       <c r="C172" s="2" t="s">
@@ -22406,7 +22406,7 @@
       <c r="B173" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="C173" s="2" t="s">
+      <c r="C173" s="3" t="s">
         <v>1091</v>
       </c>
       <c r="D173" s="2"/>
@@ -22471,7 +22471,7 @@
       <c r="A175" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="B175" s="3" t="s">
         <v>1102</v>
       </c>
       <c r="C175" s="2" t="s">
@@ -22505,10 +22505,10 @@
       <c r="A176" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="B176" s="3" t="s">
         <v>1108</v>
       </c>
-      <c r="C176" s="2" t="s">
+      <c r="C176" s="3" t="s">
         <v>1109</v>
       </c>
       <c r="D176" s="2"/>
@@ -22539,10 +22539,10 @@
       <c r="A177" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="B177" s="3" t="s">
         <v>1114</v>
       </c>
-      <c r="C177" s="2" t="s">
+      <c r="C177" s="3" t="s">
         <v>1115</v>
       </c>
       <c r="D177" s="2"/>
@@ -22573,10 +22573,10 @@
       <c r="A178" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="B178" s="3" t="s">
         <v>1120</v>
       </c>
-      <c r="C178" s="2" t="s">
+      <c r="C178" s="3" t="s">
         <v>1121</v>
       </c>
       <c r="D178" s="2"/>
@@ -22607,10 +22607,10 @@
       <c r="A179" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="B179" s="3" t="s">
         <v>1126</v>
       </c>
-      <c r="C179" s="2" t="s">
+      <c r="C179" s="3" t="s">
         <v>1127</v>
       </c>
       <c r="D179" s="2"/>
@@ -22641,10 +22641,10 @@
       <c r="A180" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="B180" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="C180" s="2" t="s">
+      <c r="C180" s="3" t="s">
         <v>1133</v>
       </c>
       <c r="D180" s="2"/>
@@ -22675,10 +22675,10 @@
       <c r="A181" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="B181" s="3" t="s">
         <v>1138</v>
       </c>
-      <c r="C181" s="2" t="s">
+      <c r="C181" s="3" t="s">
         <v>1139</v>
       </c>
       <c r="D181" s="2"/>
@@ -22709,10 +22709,10 @@
       <c r="A182" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="B182" s="3" t="s">
         <v>1144</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="C182" s="3" t="s">
         <v>1145</v>
       </c>
       <c r="D182" s="2"/>
@@ -22743,10 +22743,10 @@
       <c r="A183" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="B183" s="3" t="s">
         <v>1150</v>
       </c>
-      <c r="C183" s="2" t="s">
+      <c r="C183" s="3" t="s">
         <v>1151</v>
       </c>
       <c r="D183" s="2"/>
@@ -22777,10 +22777,10 @@
       <c r="A184" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="B184" s="3" t="s">
         <v>1156</v>
       </c>
-      <c r="C184" s="2" t="s">
+      <c r="C184" s="3" t="s">
         <v>1157</v>
       </c>
       <c r="D184" s="2"/>
@@ -22811,10 +22811,10 @@
       <c r="A185" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="B185" s="3" t="s">
         <v>1162</v>
       </c>
-      <c r="C185" s="2" t="s">
+      <c r="C185" s="3" t="s">
         <v>1163</v>
       </c>
       <c r="D185" s="2"/>
@@ -22848,7 +22848,7 @@
       <c r="B186" s="3" t="s">
         <v>1168</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="C186" s="3" t="s">
         <v>1169</v>
       </c>
       <c r="D186" s="2"/>
@@ -22879,10 +22879,10 @@
       <c r="A187" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B187" s="3" t="s">
         <v>1174</v>
       </c>
-      <c r="C187" s="2" t="s">
+      <c r="C187" s="3" t="s">
         <v>1175</v>
       </c>
       <c r="D187" s="2"/>
@@ -22913,10 +22913,10 @@
       <c r="A188" s="2" t="s">
         <v>1179</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="B188" s="3" t="s">
         <v>1180</v>
       </c>
-      <c r="C188" s="2" t="s">
+      <c r="C188" s="3" t="s">
         <v>1181</v>
       </c>
       <c r="D188" s="2"/>
@@ -22947,10 +22947,10 @@
       <c r="A189" s="2" t="s">
         <v>1185</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B189" s="3" t="s">
         <v>1186</v>
       </c>
-      <c r="C189" s="2" t="s">
+      <c r="C189" s="3" t="s">
         <v>1187</v>
       </c>
       <c r="D189" s="2"/>
@@ -22981,10 +22981,10 @@
       <c r="A190" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B190" s="3" t="s">
         <v>1192</v>
       </c>
-      <c r="C190" s="2" t="s">
+      <c r="C190" s="3" t="s">
         <v>1193</v>
       </c>
       <c r="D190" s="2"/>
@@ -23018,7 +23018,7 @@
       <c r="B191" s="3" t="s">
         <v>1198</v>
       </c>
-      <c r="C191" s="2" t="s">
+      <c r="C191" s="3" t="s">
         <v>1199</v>
       </c>
       <c r="D191" s="2"/>
@@ -23049,10 +23049,10 @@
       <c r="A192" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="B192" s="3" t="s">
         <v>1204</v>
       </c>
-      <c r="C192" s="2" t="s">
+      <c r="C192" s="3" t="s">
         <v>1205</v>
       </c>
       <c r="D192" s="2"/>
@@ -23083,10 +23083,10 @@
       <c r="A193" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="B193" s="3" t="s">
         <v>1210</v>
       </c>
-      <c r="C193" s="2" t="s">
+      <c r="C193" s="3" t="s">
         <v>1211</v>
       </c>
       <c r="D193" s="2"/>
@@ -23117,10 +23117,10 @@
       <c r="A194" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B194" s="3" t="s">
         <v>1216</v>
       </c>
-      <c r="C194" s="2" t="s">
+      <c r="C194" s="3" t="s">
         <v>1217</v>
       </c>
       <c r="D194" s="2"/>
@@ -23151,10 +23151,10 @@
       <c r="A195" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="B195" s="3" t="s">
         <v>1222</v>
       </c>
-      <c r="C195" s="2" t="s">
+      <c r="C195" s="3" t="s">
         <v>1223</v>
       </c>
       <c r="D195" s="2"/>
@@ -23185,10 +23185,10 @@
       <c r="A196" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="B196" s="3" t="s">
         <v>1228</v>
       </c>
-      <c r="C196" s="2" t="s">
+      <c r="C196" s="3" t="s">
         <v>1229</v>
       </c>
       <c r="D196" s="2"/>
@@ -23219,10 +23219,10 @@
       <c r="A197" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="B197" s="2" t="s">
+      <c r="B197" s="3" t="s">
         <v>1234</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="C197" s="3" t="s">
         <v>1235</v>
       </c>
       <c r="D197" s="2"/>
@@ -23253,10 +23253,10 @@
       <c r="A198" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B198" s="3" t="s">
         <v>1240</v>
       </c>
-      <c r="C198" s="2" t="s">
+      <c r="C198" s="3" t="s">
         <v>1241</v>
       </c>
       <c r="D198" s="2"/>
@@ -23287,10 +23287,10 @@
       <c r="A199" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B199" s="3" t="s">
         <v>1246</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C199" s="3" t="s">
         <v>1247</v>
       </c>
       <c r="D199" s="2"/>
@@ -23321,10 +23321,10 @@
       <c r="A200" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="B200" s="3" t="s">
         <v>1252</v>
       </c>
-      <c r="C200" s="2" t="s">
+      <c r="C200" s="3" t="s">
         <v>1253</v>
       </c>
       <c r="D200" s="2"/>
@@ -23355,10 +23355,10 @@
       <c r="A201" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="B201" s="2" t="s">
+      <c r="B201" s="3" t="s">
         <v>1258</v>
       </c>
-      <c r="C201" s="2" t="s">
+      <c r="C201" s="3" t="s">
         <v>1259</v>
       </c>
       <c r="D201" s="2"/>
@@ -23389,10 +23389,10 @@
       <c r="A202" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="B202" s="2" t="s">
+      <c r="B202" s="3" t="s">
         <v>1264</v>
       </c>
-      <c r="C202" s="2" t="s">
+      <c r="C202" s="3" t="s">
         <v>1265</v>
       </c>
       <c r="D202" s="2"/>
@@ -23423,10 +23423,10 @@
       <c r="A203" s="2" t="s">
         <v>1269</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B203" s="3" t="s">
         <v>1270</v>
       </c>
-      <c r="C203" s="2" t="s">
+      <c r="C203" s="3" t="s">
         <v>1271</v>
       </c>
       <c r="D203" s="2"/>
@@ -23457,10 +23457,10 @@
       <c r="A204" s="2" t="s">
         <v>1275</v>
       </c>
-      <c r="B204" s="2" t="s">
+      <c r="B204" s="3" t="s">
         <v>1276</v>
       </c>
-      <c r="C204" s="2" t="s">
+      <c r="C204" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="D204" s="2"/>
@@ -23491,7 +23491,7 @@
       <c r="A205" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="B205" s="2" t="s">
+      <c r="B205" s="3" t="s">
         <v>1282</v>
       </c>
       <c r="C205" s="3" t="s">
@@ -23525,10 +23525,10 @@
       <c r="A206" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="B206" s="2" t="s">
+      <c r="B206" s="3" t="s">
         <v>1288</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="C206" s="3" t="s">
         <v>1289</v>
       </c>
       <c r="D206" s="2"/>
@@ -23559,10 +23559,10 @@
       <c r="A207" s="2" t="s">
         <v>1293</v>
       </c>
-      <c r="B207" s="2" t="s">
+      <c r="B207" s="3" t="s">
         <v>1294</v>
       </c>
-      <c r="C207" s="2" t="s">
+      <c r="C207" s="3" t="s">
         <v>1295</v>
       </c>
       <c r="D207" s="2"/>
@@ -23593,10 +23593,10 @@
       <c r="A208" s="2" t="s">
         <v>1299</v>
       </c>
-      <c r="B208" s="2" t="s">
+      <c r="B208" s="3" t="s">
         <v>1300</v>
       </c>
-      <c r="C208" s="2" t="s">
+      <c r="C208" s="3" t="s">
         <v>1301</v>
       </c>
       <c r="D208" s="2"/>
@@ -23627,10 +23627,10 @@
       <c r="A209" s="2" t="s">
         <v>1305</v>
       </c>
-      <c r="B209" s="2" t="s">
+      <c r="B209" s="3" t="s">
         <v>1306</v>
       </c>
-      <c r="C209" s="2" t="s">
+      <c r="C209" s="3" t="s">
         <v>1307</v>
       </c>
       <c r="D209" s="2"/>
@@ -23661,7 +23661,7 @@
       <c r="A210" s="2" t="s">
         <v>1311</v>
       </c>
-      <c r="B210" s="2" t="s">
+      <c r="B210" s="3" t="s">
         <v>1312</v>
       </c>
       <c r="C210" s="2" t="s">
@@ -23695,10 +23695,10 @@
       <c r="A211" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="B211" s="2" t="s">
+      <c r="B211" s="3" t="s">
         <v>1318</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="C211" s="3" t="s">
         <v>1319</v>
       </c>
       <c r="D211" s="2"/>
@@ -23729,10 +23729,10 @@
       <c r="A212" s="2" t="s">
         <v>1323</v>
       </c>
-      <c r="B212" s="2" t="s">
+      <c r="B212" s="3" t="s">
         <v>1324</v>
       </c>
-      <c r="C212" s="2" t="s">
+      <c r="C212" s="3" t="s">
         <v>1325</v>
       </c>
       <c r="D212" s="2"/>
@@ -23763,10 +23763,10 @@
       <c r="A213" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="B213" s="3" t="s">
         <v>1330</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="C213" s="3" t="s">
         <v>1331</v>
       </c>
       <c r="D213" s="2"/>
@@ -23797,10 +23797,10 @@
       <c r="A214" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="B214" s="2" t="s">
+      <c r="B214" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="C214" s="2" t="s">
+      <c r="C214" s="3" t="s">
         <v>1337</v>
       </c>
       <c r="D214" s="2"/>
@@ -23831,10 +23831,10 @@
       <c r="A215" s="2" t="s">
         <v>1341</v>
       </c>
-      <c r="B215" s="2" t="s">
+      <c r="B215" s="3" t="s">
         <v>1342</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="C215" s="3" t="s">
         <v>1343</v>
       </c>
       <c r="D215" s="2"/>
@@ -23865,10 +23865,10 @@
       <c r="A216" s="2" t="s">
         <v>1347</v>
       </c>
-      <c r="B216" s="2" t="s">
+      <c r="B216" s="3" t="s">
         <v>1348</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="C216" s="3" t="s">
         <v>1349</v>
       </c>
       <c r="D216" s="2"/>
@@ -23899,7 +23899,7 @@
       <c r="A217" s="2" t="s">
         <v>1353</v>
       </c>
-      <c r="B217" s="2" t="s">
+      <c r="B217" s="3" t="s">
         <v>1354</v>
       </c>
       <c r="C217" s="3" t="s">
@@ -23933,10 +23933,10 @@
       <c r="A218" s="2" t="s">
         <v>1359</v>
       </c>
-      <c r="B218" s="2" t="s">
+      <c r="B218" s="3" t="s">
         <v>1360</v>
       </c>
-      <c r="C218" s="2" t="s">
+      <c r="C218" s="3" t="s">
         <v>1361</v>
       </c>
       <c r="D218" s="2"/>
@@ -23967,10 +23967,10 @@
       <c r="A219" s="2" t="s">
         <v>1365</v>
       </c>
-      <c r="B219" s="2" t="s">
+      <c r="B219" s="3" t="s">
         <v>1366</v>
       </c>
-      <c r="C219" s="2" t="s">
+      <c r="C219" s="3" t="s">
         <v>1367</v>
       </c>
       <c r="D219" s="2"/>
@@ -24001,10 +24001,10 @@
       <c r="A220" s="2" t="s">
         <v>1371</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="B220" s="3" t="s">
         <v>1372</v>
       </c>
-      <c r="C220" s="2" t="s">
+      <c r="C220" s="3" t="s">
         <v>1373</v>
       </c>
       <c r="D220" s="2"/>
@@ -24035,10 +24035,10 @@
       <c r="A221" s="2" t="s">
         <v>1377</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="B221" s="3" t="s">
         <v>1378</v>
       </c>
-      <c r="C221" s="2" t="s">
+      <c r="C221" s="3" t="s">
         <v>1379</v>
       </c>
       <c r="D221" s="2"/>
@@ -24069,10 +24069,10 @@
       <c r="A222" s="2" t="s">
         <v>1383</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="3" t="s">
         <v>1384</v>
       </c>
-      <c r="C222" s="2" t="s">
+      <c r="C222" s="3" t="s">
         <v>1385</v>
       </c>
       <c r="D222" s="2"/>
@@ -24103,10 +24103,10 @@
       <c r="A223" s="2" t="s">
         <v>1389</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="B223" s="3" t="s">
         <v>1390</v>
       </c>
-      <c r="C223" s="2" t="s">
+      <c r="C223" s="3" t="s">
         <v>1391</v>
       </c>
       <c r="D223" s="2"/>
@@ -24137,10 +24137,10 @@
       <c r="A224" s="2" t="s">
         <v>1395</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="B224" s="3" t="s">
         <v>1396</v>
       </c>
-      <c r="C224" s="2" t="s">
+      <c r="C224" s="3" t="s">
         <v>1397</v>
       </c>
       <c r="D224" s="2"/>
@@ -24171,10 +24171,10 @@
       <c r="A225" s="2" t="s">
         <v>1401</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="B225" s="3" t="s">
         <v>1402</v>
       </c>
-      <c r="C225" s="2" t="s">
+      <c r="C225" s="3" t="s">
         <v>1403</v>
       </c>
       <c r="D225" s="2"/>
@@ -24205,10 +24205,10 @@
       <c r="A226" s="2" t="s">
         <v>1407</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="B226" s="3" t="s">
         <v>1408</v>
       </c>
-      <c r="C226" s="2" t="s">
+      <c r="C226" s="3" t="s">
         <v>1409</v>
       </c>
       <c r="D226" s="2"/>
@@ -24239,7 +24239,7 @@
       <c r="A227" s="2" t="s">
         <v>1413</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="B227" s="3" t="s">
         <v>1414</v>
       </c>
       <c r="C227" s="2" t="s">
@@ -24273,10 +24273,10 @@
       <c r="A228" s="2" t="s">
         <v>1419</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="B228" s="3" t="s">
         <v>1420</v>
       </c>
-      <c r="C228" s="2" t="s">
+      <c r="C228" s="3" t="s">
         <v>1421</v>
       </c>
       <c r="D228" s="2"/>
@@ -24307,10 +24307,10 @@
       <c r="A229" s="2" t="s">
         <v>1425</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="B229" s="3" t="s">
         <v>1426</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="C229" s="3" t="s">
         <v>1427</v>
       </c>
       <c r="D229" s="2"/>
@@ -24341,7 +24341,7 @@
       <c r="A230" s="2" t="s">
         <v>1431</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="B230" s="3" t="s">
         <v>1432</v>
       </c>
       <c r="C230" s="3" t="s">
@@ -24375,10 +24375,10 @@
       <c r="A231" s="2" t="s">
         <v>1437</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="B231" s="3" t="s">
         <v>1438</v>
       </c>
-      <c r="C231" s="2" t="s">
+      <c r="C231" s="3" t="s">
         <v>1439</v>
       </c>
       <c r="D231" s="2"/>
@@ -24409,7 +24409,7 @@
       <c r="A232" s="2" t="s">
         <v>1443</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="B232" s="3" t="s">
         <v>1444</v>
       </c>
       <c r="C232" s="3" t="s">
@@ -24446,7 +24446,7 @@
       <c r="B233" s="3" t="s">
         <v>1450</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="C233" s="3" t="s">
         <v>1451</v>
       </c>
       <c r="D233" s="2"/>
@@ -24477,10 +24477,10 @@
       <c r="A234" s="2" t="s">
         <v>1455</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="B234" s="3" t="s">
         <v>1456</v>
       </c>
-      <c r="C234" s="2" t="s">
+      <c r="C234" s="3" t="s">
         <v>1457</v>
       </c>
       <c r="D234" s="2"/>
@@ -24511,10 +24511,10 @@
       <c r="A235" s="2" t="s">
         <v>1461</v>
       </c>
-      <c r="B235" s="2" t="s">
+      <c r="B235" s="3" t="s">
         <v>1462</v>
       </c>
-      <c r="C235" s="2" t="s">
+      <c r="C235" s="3" t="s">
         <v>1463</v>
       </c>
       <c r="D235" s="2"/>
@@ -24545,10 +24545,10 @@
       <c r="A236" s="2" t="s">
         <v>1467</v>
       </c>
-      <c r="B236" s="2" t="s">
+      <c r="B236" s="3" t="s">
         <v>1468</v>
       </c>
-      <c r="C236" s="2" t="s">
+      <c r="C236" s="3" t="s">
         <v>1469</v>
       </c>
       <c r="D236" s="2"/>
@@ -24579,10 +24579,10 @@
       <c r="A237" s="2" t="s">
         <v>1473</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="B237" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="C237" s="2" t="s">
+      <c r="C237" s="3" t="s">
         <v>1475</v>
       </c>
       <c r="D237" s="2"/>
@@ -24613,10 +24613,10 @@
       <c r="A238" s="2" t="s">
         <v>1479</v>
       </c>
-      <c r="B238" s="2" t="s">
+      <c r="B238" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="C238" s="2" t="s">
+      <c r="C238" s="3" t="s">
         <v>1481</v>
       </c>
       <c r="D238" s="2"/>
@@ -24647,10 +24647,10 @@
       <c r="A239" s="2" t="s">
         <v>1485</v>
       </c>
-      <c r="B239" s="2" t="s">
+      <c r="B239" s="3" t="s">
         <v>1486</v>
       </c>
-      <c r="C239" s="2" t="s">
+      <c r="C239" s="3" t="s">
         <v>1487</v>
       </c>
       <c r="D239" s="2"/>
@@ -24681,10 +24681,10 @@
       <c r="A240" s="2" t="s">
         <v>1491</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="B240" s="3" t="s">
         <v>1492</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="C240" s="3" t="s">
         <v>1493</v>
       </c>
       <c r="D240" s="2"/>
@@ -24715,10 +24715,10 @@
       <c r="A241" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="B241" s="2" t="s">
+      <c r="B241" s="3" t="s">
         <v>1498</v>
       </c>
-      <c r="C241" s="2" t="s">
+      <c r="C241" s="3" t="s">
         <v>1499</v>
       </c>
       <c r="D241" s="2"/>
@@ -24749,10 +24749,10 @@
       <c r="A242" s="2" t="s">
         <v>1503</v>
       </c>
-      <c r="B242" s="2" t="s">
+      <c r="B242" s="3" t="s">
         <v>1504</v>
       </c>
-      <c r="C242" s="2" t="s">
+      <c r="C242" s="3" t="s">
         <v>1505</v>
       </c>
       <c r="D242" s="2"/>
@@ -24783,10 +24783,10 @@
       <c r="A243" s="2" t="s">
         <v>1509</v>
       </c>
-      <c r="B243" s="2" t="s">
+      <c r="B243" s="3" t="s">
         <v>1510</v>
       </c>
-      <c r="C243" s="2" t="s">
+      <c r="C243" s="3" t="s">
         <v>1511</v>
       </c>
       <c r="D243" s="2"/>
@@ -24817,10 +24817,10 @@
       <c r="A244" s="2" t="s">
         <v>1515</v>
       </c>
-      <c r="B244" s="2" t="s">
+      <c r="B244" s="3" t="s">
         <v>1516</v>
       </c>
-      <c r="C244" s="2" t="s">
+      <c r="C244" s="3" t="s">
         <v>1517</v>
       </c>
       <c r="D244" s="2"/>
@@ -24851,10 +24851,10 @@
       <c r="A245" s="2" t="s">
         <v>1521</v>
       </c>
-      <c r="B245" s="2" t="s">
+      <c r="B245" s="3" t="s">
         <v>1522</v>
       </c>
-      <c r="C245" s="2" t="s">
+      <c r="C245" s="3" t="s">
         <v>1523</v>
       </c>
       <c r="D245" s="2"/>
@@ -24885,10 +24885,10 @@
       <c r="A246" s="2" t="s">
         <v>1527</v>
       </c>
-      <c r="B246" s="2" t="s">
+      <c r="B246" s="3" t="s">
         <v>1528</v>
       </c>
-      <c r="C246" s="2" t="s">
+      <c r="C246" s="3" t="s">
         <v>1529</v>
       </c>
       <c r="D246" s="2"/>
@@ -24919,10 +24919,10 @@
       <c r="A247" s="2" t="s">
         <v>1533</v>
       </c>
-      <c r="B247" s="2" t="s">
+      <c r="B247" s="3" t="s">
         <v>1534</v>
       </c>
-      <c r="C247" s="2" t="s">
+      <c r="C247" s="3" t="s">
         <v>1535</v>
       </c>
       <c r="D247" s="2"/>
@@ -24953,10 +24953,10 @@
       <c r="A248" s="2" t="s">
         <v>1539</v>
       </c>
-      <c r="B248" s="2" t="s">
+      <c r="B248" s="3" t="s">
         <v>1540</v>
       </c>
-      <c r="C248" s="2" t="s">
+      <c r="C248" s="3" t="s">
         <v>1541</v>
       </c>
       <c r="D248" s="2"/>
@@ -24987,10 +24987,10 @@
       <c r="A249" s="2" t="s">
         <v>1545</v>
       </c>
-      <c r="B249" s="2" t="s">
+      <c r="B249" s="3" t="s">
         <v>1546</v>
       </c>
-      <c r="C249" s="2" t="s">
+      <c r="C249" s="3" t="s">
         <v>1547</v>
       </c>
       <c r="D249" s="2"/>
@@ -25021,10 +25021,10 @@
       <c r="A250" s="2" t="s">
         <v>1551</v>
       </c>
-      <c r="B250" s="2" t="s">
+      <c r="B250" s="3" t="s">
         <v>1552</v>
       </c>
-      <c r="C250" s="2" t="s">
+      <c r="C250" s="3" t="s">
         <v>1553</v>
       </c>
       <c r="D250" s="2"/>
@@ -25055,10 +25055,10 @@
       <c r="A251" s="2" t="s">
         <v>1557</v>
       </c>
-      <c r="B251" s="2" t="s">
+      <c r="B251" s="3" t="s">
         <v>1558</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="C251" s="3" t="s">
         <v>1559</v>
       </c>
       <c r="D251" s="2"/>
@@ -25089,10 +25089,10 @@
       <c r="A252" s="2" t="s">
         <v>1563</v>
       </c>
-      <c r="B252" s="2" t="s">
+      <c r="B252" s="3" t="s">
         <v>1564</v>
       </c>
-      <c r="C252" s="2" t="s">
+      <c r="C252" s="3" t="s">
         <v>1565</v>
       </c>
       <c r="D252" s="2"/>
@@ -25123,10 +25123,10 @@
       <c r="A253" s="2" t="s">
         <v>1569</v>
       </c>
-      <c r="B253" s="2" t="s">
+      <c r="B253" s="3" t="s">
         <v>1570</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="C253" s="3" t="s">
         <v>1571</v>
       </c>
       <c r="D253" s="2"/>
@@ -25157,10 +25157,10 @@
       <c r="A254" s="2" t="s">
         <v>1575</v>
       </c>
-      <c r="B254" s="2" t="s">
+      <c r="B254" s="3" t="s">
         <v>1576</v>
       </c>
-      <c r="C254" s="2" t="s">
+      <c r="C254" s="3" t="s">
         <v>1577</v>
       </c>
       <c r="D254" s="2"/>
@@ -25191,10 +25191,10 @@
       <c r="A255" s="2" t="s">
         <v>1581</v>
       </c>
-      <c r="B255" s="2" t="s">
+      <c r="B255" s="3" t="s">
         <v>1582</v>
       </c>
-      <c r="C255" s="2" t="s">
+      <c r="C255" s="3" t="s">
         <v>1583</v>
       </c>
       <c r="D255" s="2"/>
@@ -25225,7 +25225,7 @@
       <c r="A256" s="2" t="s">
         <v>1587</v>
       </c>
-      <c r="B256" s="2" t="s">
+      <c r="B256" s="3" t="s">
         <v>1588</v>
       </c>
       <c r="C256" s="3" t="s">
@@ -25259,10 +25259,10 @@
       <c r="A257" s="2" t="s">
         <v>1593</v>
       </c>
-      <c r="B257" s="2" t="s">
+      <c r="B257" s="3" t="s">
         <v>1594</v>
       </c>
-      <c r="C257" s="2" t="s">
+      <c r="C257" s="3" t="s">
         <v>1595</v>
       </c>
       <c r="D257" s="2"/>
@@ -25293,7 +25293,7 @@
       <c r="A258" s="2" t="s">
         <v>1599</v>
       </c>
-      <c r="B258" s="2" t="s">
+      <c r="B258" s="3" t="s">
         <v>1600</v>
       </c>
       <c r="C258" s="3" t="s">
@@ -25327,10 +25327,10 @@
       <c r="A259" s="2" t="s">
         <v>1605</v>
       </c>
-      <c r="B259" s="2" t="s">
+      <c r="B259" s="3" t="s">
         <v>1606</v>
       </c>
-      <c r="C259" s="2" t="s">
+      <c r="C259" s="3" t="s">
         <v>1607</v>
       </c>
       <c r="D259" s="2"/>
@@ -25361,10 +25361,10 @@
       <c r="A260" s="2" t="s">
         <v>1611</v>
       </c>
-      <c r="B260" s="2" t="s">
+      <c r="B260" s="3" t="s">
         <v>1612</v>
       </c>
-      <c r="C260" s="2" t="s">
+      <c r="C260" s="3" t="s">
         <v>1613</v>
       </c>
       <c r="D260" s="2"/>
@@ -25395,10 +25395,10 @@
       <c r="A261" s="2" t="s">
         <v>1617</v>
       </c>
-      <c r="B261" s="2" t="s">
+      <c r="B261" s="3" t="s">
         <v>1618</v>
       </c>
-      <c r="C261" s="2" t="s">
+      <c r="C261" s="3" t="s">
         <v>1619</v>
       </c>
       <c r="D261" s="2"/>
@@ -25429,7 +25429,7 @@
       <c r="A262" s="2" t="s">
         <v>1623</v>
       </c>
-      <c r="B262" s="2" t="s">
+      <c r="B262" s="3" t="s">
         <v>1624</v>
       </c>
       <c r="C262" s="3" t="s">
@@ -25463,10 +25463,10 @@
       <c r="A263" s="2" t="s">
         <v>1629</v>
       </c>
-      <c r="B263" s="2" t="s">
+      <c r="B263" s="3" t="s">
         <v>1630</v>
       </c>
-      <c r="C263" s="2" t="s">
+      <c r="C263" s="3" t="s">
         <v>1631</v>
       </c>
       <c r="D263" s="2"/>
@@ -25531,10 +25531,10 @@
       <c r="A265" s="2" t="s">
         <v>1641</v>
       </c>
-      <c r="B265" s="2" t="s">
+      <c r="B265" s="3" t="s">
         <v>1642</v>
       </c>
-      <c r="C265" s="2" t="s">
+      <c r="C265" s="3" t="s">
         <v>1643</v>
       </c>
       <c r="D265" s="2"/>
@@ -25565,10 +25565,10 @@
       <c r="A266" s="2" t="s">
         <v>1647</v>
       </c>
-      <c r="B266" s="2" t="s">
+      <c r="B266" s="3" t="s">
         <v>1648</v>
       </c>
-      <c r="C266" s="2" t="s">
+      <c r="C266" s="3" t="s">
         <v>1649</v>
       </c>
       <c r="D266" s="2"/>
@@ -25599,10 +25599,10 @@
       <c r="A267" s="2" t="s">
         <v>1653</v>
       </c>
-      <c r="B267" s="2" t="s">
+      <c r="B267" s="3" t="s">
         <v>1654</v>
       </c>
-      <c r="C267" s="2" t="s">
+      <c r="C267" s="3" t="s">
         <v>1655</v>
       </c>
       <c r="D267" s="2"/>
@@ -25633,10 +25633,10 @@
       <c r="A268" s="2" t="s">
         <v>1659</v>
       </c>
-      <c r="B268" s="2" t="s">
+      <c r="B268" s="3" t="s">
         <v>1660</v>
       </c>
-      <c r="C268" s="2" t="s">
+      <c r="C268" s="3" t="s">
         <v>1661</v>
       </c>
       <c r="D268" s="2"/>
@@ -25667,10 +25667,10 @@
       <c r="A269" s="2" t="s">
         <v>1665</v>
       </c>
-      <c r="B269" s="2" t="s">
+      <c r="B269" s="3" t="s">
         <v>1666</v>
       </c>
-      <c r="C269" s="2" t="s">
+      <c r="C269" s="3" t="s">
         <v>1667</v>
       </c>
       <c r="D269" s="2"/>
@@ -25701,10 +25701,10 @@
       <c r="A270" s="2" t="s">
         <v>1671</v>
       </c>
-      <c r="B270" s="2" t="s">
+      <c r="B270" s="3" t="s">
         <v>1672</v>
       </c>
-      <c r="C270" s="2" t="s">
+      <c r="C270" s="3" t="s">
         <v>1673</v>
       </c>
       <c r="D270" s="2"/>
@@ -25735,10 +25735,10 @@
       <c r="A271" s="2" t="s">
         <v>1677</v>
       </c>
-      <c r="B271" s="2" t="s">
+      <c r="B271" s="3" t="s">
         <v>1678</v>
       </c>
-      <c r="C271" s="2" t="s">
+      <c r="C271" s="3" t="s">
         <v>1679</v>
       </c>
       <c r="D271" s="2"/>
@@ -25769,10 +25769,10 @@
       <c r="A272" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="B272" s="2" t="s">
+      <c r="B272" s="3" t="s">
         <v>1684</v>
       </c>
-      <c r="C272" s="2" t="s">
+      <c r="C272" s="3" t="s">
         <v>1685</v>
       </c>
       <c r="D272" s="2"/>
@@ -25803,10 +25803,10 @@
       <c r="A273" s="2" t="s">
         <v>1689</v>
       </c>
-      <c r="B273" s="2" t="s">
+      <c r="B273" s="3" t="s">
         <v>1690</v>
       </c>
-      <c r="C273" s="2" t="s">
+      <c r="C273" s="3" t="s">
         <v>1691</v>
       </c>
       <c r="D273" s="2"/>
@@ -25837,10 +25837,10 @@
       <c r="A274" s="2" t="s">
         <v>1695</v>
       </c>
-      <c r="B274" s="2" t="s">
+      <c r="B274" s="3" t="s">
         <v>1696</v>
       </c>
-      <c r="C274" s="2" t="s">
+      <c r="C274" s="3" t="s">
         <v>1697</v>
       </c>
       <c r="D274" s="2"/>
@@ -25871,10 +25871,10 @@
       <c r="A275" s="2" t="s">
         <v>1701</v>
       </c>
-      <c r="B275" s="2" t="s">
+      <c r="B275" s="3" t="s">
         <v>1702</v>
       </c>
-      <c r="C275" s="2" t="s">
+      <c r="C275" s="3" t="s">
         <v>1703</v>
       </c>
       <c r="D275" s="2"/>
@@ -25908,7 +25908,7 @@
       <c r="B276" s="2" t="s">
         <v>1708</v>
       </c>
-      <c r="C276" s="2" t="s">
+      <c r="C276" s="3" t="s">
         <v>1709</v>
       </c>
       <c r="D276" s="2"/>
@@ -25939,10 +25939,10 @@
       <c r="A277" s="2" t="s">
         <v>1713</v>
       </c>
-      <c r="B277" s="2" t="s">
+      <c r="B277" s="3" t="s">
         <v>1714</v>
       </c>
-      <c r="C277" s="2" t="s">
+      <c r="C277" s="3" t="s">
         <v>1715</v>
       </c>
       <c r="D277" s="2"/>
@@ -25973,10 +25973,10 @@
       <c r="A278" s="2" t="s">
         <v>1719</v>
       </c>
-      <c r="B278" s="2" t="s">
+      <c r="B278" s="3" t="s">
         <v>1720</v>
       </c>
-      <c r="C278" s="2" t="s">
+      <c r="C278" s="3" t="s">
         <v>1721</v>
       </c>
       <c r="D278" s="2"/>
@@ -26007,10 +26007,10 @@
       <c r="A279" s="2" t="s">
         <v>1725</v>
       </c>
-      <c r="B279" s="2" t="s">
+      <c r="B279" s="3" t="s">
         <v>1726</v>
       </c>
-      <c r="C279" s="2" t="s">
+      <c r="C279" s="3" t="s">
         <v>1727</v>
       </c>
       <c r="D279" s="2"/>
@@ -26041,7 +26041,7 @@
       <c r="A280" s="2" t="s">
         <v>1731</v>
       </c>
-      <c r="B280" s="2" t="s">
+      <c r="B280" s="3" t="s">
         <v>1732</v>
       </c>
       <c r="C280" s="3" t="s">
@@ -26075,10 +26075,10 @@
       <c r="A281" s="2" t="s">
         <v>1737</v>
       </c>
-      <c r="B281" s="2" t="s">
+      <c r="B281" s="3" t="s">
         <v>1738</v>
       </c>
-      <c r="C281" s="2" t="s">
+      <c r="C281" s="3" t="s">
         <v>1739</v>
       </c>
       <c r="D281" s="2"/>
@@ -26109,10 +26109,10 @@
       <c r="A282" s="2" t="s">
         <v>1744</v>
       </c>
-      <c r="B282" s="2" t="s">
+      <c r="B282" s="3" t="s">
         <v>1745</v>
       </c>
-      <c r="C282" s="2" t="s">
+      <c r="C282" s="3" t="s">
         <v>1746</v>
       </c>
       <c r="D282" s="2"/>
@@ -26143,10 +26143,10 @@
       <c r="A283" s="2" t="s">
         <v>1750</v>
       </c>
-      <c r="B283" s="2" t="s">
+      <c r="B283" s="3" t="s">
         <v>1751</v>
       </c>
-      <c r="C283" s="2" t="s">
+      <c r="C283" s="3" t="s">
         <v>1752</v>
       </c>
       <c r="D283" s="2"/>
@@ -26177,10 +26177,10 @@
       <c r="A284" s="2" t="s">
         <v>1756</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="B284" s="3" t="s">
         <v>1757</v>
       </c>
-      <c r="C284" s="2" t="s">
+      <c r="C284" s="3" t="s">
         <v>1758</v>
       </c>
       <c r="D284" s="2"/>
@@ -26211,10 +26211,10 @@
       <c r="A285" s="2" t="s">
         <v>1762</v>
       </c>
-      <c r="B285" s="2" t="s">
+      <c r="B285" s="3" t="s">
         <v>1763</v>
       </c>
-      <c r="C285" s="2" t="s">
+      <c r="C285" s="3" t="s">
         <v>1764</v>
       </c>
       <c r="D285" s="2"/>
@@ -26248,7 +26248,7 @@
       <c r="B286" s="3" t="s">
         <v>1769</v>
       </c>
-      <c r="C286" s="2" t="s">
+      <c r="C286" s="3" t="s">
         <v>1770</v>
       </c>
       <c r="D286" s="2"/>
@@ -26279,10 +26279,10 @@
       <c r="A287" s="2" t="s">
         <v>1774</v>
       </c>
-      <c r="B287" s="2" t="s">
+      <c r="B287" s="3" t="s">
         <v>1775</v>
       </c>
-      <c r="C287" s="2" t="s">
+      <c r="C287" s="3" t="s">
         <v>1776</v>
       </c>
       <c r="D287" s="2"/>
@@ -26313,10 +26313,10 @@
       <c r="A288" s="2" t="s">
         <v>1780</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="B288" s="3" t="s">
         <v>1781</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="C288" s="3" t="s">
         <v>1782</v>
       </c>
       <c r="D288" s="2"/>
@@ -26347,10 +26347,10 @@
       <c r="A289" s="2" t="s">
         <v>1786</v>
       </c>
-      <c r="B289" s="2" t="s">
+      <c r="B289" s="3" t="s">
         <v>1787</v>
       </c>
-      <c r="C289" s="2" t="s">
+      <c r="C289" s="3" t="s">
         <v>1788</v>
       </c>
       <c r="D289" s="2"/>
@@ -26381,10 +26381,10 @@
       <c r="A290" s="2" t="s">
         <v>1792</v>
       </c>
-      <c r="B290" s="2" t="s">
+      <c r="B290" s="3" t="s">
         <v>1793</v>
       </c>
-      <c r="C290" s="2" t="s">
+      <c r="C290" s="3" t="s">
         <v>1794</v>
       </c>
       <c r="D290" s="2"/>
@@ -26415,10 +26415,10 @@
       <c r="A291" s="2" t="s">
         <v>1798</v>
       </c>
-      <c r="B291" s="2" t="s">
+      <c r="B291" s="3" t="s">
         <v>1799</v>
       </c>
-      <c r="C291" s="2" t="s">
+      <c r="C291" s="3" t="s">
         <v>1800</v>
       </c>
       <c r="D291" s="2"/>
@@ -26449,10 +26449,10 @@
       <c r="A292" s="2" t="s">
         <v>1804</v>
       </c>
-      <c r="B292" s="2" t="s">
+      <c r="B292" s="3" t="s">
         <v>1805</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="C292" s="3" t="s">
         <v>1806</v>
       </c>
       <c r="D292" s="2"/>
@@ -26483,10 +26483,10 @@
       <c r="A293" s="2" t="s">
         <v>1810</v>
       </c>
-      <c r="B293" s="2" t="s">
+      <c r="B293" s="3" t="s">
         <v>1811</v>
       </c>
-      <c r="C293" s="2" t="s">
+      <c r="C293" s="3" t="s">
         <v>1812</v>
       </c>
       <c r="D293" s="2"/>
@@ -26517,10 +26517,10 @@
       <c r="A294" s="2" t="s">
         <v>1816</v>
       </c>
-      <c r="B294" s="2" t="s">
+      <c r="B294" s="3" t="s">
         <v>1817</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="C294" s="3" t="s">
         <v>1818</v>
       </c>
       <c r="D294" s="2"/>
@@ -26554,7 +26554,7 @@
       <c r="B295" s="3" t="s">
         <v>1823</v>
       </c>
-      <c r="C295" s="2" t="s">
+      <c r="C295" s="3" t="s">
         <v>1824</v>
       </c>
       <c r="D295" s="2"/>
@@ -26585,10 +26585,10 @@
       <c r="A296" s="2" t="s">
         <v>1828</v>
       </c>
-      <c r="B296" s="2" t="s">
+      <c r="B296" s="3" t="s">
         <v>1829</v>
       </c>
-      <c r="C296" s="2" t="s">
+      <c r="C296" s="3" t="s">
         <v>1830</v>
       </c>
       <c r="D296" s="2"/>
@@ -26619,10 +26619,10 @@
       <c r="A297" s="2" t="s">
         <v>1834</v>
       </c>
-      <c r="B297" s="2" t="s">
+      <c r="B297" s="3" t="s">
         <v>1835</v>
       </c>
-      <c r="C297" s="2" t="s">
+      <c r="C297" s="3" t="s">
         <v>1836</v>
       </c>
       <c r="D297" s="2"/>
@@ -26653,10 +26653,10 @@
       <c r="A298" s="2" t="s">
         <v>1840</v>
       </c>
-      <c r="B298" s="2" t="s">
+      <c r="B298" s="3" t="s">
         <v>1841</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="C298" s="3" t="s">
         <v>1842</v>
       </c>
       <c r="D298" s="2"/>
@@ -26690,7 +26690,7 @@
       <c r="B299" s="3" t="s">
         <v>1847</v>
       </c>
-      <c r="C299" s="2" t="s">
+      <c r="C299" s="3" t="s">
         <v>1848</v>
       </c>
       <c r="D299" s="2"/>
@@ -26721,10 +26721,10 @@
       <c r="A300" s="2" t="s">
         <v>1852</v>
       </c>
-      <c r="B300" s="2" t="s">
+      <c r="B300" s="3" t="s">
         <v>1853</v>
       </c>
-      <c r="C300" s="2" t="s">
+      <c r="C300" s="3" t="s">
         <v>1854</v>
       </c>
       <c r="D300" s="2"/>
@@ -26755,10 +26755,10 @@
       <c r="A301" s="2" t="s">
         <v>1858</v>
       </c>
-      <c r="B301" s="2" t="s">
+      <c r="B301" s="3" t="s">
         <v>1859</v>
       </c>
-      <c r="C301" s="2" t="s">
+      <c r="C301" s="3" t="s">
         <v>1860</v>
       </c>
       <c r="D301" s="2"/>
@@ -26789,10 +26789,10 @@
       <c r="A302" s="2" t="s">
         <v>1864</v>
       </c>
-      <c r="B302" s="2" t="s">
+      <c r="B302" s="3" t="s">
         <v>1865</v>
       </c>
-      <c r="C302" s="2" t="s">
+      <c r="C302" s="3" t="s">
         <v>1866</v>
       </c>
       <c r="D302" s="2"/>
@@ -26823,10 +26823,10 @@
       <c r="A303" s="2" t="s">
         <v>1870</v>
       </c>
-      <c r="B303" s="2" t="s">
+      <c r="B303" s="3" t="s">
         <v>1871</v>
       </c>
-      <c r="C303" s="2" t="s">
+      <c r="C303" s="3" t="s">
         <v>1872</v>
       </c>
       <c r="D303" s="2"/>
@@ -26860,7 +26860,7 @@
       <c r="B304" s="2" t="s">
         <v>1877</v>
       </c>
-      <c r="C304" s="2" t="s">
+      <c r="C304" s="3" t="s">
         <v>1878</v>
       </c>
       <c r="D304" s="2"/>
@@ -26891,10 +26891,10 @@
       <c r="A305" s="2" t="s">
         <v>1882</v>
       </c>
-      <c r="B305" s="2" t="s">
+      <c r="B305" s="3" t="s">
         <v>1883</v>
       </c>
-      <c r="C305" s="2" t="s">
+      <c r="C305" s="3" t="s">
         <v>1884</v>
       </c>
       <c r="D305" s="2"/>
@@ -26928,7 +26928,7 @@
       <c r="B306" s="3" t="s">
         <v>1889</v>
       </c>
-      <c r="C306" s="2" t="s">
+      <c r="C306" s="3" t="s">
         <v>1890</v>
       </c>
       <c r="D306" s="2"/>
@@ -26959,10 +26959,10 @@
       <c r="A307" s="2" t="s">
         <v>1894</v>
       </c>
-      <c r="B307" s="2" t="s">
+      <c r="B307" s="3" t="s">
         <v>1895</v>
       </c>
-      <c r="C307" s="2" t="s">
+      <c r="C307" s="3" t="s">
         <v>1896</v>
       </c>
       <c r="D307" s="2"/>
@@ -26993,10 +26993,10 @@
       <c r="A308" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="B308" s="2" t="s">
+      <c r="B308" s="3" t="s">
         <v>1901</v>
       </c>
-      <c r="C308" s="2" t="s">
+      <c r="C308" s="3" t="s">
         <v>1902</v>
       </c>
       <c r="D308" s="2"/>
@@ -27027,10 +27027,10 @@
       <c r="A309" s="2" t="s">
         <v>1906</v>
       </c>
-      <c r="B309" s="2" t="s">
+      <c r="B309" s="3" t="s">
         <v>1907</v>
       </c>
-      <c r="C309" s="2" t="s">
+      <c r="C309" s="3" t="s">
         <v>1908</v>
       </c>
       <c r="D309" s="2"/>
@@ -27061,10 +27061,10 @@
       <c r="A310" s="2" t="s">
         <v>1912</v>
       </c>
-      <c r="B310" s="2" t="s">
+      <c r="B310" s="3" t="s">
         <v>1913</v>
       </c>
-      <c r="C310" s="2" t="s">
+      <c r="C310" s="3" t="s">
         <v>1914</v>
       </c>
       <c r="D310" s="2"/>
@@ -27095,10 +27095,10 @@
       <c r="A311" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="B311" s="2" t="s">
+      <c r="B311" s="3" t="s">
         <v>1919</v>
       </c>
-      <c r="C311" s="2" t="s">
+      <c r="C311" s="3" t="s">
         <v>1920</v>
       </c>
       <c r="D311" s="2"/>
@@ -27129,10 +27129,10 @@
       <c r="A312" s="2" t="s">
         <v>1924</v>
       </c>
-      <c r="B312" s="2" t="s">
+      <c r="B312" s="3" t="s">
         <v>1925</v>
       </c>
-      <c r="C312" s="2" t="s">
+      <c r="C312" s="3" t="s">
         <v>1926</v>
       </c>
       <c r="D312" s="2"/>
@@ -27163,10 +27163,10 @@
       <c r="A313" s="2" t="s">
         <v>1930</v>
       </c>
-      <c r="B313" s="2" t="s">
+      <c r="B313" s="3" t="s">
         <v>1931</v>
       </c>
-      <c r="C313" s="2" t="s">
+      <c r="C313" s="3" t="s">
         <v>1932</v>
       </c>
       <c r="D313" s="2"/>
@@ -27197,7 +27197,7 @@
       <c r="A314" s="2" t="s">
         <v>1936</v>
       </c>
-      <c r="B314" s="2" t="s">
+      <c r="B314" s="3" t="s">
         <v>1937</v>
       </c>
       <c r="C314" s="2"/>
@@ -27261,7 +27261,7 @@
       <c r="A316" s="2" t="s">
         <v>1946</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="B316" s="3" t="s">
         <v>1947</v>
       </c>
       <c r="C316" s="2"/>
@@ -27293,7 +27293,7 @@
       <c r="A317" s="2" t="s">
         <v>1951</v>
       </c>
-      <c r="B317" s="2" t="s">
+      <c r="B317" s="3" t="s">
         <v>1952</v>
       </c>
       <c r="C317" s="2"/>
@@ -27325,7 +27325,7 @@
       <c r="A318" s="2" t="s">
         <v>1956</v>
       </c>
-      <c r="B318" s="2" t="s">
+      <c r="B318" s="3" t="s">
         <v>1957</v>
       </c>
       <c r="C318" s="2"/>
@@ -27357,7 +27357,7 @@
       <c r="A319" s="2" t="s">
         <v>1961</v>
       </c>
-      <c r="B319" s="2" t="s">
+      <c r="B319" s="3" t="s">
         <v>1962</v>
       </c>
       <c r="C319" s="2"/>
@@ -27389,7 +27389,7 @@
       <c r="A320" s="2" t="s">
         <v>1966</v>
       </c>
-      <c r="B320" s="2" t="s">
+      <c r="B320" s="3" t="s">
         <v>1967</v>
       </c>
       <c r="C320" s="2"/>
@@ -27421,7 +27421,7 @@
       <c r="A321" s="2" t="s">
         <v>1971</v>
       </c>
-      <c r="B321" s="2" t="s">
+      <c r="B321" s="3" t="s">
         <v>1972</v>
       </c>
       <c r="C321" s="2"/>
@@ -27453,7 +27453,7 @@
       <c r="A322" s="2" t="s">
         <v>1976</v>
       </c>
-      <c r="B322" s="2" t="s">
+      <c r="B322" s="3" t="s">
         <v>1977</v>
       </c>
       <c r="C322" s="2"/>
@@ -27517,7 +27517,7 @@
       <c r="A324" s="2" t="s">
         <v>1986</v>
       </c>
-      <c r="B324" s="2" t="s">
+      <c r="B324" s="3" t="s">
         <v>1987</v>
       </c>
       <c r="C324" s="2"/>
@@ -27549,7 +27549,7 @@
       <c r="A325" s="2" t="s">
         <v>1991</v>
       </c>
-      <c r="B325" s="2" t="s">
+      <c r="B325" s="3" t="s">
         <v>1992</v>
       </c>
       <c r="C325" s="2"/>
@@ -27581,7 +27581,7 @@
       <c r="A326" s="2" t="s">
         <v>1996</v>
       </c>
-      <c r="B326" s="2" t="s">
+      <c r="B326" s="3" t="s">
         <v>1997</v>
       </c>
       <c r="C326" s="2"/>
@@ -27613,7 +27613,7 @@
       <c r="A327" s="2" t="s">
         <v>2001</v>
       </c>
-      <c r="B327" s="2" t="s">
+      <c r="B327" s="3" t="s">
         <v>2002</v>
       </c>
       <c r="C327" s="2"/>
@@ -27645,7 +27645,7 @@
       <c r="A328" s="2" t="s">
         <v>2007</v>
       </c>
-      <c r="B328" s="2" t="s">
+      <c r="B328" s="3" t="s">
         <v>2008</v>
       </c>
       <c r="C328" s="2"/>
@@ -27709,7 +27709,7 @@
       <c r="A330" s="2" t="s">
         <v>2017</v>
       </c>
-      <c r="B330" s="2" t="s">
+      <c r="B330" s="3" t="s">
         <v>2018</v>
       </c>
       <c r="C330" s="2"/>
@@ -27741,7 +27741,7 @@
       <c r="A331" s="2" t="s">
         <v>2022</v>
       </c>
-      <c r="B331" s="2" t="s">
+      <c r="B331" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="C331" s="2"/>
@@ -27773,7 +27773,7 @@
       <c r="A332" s="2" t="s">
         <v>2027</v>
       </c>
-      <c r="B332" s="2" t="s">
+      <c r="B332" s="3" t="s">
         <v>2028</v>
       </c>
       <c r="C332" s="2"/>
@@ -27805,7 +27805,7 @@
       <c r="A333" s="2" t="s">
         <v>2032</v>
       </c>
-      <c r="B333" s="2" t="s">
+      <c r="B333" s="3" t="s">
         <v>2033</v>
       </c>
       <c r="C333" s="2"/>
@@ -27837,7 +27837,7 @@
       <c r="A334" s="2" t="s">
         <v>2037</v>
       </c>
-      <c r="B334" s="2" t="s">
+      <c r="B334" s="3" t="s">
         <v>2038</v>
       </c>
       <c r="C334" s="2"/>
@@ -27869,7 +27869,7 @@
       <c r="A335" s="2" t="s">
         <v>2042</v>
       </c>
-      <c r="B335" s="2" t="s">
+      <c r="B335" s="3" t="s">
         <v>2043</v>
       </c>
       <c r="C335" s="2"/>
@@ -27901,7 +27901,7 @@
       <c r="A336" s="2" t="s">
         <v>2047</v>
       </c>
-      <c r="B336" s="2" t="s">
+      <c r="B336" s="3" t="s">
         <v>2048</v>
       </c>
       <c r="C336" s="2"/>
@@ -27933,7 +27933,7 @@
       <c r="A337" s="2" t="s">
         <v>2052</v>
       </c>
-      <c r="B337" s="2" t="s">
+      <c r="B337" s="3" t="s">
         <v>2053</v>
       </c>
       <c r="C337" s="2"/>
@@ -27965,7 +27965,7 @@
       <c r="A338" s="2" t="s">
         <v>2057</v>
       </c>
-      <c r="B338" s="2" t="s">
+      <c r="B338" s="3" t="s">
         <v>2058</v>
       </c>
       <c r="C338" s="2"/>
@@ -27997,7 +27997,7 @@
       <c r="A339" s="2" t="s">
         <v>2062</v>
       </c>
-      <c r="B339" s="2" t="s">
+      <c r="B339" s="3" t="s">
         <v>2063</v>
       </c>
       <c r="C339" s="2"/>
@@ -28029,7 +28029,7 @@
       <c r="A340" s="2" t="s">
         <v>2067</v>
       </c>
-      <c r="B340" s="2" t="s">
+      <c r="B340" s="3" t="s">
         <v>2068</v>
       </c>
       <c r="C340" s="2"/>
@@ -28061,7 +28061,7 @@
       <c r="A341" s="2" t="s">
         <v>2072</v>
       </c>
-      <c r="B341" s="2" t="s">
+      <c r="B341" s="3" t="s">
         <v>2073</v>
       </c>
       <c r="C341" s="2"/>
@@ -28093,7 +28093,7 @@
       <c r="A342" s="2" t="s">
         <v>2077</v>
       </c>
-      <c r="B342" s="2" t="s">
+      <c r="B342" s="3" t="s">
         <v>2078</v>
       </c>
       <c r="C342" s="2"/>
@@ -28125,7 +28125,7 @@
       <c r="A343" s="2" t="s">
         <v>2082</v>
       </c>
-      <c r="B343" s="2" t="s">
+      <c r="B343" s="3" t="s">
         <v>2083</v>
       </c>
       <c r="C343" s="2"/>
@@ -28157,7 +28157,7 @@
       <c r="A344" s="2" t="s">
         <v>2087</v>
       </c>
-      <c r="B344" s="2" t="s">
+      <c r="B344" s="3" t="s">
         <v>2088</v>
       </c>
       <c r="C344" s="2"/>
@@ -28189,7 +28189,7 @@
       <c r="A345" s="2" t="s">
         <v>2092</v>
       </c>
-      <c r="B345" s="2" t="s">
+      <c r="B345" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="C345" s="2"/>
@@ -28221,7 +28221,7 @@
       <c r="A346" s="2" t="s">
         <v>2097</v>
       </c>
-      <c r="B346" s="2" t="s">
+      <c r="B346" s="3" t="s">
         <v>2098</v>
       </c>
       <c r="C346" s="2"/>
@@ -28253,7 +28253,7 @@
       <c r="A347" s="2" t="s">
         <v>2102</v>
       </c>
-      <c r="B347" s="2" t="s">
+      <c r="B347" s="3" t="s">
         <v>2103</v>
       </c>
       <c r="C347" s="2"/>
@@ -28285,7 +28285,7 @@
       <c r="A348" s="2" t="s">
         <v>2107</v>
       </c>
-      <c r="B348" s="2" t="s">
+      <c r="B348" s="3" t="s">
         <v>2108</v>
       </c>
       <c r="C348" s="2"/>
@@ -28317,7 +28317,7 @@
       <c r="A349" s="2" t="s">
         <v>2112</v>
       </c>
-      <c r="B349" s="2" t="s">
+      <c r="B349" s="3" t="s">
         <v>2113</v>
       </c>
       <c r="C349" s="2"/>
@@ -28349,7 +28349,7 @@
       <c r="A350" s="2" t="s">
         <v>2117</v>
       </c>
-      <c r="B350" s="2" t="s">
+      <c r="B350" s="3" t="s">
         <v>2118</v>
       </c>
       <c r="C350" s="2"/>
@@ -28381,7 +28381,7 @@
       <c r="A351" s="2" t="s">
         <v>2122</v>
       </c>
-      <c r="B351" s="2" t="s">
+      <c r="B351" s="3" t="s">
         <v>2123</v>
       </c>
       <c r="C351" s="2"/>
@@ -28413,7 +28413,7 @@
       <c r="A352" s="2" t="s">
         <v>2127</v>
       </c>
-      <c r="B352" s="2" t="s">
+      <c r="B352" s="3" t="s">
         <v>2128</v>
       </c>
       <c r="C352" s="2"/>
@@ -28445,7 +28445,7 @@
       <c r="A353" s="2" t="s">
         <v>2132</v>
       </c>
-      <c r="B353" s="2" t="s">
+      <c r="B353" s="3" t="s">
         <v>2133</v>
       </c>
       <c r="C353" s="2"/>
@@ -28477,7 +28477,7 @@
       <c r="A354" s="2" t="s">
         <v>2137</v>
       </c>
-      <c r="B354" s="2" t="s">
+      <c r="B354" s="3" t="s">
         <v>2138</v>
       </c>
       <c r="C354" s="2"/>
@@ -28509,7 +28509,7 @@
       <c r="A355" s="2" t="s">
         <v>2142</v>
       </c>
-      <c r="B355" s="2" t="s">
+      <c r="B355" s="3" t="s">
         <v>2143</v>
       </c>
       <c r="C355" s="2"/>
@@ -28541,7 +28541,7 @@
       <c r="A356" s="2" t="s">
         <v>2147</v>
       </c>
-      <c r="B356" s="2" t="s">
+      <c r="B356" s="3" t="s">
         <v>2148</v>
       </c>
       <c r="C356" s="2"/>
@@ -28573,7 +28573,7 @@
       <c r="A357" s="2" t="s">
         <v>2152</v>
       </c>
-      <c r="B357" s="2" t="s">
+      <c r="B357" s="3" t="s">
         <v>2153</v>
       </c>
       <c r="C357" s="2"/>
@@ -28605,7 +28605,7 @@
       <c r="A358" s="2" t="s">
         <v>2157</v>
       </c>
-      <c r="B358" s="2" t="s">
+      <c r="B358" s="3" t="s">
         <v>2158</v>
       </c>
       <c r="C358" s="2"/>
@@ -28637,7 +28637,7 @@
       <c r="A359" s="2" t="s">
         <v>2162</v>
       </c>
-      <c r="B359" s="2" t="s">
+      <c r="B359" s="3" t="s">
         <v>2163</v>
       </c>
       <c r="C359" s="2"/>
@@ -28669,7 +28669,7 @@
       <c r="A360" s="2" t="s">
         <v>2167</v>
       </c>
-      <c r="B360" s="2" t="s">
+      <c r="B360" s="3" t="s">
         <v>2168</v>
       </c>
       <c r="C360" s="2"/>
@@ -28701,7 +28701,7 @@
       <c r="A361" s="2" t="s">
         <v>2172</v>
       </c>
-      <c r="B361" s="2" t="s">
+      <c r="B361" s="3" t="s">
         <v>2173</v>
       </c>
       <c r="C361" s="2"/>
@@ -28733,7 +28733,7 @@
       <c r="A362" s="2" t="s">
         <v>2177</v>
       </c>
-      <c r="B362" s="2" t="s">
+      <c r="B362" s="3" t="s">
         <v>2178</v>
       </c>
       <c r="C362" s="2"/>
@@ -28765,7 +28765,7 @@
       <c r="A363" s="2" t="s">
         <v>2182</v>
       </c>
-      <c r="B363" s="2" t="s">
+      <c r="B363" s="3" t="s">
         <v>2183</v>
       </c>
       <c r="C363" s="2"/>
@@ -28797,7 +28797,7 @@
       <c r="A364" s="2" t="s">
         <v>2187</v>
       </c>
-      <c r="B364" s="2" t="s">
+      <c r="B364" s="3" t="s">
         <v>2188</v>
       </c>
       <c r="C364" s="2"/>
@@ -28829,7 +28829,7 @@
       <c r="A365" s="2" t="s">
         <v>2192</v>
       </c>
-      <c r="B365" s="2" t="s">
+      <c r="B365" s="3" t="s">
         <v>2193</v>
       </c>
       <c r="C365" s="2"/>
@@ -28861,7 +28861,7 @@
       <c r="A366" s="2" t="s">
         <v>2197</v>
       </c>
-      <c r="B366" s="2" t="s">
+      <c r="B366" s="3" t="s">
         <v>2198</v>
       </c>
       <c r="C366" s="2"/>
@@ -28893,7 +28893,7 @@
       <c r="A367" s="2" t="s">
         <v>2202</v>
       </c>
-      <c r="B367" s="2" t="s">
+      <c r="B367" s="3" t="s">
         <v>2203</v>
       </c>
       <c r="C367" s="2"/>
@@ -28925,7 +28925,7 @@
       <c r="A368" s="2" t="s">
         <v>2207</v>
       </c>
-      <c r="B368" s="2" t="s">
+      <c r="B368" s="3" t="s">
         <v>2208</v>
       </c>
       <c r="C368" s="2"/>
@@ -28957,7 +28957,7 @@
       <c r="A369" s="2" t="s">
         <v>2212</v>
       </c>
-      <c r="B369" s="2" t="s">
+      <c r="B369" s="3" t="s">
         <v>2213</v>
       </c>
       <c r="C369" s="2"/>
@@ -28989,7 +28989,7 @@
       <c r="A370" s="2" t="s">
         <v>2217</v>
       </c>
-      <c r="B370" s="2" t="s">
+      <c r="B370" s="3" t="s">
         <v>2218</v>
       </c>
       <c r="C370" s="2"/>
@@ -29021,7 +29021,7 @@
       <c r="A371" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="B371" s="2" t="s">
+      <c r="B371" s="3" t="s">
         <v>2223</v>
       </c>
       <c r="C371" s="2"/>
@@ -29053,7 +29053,7 @@
       <c r="A372" s="2" t="s">
         <v>2227</v>
       </c>
-      <c r="B372" s="2" t="s">
+      <c r="B372" s="3" t="s">
         <v>2228</v>
       </c>
       <c r="C372" s="2"/>
@@ -29085,7 +29085,7 @@
       <c r="A373" s="2" t="s">
         <v>2232</v>
       </c>
-      <c r="B373" s="2" t="s">
+      <c r="B373" s="3" t="s">
         <v>2233</v>
       </c>
       <c r="C373" s="2"/>
@@ -29117,7 +29117,7 @@
       <c r="A374" s="2" t="s">
         <v>2237</v>
       </c>
-      <c r="B374" s="2" t="s">
+      <c r="B374" s="3" t="s">
         <v>2238</v>
       </c>
       <c r="C374" s="2"/>
@@ -29149,7 +29149,7 @@
       <c r="A375" s="2" t="s">
         <v>2242</v>
       </c>
-      <c r="B375" s="2" t="s">
+      <c r="B375" s="3" t="s">
         <v>2243</v>
       </c>
       <c r="C375" s="2"/>
@@ -29181,7 +29181,7 @@
       <c r="A376" s="2" t="s">
         <v>2247</v>
       </c>
-      <c r="B376" s="2" t="s">
+      <c r="B376" s="3" t="s">
         <v>2248</v>
       </c>
       <c r="C376" s="2"/>
@@ -29213,7 +29213,7 @@
       <c r="A377" s="2" t="s">
         <v>2252</v>
       </c>
-      <c r="B377" s="2" t="s">
+      <c r="B377" s="3" t="s">
         <v>2253</v>
       </c>
       <c r="C377" s="2"/>
@@ -29245,7 +29245,7 @@
       <c r="A378" s="2" t="s">
         <v>2257</v>
       </c>
-      <c r="B378" s="2" t="s">
+      <c r="B378" s="3" t="s">
         <v>2258</v>
       </c>
       <c r="C378" s="2"/>
@@ -29277,7 +29277,7 @@
       <c r="A379" s="2" t="s">
         <v>2262</v>
       </c>
-      <c r="B379" s="2" t="s">
+      <c r="B379" s="3" t="s">
         <v>2263</v>
       </c>
       <c r="C379" s="2"/>
@@ -29309,7 +29309,7 @@
       <c r="A380" s="2" t="s">
         <v>2267</v>
       </c>
-      <c r="B380" s="2" t="s">
+      <c r="B380" s="3" t="s">
         <v>2268</v>
       </c>
       <c r="C380" s="2"/>
@@ -29341,7 +29341,7 @@
       <c r="A381" s="2" t="s">
         <v>2272</v>
       </c>
-      <c r="B381" s="2" t="s">
+      <c r="B381" s="3" t="s">
         <v>2273</v>
       </c>
       <c r="C381" s="2"/>
@@ -29373,7 +29373,7 @@
       <c r="A382" s="2" t="s">
         <v>2277</v>
       </c>
-      <c r="B382" s="2" t="s">
+      <c r="B382" s="3" t="s">
         <v>2278</v>
       </c>
       <c r="C382" s="2"/>
@@ -29405,7 +29405,7 @@
       <c r="A383" s="2" t="s">
         <v>2282</v>
       </c>
-      <c r="B383" s="2" t="s">
+      <c r="B383" s="3" t="s">
         <v>2283</v>
       </c>
       <c r="C383" s="2"/>
@@ -29437,7 +29437,7 @@
       <c r="A384" s="2" t="s">
         <v>2287</v>
       </c>
-      <c r="B384" s="2" t="s">
+      <c r="B384" s="3" t="s">
         <v>2288</v>
       </c>
       <c r="C384" s="2"/>
@@ -29469,7 +29469,7 @@
       <c r="A385" s="2" t="s">
         <v>2292</v>
       </c>
-      <c r="B385" s="2" t="s">
+      <c r="B385" s="3" t="s">
         <v>2293</v>
       </c>
       <c r="C385" s="2"/>
@@ -29501,7 +29501,7 @@
       <c r="A386" s="2" t="s">
         <v>2297</v>
       </c>
-      <c r="B386" s="2" t="s">
+      <c r="B386" s="3" t="s">
         <v>2298</v>
       </c>
       <c r="C386" s="2"/>
@@ -29565,7 +29565,7 @@
       <c r="A388" s="2" t="s">
         <v>2307</v>
       </c>
-      <c r="B388" s="2" t="s">
+      <c r="B388" s="3" t="s">
         <v>2308</v>
       </c>
       <c r="C388" s="2"/>
@@ -29597,7 +29597,7 @@
       <c r="A389" s="2" t="s">
         <v>2312</v>
       </c>
-      <c r="B389" s="2" t="s">
+      <c r="B389" s="3" t="s">
         <v>2313</v>
       </c>
       <c r="C389" s="2"/>
@@ -29629,7 +29629,7 @@
       <c r="A390" s="2" t="s">
         <v>2317</v>
       </c>
-      <c r="B390" s="2" t="s">
+      <c r="B390" s="3" t="s">
         <v>2318</v>
       </c>
       <c r="C390" s="2"/>
@@ -29661,7 +29661,7 @@
       <c r="A391" s="2" t="s">
         <v>2322</v>
       </c>
-      <c r="B391" s="2" t="s">
+      <c r="B391" s="3" t="s">
         <v>2323</v>
       </c>
       <c r="C391" s="2"/>
@@ -29693,7 +29693,7 @@
       <c r="A392" s="2" t="s">
         <v>2327</v>
       </c>
-      <c r="B392" s="2" t="s">
+      <c r="B392" s="3" t="s">
         <v>2328</v>
       </c>
       <c r="C392" s="2"/>
@@ -29725,7 +29725,7 @@
       <c r="A393" s="2" t="s">
         <v>2332</v>
       </c>
-      <c r="B393" s="2" t="s">
+      <c r="B393" s="3" t="s">
         <v>2333</v>
       </c>
       <c r="C393" s="2"/>
@@ -29757,7 +29757,7 @@
       <c r="A394" s="2" t="s">
         <v>2337</v>
       </c>
-      <c r="B394" s="2" t="s">
+      <c r="B394" s="3" t="s">
         <v>2338</v>
       </c>
       <c r="C394" s="2"/>
@@ -29789,7 +29789,7 @@
       <c r="A395" s="2" t="s">
         <v>2342</v>
       </c>
-      <c r="B395" s="2" t="s">
+      <c r="B395" s="3" t="s">
         <v>2343</v>
       </c>
       <c r="C395" s="2"/>
@@ -29821,7 +29821,7 @@
       <c r="A396" s="2" t="s">
         <v>2347</v>
       </c>
-      <c r="B396" s="2" t="s">
+      <c r="B396" s="3" t="s">
         <v>2348</v>
       </c>
       <c r="C396" s="2"/>
@@ -29853,7 +29853,7 @@
       <c r="A397" s="2" t="s">
         <v>2352</v>
       </c>
-      <c r="B397" s="2" t="s">
+      <c r="B397" s="3" t="s">
         <v>2353</v>
       </c>
       <c r="C397" s="2"/>
@@ -29885,7 +29885,7 @@
       <c r="A398" s="2" t="s">
         <v>2357</v>
       </c>
-      <c r="B398" s="2" t="s">
+      <c r="B398" s="3" t="s">
         <v>2358</v>
       </c>
       <c r="C398" s="2"/>
@@ -29917,7 +29917,7 @@
       <c r="A399" s="2" t="s">
         <v>2362</v>
       </c>
-      <c r="B399" s="2" t="s">
+      <c r="B399" s="3" t="s">
         <v>2363</v>
       </c>
       <c r="C399" s="2"/>
@@ -29949,7 +29949,7 @@
       <c r="A400" s="2" t="s">
         <v>2367</v>
       </c>
-      <c r="B400" s="2" t="s">
+      <c r="B400" s="3" t="s">
         <v>2368</v>
       </c>
       <c r="C400" s="2"/>
@@ -29981,7 +29981,7 @@
       <c r="A401" s="2" t="s">
         <v>2372</v>
       </c>
-      <c r="B401" s="2" t="s">
+      <c r="B401" s="3" t="s">
         <v>2373</v>
       </c>
       <c r="C401" s="2"/>
@@ -30013,7 +30013,7 @@
       <c r="A402" s="2" t="s">
         <v>2377</v>
       </c>
-      <c r="B402" s="2" t="s">
+      <c r="B402" s="3" t="s">
         <v>2378</v>
       </c>
       <c r="C402" s="2"/>
@@ -30045,7 +30045,7 @@
       <c r="A403" s="2" t="s">
         <v>2382</v>
       </c>
-      <c r="B403" s="2" t="s">
+      <c r="B403" s="3" t="s">
         <v>2383</v>
       </c>
       <c r="C403" s="2"/>
@@ -30077,7 +30077,7 @@
       <c r="A404" s="2" t="s">
         <v>2387</v>
       </c>
-      <c r="B404" s="2" t="s">
+      <c r="B404" s="3" t="s">
         <v>2388</v>
       </c>
       <c r="C404" s="2"/>
@@ -30109,7 +30109,7 @@
       <c r="A405" s="2" t="s">
         <v>2392</v>
       </c>
-      <c r="B405" s="2" t="s">
+      <c r="B405" s="3" t="s">
         <v>2393</v>
       </c>
       <c r="C405" s="2"/>
@@ -30141,7 +30141,7 @@
       <c r="A406" s="2" t="s">
         <v>2397</v>
       </c>
-      <c r="B406" s="2" t="s">
+      <c r="B406" s="3" t="s">
         <v>2398</v>
       </c>
       <c r="C406" s="2"/>
@@ -30173,7 +30173,7 @@
       <c r="A407" s="2" t="s">
         <v>2402</v>
       </c>
-      <c r="B407" s="2" t="s">
+      <c r="B407" s="3" t="s">
         <v>2403</v>
       </c>
       <c r="C407" s="2"/>
@@ -30205,7 +30205,7 @@
       <c r="A408" s="2" t="s">
         <v>2407</v>
       </c>
-      <c r="B408" s="2" t="s">
+      <c r="B408" s="3" t="s">
         <v>2408</v>
       </c>
       <c r="C408" s="2"/>
@@ -30237,7 +30237,7 @@
       <c r="A409" s="2" t="s">
         <v>2412</v>
       </c>
-      <c r="B409" s="2" t="s">
+      <c r="B409" s="3" t="s">
         <v>2413</v>
       </c>
       <c r="C409" s="2"/>
@@ -30269,7 +30269,7 @@
       <c r="A410" s="2" t="s">
         <v>2417</v>
       </c>
-      <c r="B410" s="2" t="s">
+      <c r="B410" s="3" t="s">
         <v>2418</v>
       </c>
       <c r="C410" s="2"/>
@@ -30301,7 +30301,7 @@
       <c r="A411" s="2" t="s">
         <v>2422</v>
       </c>
-      <c r="B411" s="2" t="s">
+      <c r="B411" s="3" t="s">
         <v>2423</v>
       </c>
       <c r="C411" s="2"/>
@@ -30365,7 +30365,7 @@
       <c r="A413" s="2" t="s">
         <v>2432</v>
       </c>
-      <c r="B413" s="2" t="s">
+      <c r="B413" s="3" t="s">
         <v>2433</v>
       </c>
       <c r="C413" s="2"/>
@@ -30397,7 +30397,7 @@
       <c r="A414" s="2" t="s">
         <v>2437</v>
       </c>
-      <c r="B414" s="2" t="s">
+      <c r="B414" s="3" t="s">
         <v>2438</v>
       </c>
       <c r="C414" s="2"/>
@@ -30429,7 +30429,7 @@
       <c r="A415" s="2" t="s">
         <v>2442</v>
       </c>
-      <c r="B415" s="2" t="s">
+      <c r="B415" s="3" t="s">
         <v>2438</v>
       </c>
       <c r="C415" s="2"/>
@@ -30461,7 +30461,7 @@
       <c r="A416" s="2" t="s">
         <v>2443</v>
       </c>
-      <c r="B416" s="2" t="s">
+      <c r="B416" s="3" t="s">
         <v>2444</v>
       </c>
       <c r="C416" s="2"/>
@@ -30493,7 +30493,7 @@
       <c r="A417" s="2" t="s">
         <v>2448</v>
       </c>
-      <c r="B417" s="2" t="s">
+      <c r="B417" s="3" t="s">
         <v>2449</v>
       </c>
       <c r="C417" s="2"/>
@@ -30525,7 +30525,7 @@
       <c r="A418" s="2" t="s">
         <v>2453</v>
       </c>
-      <c r="B418" s="2" t="s">
+      <c r="B418" s="3" t="s">
         <v>2454</v>
       </c>
       <c r="C418" s="2"/>
@@ -30557,7 +30557,7 @@
       <c r="A419" s="2" t="s">
         <v>2458</v>
       </c>
-      <c r="B419" s="2" t="s">
+      <c r="B419" s="3" t="s">
         <v>2459</v>
       </c>
       <c r="C419" s="2"/>
@@ -30589,7 +30589,7 @@
       <c r="A420" s="2" t="s">
         <v>2463</v>
       </c>
-      <c r="B420" s="2" t="s">
+      <c r="B420" s="3" t="s">
         <v>2464</v>
       </c>
       <c r="C420" s="2"/>
@@ -30621,7 +30621,7 @@
       <c r="A421" s="2" t="s">
         <v>2468</v>
       </c>
-      <c r="B421" s="2" t="s">
+      <c r="B421" s="3" t="s">
         <v>2469</v>
       </c>
       <c r="C421" s="2"/>
@@ -30653,7 +30653,7 @@
       <c r="A422" s="2" t="s">
         <v>2473</v>
       </c>
-      <c r="B422" s="2" t="s">
+      <c r="B422" s="3" t="s">
         <v>2474</v>
       </c>
       <c r="C422" s="2"/>
@@ -30685,7 +30685,7 @@
       <c r="A423" s="2" t="s">
         <v>2478</v>
       </c>
-      <c r="B423" s="2" t="s">
+      <c r="B423" s="3" t="s">
         <v>2479</v>
       </c>
       <c r="C423" s="2"/>
@@ -30717,7 +30717,7 @@
       <c r="A424" s="2" t="s">
         <v>2483</v>
       </c>
-      <c r="B424" s="2" t="s">
+      <c r="B424" s="3" t="s">
         <v>2484</v>
       </c>
       <c r="C424" s="2"/>
@@ -30749,7 +30749,7 @@
       <c r="A425" s="2" t="s">
         <v>2488</v>
       </c>
-      <c r="B425" s="2" t="s">
+      <c r="B425" s="3" t="s">
         <v>2489</v>
       </c>
       <c r="C425" s="2"/>
@@ -30781,7 +30781,7 @@
       <c r="A426" s="2" t="s">
         <v>2493</v>
       </c>
-      <c r="B426" s="2" t="s">
+      <c r="B426" s="3" t="s">
         <v>2494</v>
       </c>
       <c r="C426" s="2"/>
@@ -30813,7 +30813,7 @@
       <c r="A427" s="2" t="s">
         <v>2498</v>
       </c>
-      <c r="B427" s="2" t="s">
+      <c r="B427" s="3" t="s">
         <v>2499</v>
       </c>
       <c r="C427" s="2"/>
@@ -30845,7 +30845,7 @@
       <c r="A428" s="2" t="s">
         <v>2503</v>
       </c>
-      <c r="B428" s="2" t="s">
+      <c r="B428" s="3" t="s">
         <v>2504</v>
       </c>
       <c r="C428" s="2"/>
@@ -30877,7 +30877,7 @@
       <c r="A429" s="2" t="s">
         <v>2508</v>
       </c>
-      <c r="B429" s="2" t="s">
+      <c r="B429" s="3" t="s">
         <v>2509</v>
       </c>
       <c r="C429" s="2"/>
@@ -30909,7 +30909,7 @@
       <c r="A430" s="2" t="s">
         <v>2513</v>
       </c>
-      <c r="B430" s="2" t="s">
+      <c r="B430" s="3" t="s">
         <v>2514</v>
       </c>
       <c r="C430" s="2"/>
@@ -30941,7 +30941,7 @@
       <c r="A431" s="2" t="s">
         <v>2518</v>
       </c>
-      <c r="B431" s="2" t="s">
+      <c r="B431" s="3" t="s">
         <v>2519</v>
       </c>
       <c r="C431" s="2"/>
@@ -30973,7 +30973,7 @@
       <c r="A432" s="2" t="s">
         <v>2523</v>
       </c>
-      <c r="B432" s="2" t="s">
+      <c r="B432" s="3" t="s">
         <v>2524</v>
       </c>
       <c r="C432" s="2"/>
@@ -31005,7 +31005,7 @@
       <c r="A433" s="2" t="s">
         <v>2528</v>
       </c>
-      <c r="B433" s="2" t="s">
+      <c r="B433" s="3" t="s">
         <v>2529</v>
       </c>
       <c r="C433" s="2"/>
@@ -31037,7 +31037,7 @@
       <c r="A434" s="2" t="s">
         <v>2533</v>
       </c>
-      <c r="B434" s="2" t="s">
+      <c r="B434" s="3" t="s">
         <v>2534</v>
       </c>
       <c r="C434" s="2"/>
@@ -31069,7 +31069,7 @@
       <c r="A435" s="2" t="s">
         <v>2538</v>
       </c>
-      <c r="B435" s="2" t="s">
+      <c r="B435" s="3" t="s">
         <v>2539</v>
       </c>
       <c r="C435" s="2"/>
@@ -31101,7 +31101,7 @@
       <c r="A436" s="2" t="s">
         <v>2543</v>
       </c>
-      <c r="B436" s="2" t="s">
+      <c r="B436" s="3" t="s">
         <v>2544</v>
       </c>
       <c r="C436" s="2"/>
@@ -31133,7 +31133,7 @@
       <c r="A437" s="2" t="s">
         <v>2548</v>
       </c>
-      <c r="B437" s="2" t="s">
+      <c r="B437" s="3" t="s">
         <v>2549</v>
       </c>
       <c r="C437" s="2"/>
@@ -31165,7 +31165,7 @@
       <c r="A438" s="2" t="s">
         <v>2553</v>
       </c>
-      <c r="B438" s="2" t="s">
+      <c r="B438" s="3" t="s">
         <v>2554</v>
       </c>
       <c r="C438" s="2"/>
@@ -31197,7 +31197,7 @@
       <c r="A439" s="2" t="s">
         <v>2558</v>
       </c>
-      <c r="B439" s="2" t="s">
+      <c r="B439" s="3" t="s">
         <v>2559</v>
       </c>
       <c r="C439" s="2"/>
@@ -31229,7 +31229,7 @@
       <c r="A440" s="2" t="s">
         <v>2563</v>
       </c>
-      <c r="B440" s="2" t="s">
+      <c r="B440" s="3" t="s">
         <v>2564</v>
       </c>
       <c r="C440" s="2"/>
@@ -31261,7 +31261,7 @@
       <c r="A441" s="2" t="s">
         <v>2568</v>
       </c>
-      <c r="B441" s="2" t="s">
+      <c r="B441" s="3" t="s">
         <v>2569</v>
       </c>
       <c r="C441" s="2"/>
@@ -31293,7 +31293,7 @@
       <c r="A442" s="2" t="s">
         <v>2573</v>
       </c>
-      <c r="B442" s="2" t="s">
+      <c r="B442" s="3" t="s">
         <v>2574</v>
       </c>
       <c r="C442" s="2"/>
@@ -31325,7 +31325,7 @@
       <c r="A443" s="2" t="s">
         <v>2578</v>
       </c>
-      <c r="B443" s="2" t="s">
+      <c r="B443" s="3" t="s">
         <v>2579</v>
       </c>
       <c r="C443" s="2"/>
@@ -31357,7 +31357,7 @@
       <c r="A444" s="2" t="s">
         <v>2583</v>
       </c>
-      <c r="B444" s="2" t="s">
+      <c r="B444" s="3" t="s">
         <v>2584</v>
       </c>
       <c r="C444" s="2"/>
@@ -31389,7 +31389,7 @@
       <c r="A445" s="2" t="s">
         <v>2588</v>
       </c>
-      <c r="B445" s="2" t="s">
+      <c r="B445" s="3" t="s">
         <v>2589</v>
       </c>
       <c r="C445" s="2"/>
@@ -31421,7 +31421,7 @@
       <c r="A446" s="2" t="s">
         <v>2593</v>
       </c>
-      <c r="B446" s="2" t="s">
+      <c r="B446" s="3" t="s">
         <v>2594</v>
       </c>
       <c r="C446" s="2"/>
@@ -31453,7 +31453,7 @@
       <c r="A447" s="2" t="s">
         <v>2598</v>
       </c>
-      <c r="B447" s="2" t="s">
+      <c r="B447" s="3" t="s">
         <v>2599</v>
       </c>
       <c r="C447" s="2"/>
@@ -31485,7 +31485,7 @@
       <c r="A448" s="2" t="s">
         <v>2603</v>
       </c>
-      <c r="B448" s="2" t="s">
+      <c r="B448" s="3" t="s">
         <v>2604</v>
       </c>
       <c r="C448" s="2"/>
@@ -31517,7 +31517,7 @@
       <c r="A449" s="2" t="s">
         <v>2608</v>
       </c>
-      <c r="B449" s="2" t="s">
+      <c r="B449" s="3" t="s">
         <v>2609</v>
       </c>
       <c r="C449" s="2"/>
@@ -31549,7 +31549,7 @@
       <c r="A450" s="2" t="s">
         <v>2613</v>
       </c>
-      <c r="B450" s="2" t="s">
+      <c r="B450" s="3" t="s">
         <v>2614</v>
       </c>
       <c r="C450" s="2"/>
@@ -31581,7 +31581,7 @@
       <c r="A451" s="2" t="s">
         <v>2618</v>
       </c>
-      <c r="B451" s="2" t="s">
+      <c r="B451" s="3" t="s">
         <v>2619</v>
       </c>
       <c r="C451" s="2"/>
@@ -31613,7 +31613,7 @@
       <c r="A452" s="2" t="s">
         <v>2623</v>
       </c>
-      <c r="B452" s="2" t="s">
+      <c r="B452" s="3" t="s">
         <v>2624</v>
       </c>
       <c r="C452" s="2"/>
@@ -31645,7 +31645,7 @@
       <c r="A453" s="2" t="s">
         <v>2628</v>
       </c>
-      <c r="B453" s="2" t="s">
+      <c r="B453" s="3" t="s">
         <v>2629</v>
       </c>
       <c r="C453" s="2"/>
@@ -31677,7 +31677,7 @@
       <c r="A454" s="2" t="s">
         <v>2633</v>
       </c>
-      <c r="B454" s="2" t="s">
+      <c r="B454" s="3" t="s">
         <v>2634</v>
       </c>
       <c r="C454" s="2"/>
@@ -31709,7 +31709,7 @@
       <c r="A455" s="2" t="s">
         <v>2638</v>
       </c>
-      <c r="B455" s="2" t="s">
+      <c r="B455" s="3" t="s">
         <v>2639</v>
       </c>
       <c r="C455" s="2"/>
@@ -31741,7 +31741,7 @@
       <c r="A456" s="2" t="s">
         <v>2643</v>
       </c>
-      <c r="B456" s="2" t="s">
+      <c r="B456" s="3" t="s">
         <v>2644</v>
       </c>
       <c r="C456" s="2"/>
@@ -31773,7 +31773,7 @@
       <c r="A457" s="2" t="s">
         <v>2648</v>
       </c>
-      <c r="B457" s="2" t="s">
+      <c r="B457" s="3" t="s">
         <v>2649</v>
       </c>
       <c r="C457" s="2"/>
@@ -31805,7 +31805,7 @@
       <c r="A458" s="2" t="s">
         <v>2653</v>
       </c>
-      <c r="B458" s="2" t="s">
+      <c r="B458" s="3" t="s">
         <v>2654</v>
       </c>
       <c r="C458" s="2"/>
@@ -31837,7 +31837,7 @@
       <c r="A459" s="2" t="s">
         <v>2658</v>
       </c>
-      <c r="B459" s="2" t="s">
+      <c r="B459" s="3" t="s">
         <v>2659</v>
       </c>
       <c r="C459" s="2"/>
@@ -31869,7 +31869,7 @@
       <c r="A460" s="2" t="s">
         <v>2663</v>
       </c>
-      <c r="B460" s="2" t="s">
+      <c r="B460" s="3" t="s">
         <v>2664</v>
       </c>
       <c r="C460" s="2"/>
@@ -31901,7 +31901,7 @@
       <c r="A461" s="2" t="s">
         <v>2668</v>
       </c>
-      <c r="B461" s="2" t="s">
+      <c r="B461" s="3" t="s">
         <v>2669</v>
       </c>
       <c r="C461" s="2"/>
@@ -31933,7 +31933,7 @@
       <c r="A462" s="2" t="s">
         <v>2673</v>
       </c>
-      <c r="B462" s="2" t="s">
+      <c r="B462" s="3" t="s">
         <v>2674</v>
       </c>
       <c r="C462" s="2"/>
@@ -31965,7 +31965,7 @@
       <c r="A463" s="2" t="s">
         <v>2678</v>
       </c>
-      <c r="B463" s="2" t="s">
+      <c r="B463" s="3" t="s">
         <v>2679</v>
       </c>
       <c r="C463" s="2"/>
@@ -31997,7 +31997,7 @@
       <c r="A464" s="2" t="s">
         <v>2683</v>
       </c>
-      <c r="B464" s="2" t="s">
+      <c r="B464" s="3" t="s">
         <v>2684</v>
       </c>
       <c r="C464" s="2"/>
@@ -32029,7 +32029,7 @@
       <c r="A465" s="2" t="s">
         <v>2688</v>
       </c>
-      <c r="B465" s="2" t="s">
+      <c r="B465" s="3" t="s">
         <v>2689</v>
       </c>
       <c r="C465" s="2"/>
@@ -32061,7 +32061,7 @@
       <c r="A466" s="2" t="s">
         <v>2693</v>
       </c>
-      <c r="B466" s="2" t="s">
+      <c r="B466" s="3" t="s">
         <v>2694</v>
       </c>
       <c r="C466" s="2"/>
@@ -32093,7 +32093,7 @@
       <c r="A467" s="2" t="s">
         <v>2698</v>
       </c>
-      <c r="B467" s="2" t="s">
+      <c r="B467" s="3" t="s">
         <v>2699</v>
       </c>
       <c r="C467" s="2"/>
@@ -32125,7 +32125,7 @@
       <c r="A468" s="2" t="s">
         <v>2703</v>
       </c>
-      <c r="B468" s="2" t="s">
+      <c r="B468" s="3" t="s">
         <v>2704</v>
       </c>
       <c r="C468" s="2"/>
@@ -32157,7 +32157,7 @@
       <c r="A469" s="2" t="s">
         <v>2708</v>
       </c>
-      <c r="B469" s="2" t="s">
+      <c r="B469" s="3" t="s">
         <v>2709</v>
       </c>
       <c r="C469" s="2"/>
@@ -32189,7 +32189,7 @@
       <c r="A470" s="2" t="s">
         <v>2713</v>
       </c>
-      <c r="B470" s="2" t="s">
+      <c r="B470" s="3" t="s">
         <v>2714</v>
       </c>
       <c r="C470" s="2"/>
@@ -32221,7 +32221,7 @@
       <c r="A471" s="2" t="s">
         <v>2718</v>
       </c>
-      <c r="B471" s="2" t="s">
+      <c r="B471" s="3" t="s">
         <v>2719</v>
       </c>
       <c r="C471" s="2"/>
@@ -32253,7 +32253,7 @@
       <c r="A472" s="2" t="s">
         <v>2723</v>
       </c>
-      <c r="B472" s="2" t="s">
+      <c r="B472" s="3" t="s">
         <v>2724</v>
       </c>
       <c r="C472" s="2"/>
@@ -32285,7 +32285,7 @@
       <c r="A473" s="2" t="s">
         <v>2728</v>
       </c>
-      <c r="B473" s="2" t="s">
+      <c r="B473" s="3" t="s">
         <v>2729</v>
       </c>
       <c r="C473" s="2"/>
@@ -32349,7 +32349,7 @@
       <c r="A475" s="2" t="s">
         <v>2738</v>
       </c>
-      <c r="B475" s="2" t="s">
+      <c r="B475" s="3" t="s">
         <v>2739</v>
       </c>
       <c r="C475" s="2"/>
@@ -32381,7 +32381,7 @@
       <c r="A476" s="2" t="s">
         <v>2743</v>
       </c>
-      <c r="B476" s="2" t="s">
+      <c r="B476" s="3" t="s">
         <v>2744</v>
       </c>
       <c r="C476" s="2"/>
@@ -32445,7 +32445,7 @@
       <c r="A478" s="2" t="s">
         <v>2753</v>
       </c>
-      <c r="B478" s="2" t="s">
+      <c r="B478" s="3" t="s">
         <v>2754</v>
       </c>
       <c r="C478" s="2"/>
@@ -32477,7 +32477,7 @@
       <c r="A479" s="2" t="s">
         <v>2758</v>
       </c>
-      <c r="B479" s="2" t="s">
+      <c r="B479" s="3" t="s">
         <v>2759</v>
       </c>
       <c r="C479" s="2"/>
@@ -32509,7 +32509,7 @@
       <c r="A480" s="2" t="s">
         <v>2763</v>
       </c>
-      <c r="B480" s="2" t="s">
+      <c r="B480" s="3" t="s">
         <v>2764</v>
       </c>
       <c r="C480" s="2"/>
@@ -32541,7 +32541,7 @@
       <c r="A481" s="2" t="s">
         <v>2768</v>
       </c>
-      <c r="B481" s="2" t="s">
+      <c r="B481" s="3" t="s">
         <v>2769</v>
       </c>
       <c r="C481" s="2"/>
@@ -32573,7 +32573,7 @@
       <c r="A482" s="2" t="s">
         <v>2773</v>
       </c>
-      <c r="B482" s="2" t="s">
+      <c r="B482" s="3" t="s">
         <v>2774</v>
       </c>
       <c r="C482" s="2"/>
@@ -32605,7 +32605,7 @@
       <c r="A483" s="2" t="s">
         <v>2778</v>
       </c>
-      <c r="B483" s="2" t="s">
+      <c r="B483" s="3" t="s">
         <v>2779</v>
       </c>
       <c r="C483" s="2"/>
@@ -32637,7 +32637,7 @@
       <c r="A484" s="2" t="s">
         <v>2783</v>
       </c>
-      <c r="B484" s="2" t="s">
+      <c r="B484" s="3" t="s">
         <v>2784</v>
       </c>
       <c r="C484" s="2"/>
@@ -32669,7 +32669,7 @@
       <c r="A485" s="2" t="s">
         <v>2788</v>
       </c>
-      <c r="B485" s="2" t="s">
+      <c r="B485" s="3" t="s">
         <v>2789</v>
       </c>
       <c r="C485" s="2"/>
@@ -32701,7 +32701,7 @@
       <c r="A486" s="2" t="s">
         <v>2793</v>
       </c>
-      <c r="B486" s="2" t="s">
+      <c r="B486" s="3" t="s">
         <v>2794</v>
       </c>
       <c r="C486" s="2"/>
@@ -32733,7 +32733,7 @@
       <c r="A487" s="2" t="s">
         <v>2798</v>
       </c>
-      <c r="B487" s="2" t="s">
+      <c r="B487" s="3" t="s">
         <v>2799</v>
       </c>
       <c r="C487" s="2"/>
@@ -32765,7 +32765,7 @@
       <c r="A488" s="2" t="s">
         <v>2803</v>
       </c>
-      <c r="B488" s="2" t="s">
+      <c r="B488" s="3" t="s">
         <v>2804</v>
       </c>
       <c r="C488" s="2"/>
@@ -32797,7 +32797,7 @@
       <c r="A489" s="2" t="s">
         <v>2808</v>
       </c>
-      <c r="B489" s="2" t="s">
+      <c r="B489" s="3" t="s">
         <v>2809</v>
       </c>
       <c r="C489" s="2"/>
@@ -32829,7 +32829,7 @@
       <c r="A490" s="2" t="s">
         <v>2813</v>
       </c>
-      <c r="B490" s="2" t="s">
+      <c r="B490" s="3" t="s">
         <v>2814</v>
       </c>
       <c r="C490" s="2"/>
@@ -32861,7 +32861,7 @@
       <c r="A491" s="2" t="s">
         <v>2818</v>
       </c>
-      <c r="B491" s="2" t="s">
+      <c r="B491" s="3" t="s">
         <v>2819</v>
       </c>
       <c r="C491" s="2"/>
@@ -32893,7 +32893,7 @@
       <c r="A492" s="2" t="s">
         <v>2823</v>
       </c>
-      <c r="B492" s="2" t="s">
+      <c r="B492" s="3" t="s">
         <v>2824</v>
       </c>
       <c r="C492" s="2"/>
@@ -32925,7 +32925,7 @@
       <c r="A493" s="2" t="s">
         <v>2828</v>
       </c>
-      <c r="B493" s="2" t="s">
+      <c r="B493" s="3" t="s">
         <v>2829</v>
       </c>
       <c r="C493" s="2"/>
@@ -32957,7 +32957,7 @@
       <c r="A494" s="2" t="s">
         <v>2833</v>
       </c>
-      <c r="B494" s="2" t="s">
+      <c r="B494" s="3" t="s">
         <v>2834</v>
       </c>
       <c r="C494" s="2"/>
@@ -33021,7 +33021,7 @@
       <c r="A496" s="2" t="s">
         <v>2843</v>
       </c>
-      <c r="B496" s="2" t="s">
+      <c r="B496" s="3" t="s">
         <v>2844</v>
       </c>
       <c r="C496" s="2"/>
@@ -33053,7 +33053,7 @@
       <c r="A497" s="2" t="s">
         <v>2848</v>
       </c>
-      <c r="B497" s="2" t="s">
+      <c r="B497" s="3" t="s">
         <v>2849</v>
       </c>
       <c r="C497" s="2"/>
@@ -33085,7 +33085,7 @@
       <c r="A498" s="2" t="s">
         <v>2853</v>
       </c>
-      <c r="B498" s="2" t="s">
+      <c r="B498" s="3" t="s">
         <v>2854</v>
       </c>
       <c r="C498" s="2"/>
@@ -33117,7 +33117,7 @@
       <c r="A499" s="2" t="s">
         <v>2858</v>
       </c>
-      <c r="B499" s="2" t="s">
+      <c r="B499" s="3" t="s">
         <v>2859</v>
       </c>
       <c r="C499" s="2"/>
@@ -33149,7 +33149,7 @@
       <c r="A500" s="2" t="s">
         <v>2863</v>
       </c>
-      <c r="B500" s="2" t="s">
+      <c r="B500" s="3" t="s">
         <v>2864</v>
       </c>
       <c r="C500" s="2"/>
@@ -33181,7 +33181,7 @@
       <c r="A501" s="2" t="s">
         <v>2868</v>
       </c>
-      <c r="B501" s="2" t="s">
+      <c r="B501" s="3" t="s">
         <v>2869</v>
       </c>
       <c r="C501" s="2"/>
@@ -33213,7 +33213,7 @@
       <c r="A502" s="2" t="s">
         <v>2873</v>
       </c>
-      <c r="B502" s="2" t="s">
+      <c r="B502" s="3" t="s">
         <v>2874</v>
       </c>
       <c r="C502" s="2"/>
@@ -33245,7 +33245,7 @@
       <c r="A503" s="2" t="s">
         <v>2878</v>
       </c>
-      <c r="B503" s="2" t="s">
+      <c r="B503" s="3" t="s">
         <v>2879</v>
       </c>
       <c r="C503" s="2"/>
@@ -33277,7 +33277,7 @@
       <c r="A504" s="2" t="s">
         <v>2883</v>
       </c>
-      <c r="B504" s="2" t="s">
+      <c r="B504" s="3" t="s">
         <v>2884</v>
       </c>
       <c r="C504" s="2"/>
@@ -33309,7 +33309,7 @@
       <c r="A505" s="2" t="s">
         <v>2888</v>
       </c>
-      <c r="B505" s="2" t="s">
+      <c r="B505" s="3" t="s">
         <v>2889</v>
       </c>
       <c r="C505" s="2"/>
@@ -33341,7 +33341,7 @@
       <c r="A506" s="2" t="s">
         <v>2893</v>
       </c>
-      <c r="B506" s="2" t="s">
+      <c r="B506" s="3" t="s">
         <v>2894</v>
       </c>
       <c r="C506" s="2"/>
@@ -33373,7 +33373,7 @@
       <c r="A507" s="2" t="s">
         <v>2898</v>
       </c>
-      <c r="B507" s="2" t="s">
+      <c r="B507" s="3" t="s">
         <v>2899</v>
       </c>
       <c r="C507" s="2"/>
@@ -33405,7 +33405,7 @@
       <c r="A508" s="2" t="s">
         <v>2903</v>
       </c>
-      <c r="B508" s="2" t="s">
+      <c r="B508" s="3" t="s">
         <v>2904</v>
       </c>
       <c r="C508" s="2"/>
@@ -33437,7 +33437,7 @@
       <c r="A509" s="2" t="s">
         <v>2908</v>
       </c>
-      <c r="B509" s="2" t="s">
+      <c r="B509" s="3" t="s">
         <v>2909</v>
       </c>
       <c r="C509" s="2"/>
@@ -33469,7 +33469,7 @@
       <c r="A510" s="2" t="s">
         <v>2913</v>
       </c>
-      <c r="B510" s="2" t="s">
+      <c r="B510" s="3" t="s">
         <v>2914</v>
       </c>
       <c r="C510" s="2"/>
@@ -33501,7 +33501,7 @@
       <c r="A511" s="2" t="s">
         <v>2918</v>
       </c>
-      <c r="B511" s="2" t="s">
+      <c r="B511" s="3" t="s">
         <v>2919</v>
       </c>
       <c r="C511" s="2"/>
@@ -33533,7 +33533,7 @@
       <c r="A512" s="2" t="s">
         <v>2923</v>
       </c>
-      <c r="B512" s="2" t="s">
+      <c r="B512" s="3" t="s">
         <v>2924</v>
       </c>
       <c r="C512" s="2"/>
@@ -33565,7 +33565,7 @@
       <c r="A513" s="2" t="s">
         <v>2928</v>
       </c>
-      <c r="B513" s="2" t="s">
+      <c r="B513" s="3" t="s">
         <v>2929</v>
       </c>
       <c r="C513" s="2"/>
@@ -33597,7 +33597,7 @@
       <c r="A514" s="2" t="s">
         <v>2933</v>
       </c>
-      <c r="B514" s="2" t="s">
+      <c r="B514" s="3" t="s">
         <v>2934</v>
       </c>
       <c r="C514" s="2"/>
@@ -33629,7 +33629,7 @@
       <c r="A515" s="2" t="s">
         <v>2938</v>
       </c>
-      <c r="B515" s="2" t="s">
+      <c r="B515" s="3" t="s">
         <v>2939</v>
       </c>
       <c r="C515" s="2"/>
@@ -33661,7 +33661,7 @@
       <c r="A516" s="2" t="s">
         <v>2943</v>
       </c>
-      <c r="B516" s="2" t="s">
+      <c r="B516" s="3" t="s">
         <v>2944</v>
       </c>
       <c r="C516" s="2"/>
@@ -33693,7 +33693,7 @@
       <c r="A517" s="2" t="s">
         <v>2948</v>
       </c>
-      <c r="B517" s="2" t="s">
+      <c r="B517" s="3" t="s">
         <v>2949</v>
       </c>
       <c r="C517" s="2"/>
@@ -33725,7 +33725,7 @@
       <c r="A518" s="2" t="s">
         <v>2953</v>
       </c>
-      <c r="B518" s="2" t="s">
+      <c r="B518" s="3" t="s">
         <v>2954</v>
       </c>
       <c r="C518" s="2"/>
@@ -33757,7 +33757,7 @@
       <c r="A519" s="2" t="s">
         <v>2958</v>
       </c>
-      <c r="B519" s="2" t="s">
+      <c r="B519" s="3" t="s">
         <v>2959</v>
       </c>
       <c r="C519" s="2"/>
@@ -33789,7 +33789,7 @@
       <c r="A520" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="B520" s="2" t="s">
+      <c r="B520" s="3" t="s">
         <v>2964</v>
       </c>
       <c r="C520" s="2"/>
@@ -33821,7 +33821,7 @@
       <c r="A521" s="2" t="s">
         <v>2968</v>
       </c>
-      <c r="B521" s="2" t="s">
+      <c r="B521" s="3" t="s">
         <v>2969</v>
       </c>
       <c r="C521" s="2"/>
@@ -33853,7 +33853,7 @@
       <c r="A522" s="2" t="s">
         <v>2973</v>
       </c>
-      <c r="B522" s="2" t="s">
+      <c r="B522" s="3" t="s">
         <v>2974</v>
       </c>
       <c r="C522" s="2"/>
@@ -33885,7 +33885,7 @@
       <c r="A523" s="2" t="s">
         <v>2978</v>
       </c>
-      <c r="B523" s="2" t="s">
+      <c r="B523" s="3" t="s">
         <v>2979</v>
       </c>
       <c r="C523" s="2"/>
@@ -33917,7 +33917,7 @@
       <c r="A524" s="2" t="s">
         <v>2983</v>
       </c>
-      <c r="B524" s="2" t="s">
+      <c r="B524" s="3" t="s">
         <v>2984</v>
       </c>
       <c r="C524" s="2"/>
@@ -33949,7 +33949,7 @@
       <c r="A525" s="2" t="s">
         <v>2988</v>
       </c>
-      <c r="B525" s="2" t="s">
+      <c r="B525" s="3" t="s">
         <v>2989</v>
       </c>
       <c r="C525" s="2"/>
@@ -33981,7 +33981,7 @@
       <c r="A526" s="2" t="s">
         <v>2993</v>
       </c>
-      <c r="B526" s="2" t="s">
+      <c r="B526" s="3" t="s">
         <v>2994</v>
       </c>
       <c r="C526" s="2"/>
@@ -34013,7 +34013,7 @@
       <c r="A527" s="2" t="s">
         <v>2998</v>
       </c>
-      <c r="B527" s="2" t="s">
+      <c r="B527" s="3" t="s">
         <v>2999</v>
       </c>
       <c r="C527" s="2"/>
@@ -34045,7 +34045,7 @@
       <c r="A528" s="2" t="s">
         <v>3003</v>
       </c>
-      <c r="B528" s="2" t="s">
+      <c r="B528" s="3" t="s">
         <v>3004</v>
       </c>
       <c r="C528" s="2"/>
@@ -34077,7 +34077,7 @@
       <c r="A529" s="2" t="s">
         <v>3008</v>
       </c>
-      <c r="B529" s="2" t="s">
+      <c r="B529" s="3" t="s">
         <v>3009</v>
       </c>
       <c r="C529" s="2"/>
@@ -34109,7 +34109,7 @@
       <c r="A530" s="2" t="s">
         <v>3013</v>
       </c>
-      <c r="B530" s="2" t="s">
+      <c r="B530" s="3" t="s">
         <v>3014</v>
       </c>
       <c r="C530" s="2"/>
@@ -34141,7 +34141,7 @@
       <c r="A531" s="2" t="s">
         <v>3017</v>
       </c>
-      <c r="B531" s="2" t="s">
+      <c r="B531" s="3" t="s">
         <v>3018</v>
       </c>
       <c r="C531" s="2"/>
@@ -34173,7 +34173,7 @@
       <c r="A532" s="2" t="s">
         <v>3022</v>
       </c>
-      <c r="B532" s="2" t="s">
+      <c r="B532" s="3" t="s">
         <v>3023</v>
       </c>
       <c r="C532" s="2"/>
@@ -34205,7 +34205,7 @@
       <c r="A533" s="2" t="s">
         <v>3027</v>
       </c>
-      <c r="B533" s="2" t="s">
+      <c r="B533" s="3" t="s">
         <v>3028</v>
       </c>
       <c r="C533" s="2"/>
@@ -34237,7 +34237,7 @@
       <c r="A534" s="2" t="s">
         <v>3032</v>
       </c>
-      <c r="B534" s="2" t="s">
+      <c r="B534" s="3" t="s">
         <v>3033</v>
       </c>
       <c r="C534" s="2"/>
@@ -34269,7 +34269,7 @@
       <c r="A535" s="2" t="s">
         <v>3037</v>
       </c>
-      <c r="B535" s="2" t="s">
+      <c r="B535" s="3" t="s">
         <v>3038</v>
       </c>
       <c r="C535" s="2"/>
@@ -34301,7 +34301,7 @@
       <c r="A536" s="2" t="s">
         <v>3042</v>
       </c>
-      <c r="B536" s="2" t="s">
+      <c r="B536" s="3" t="s">
         <v>3043</v>
       </c>
       <c r="C536" s="2"/>
@@ -34333,7 +34333,7 @@
       <c r="A537" s="2" t="s">
         <v>3047</v>
       </c>
-      <c r="B537" s="2" t="s">
+      <c r="B537" s="3" t="s">
         <v>3048</v>
       </c>
       <c r="C537" s="2"/>
@@ -34365,7 +34365,7 @@
       <c r="A538" s="2" t="s">
         <v>3052</v>
       </c>
-      <c r="B538" s="2" t="s">
+      <c r="B538" s="3" t="s">
         <v>3053</v>
       </c>
       <c r="C538" s="2"/>
@@ -34397,7 +34397,7 @@
       <c r="A539" s="2" t="s">
         <v>3057</v>
       </c>
-      <c r="B539" s="2" t="s">
+      <c r="B539" s="3" t="s">
         <v>3058</v>
       </c>
       <c r="C539" s="2"/>
@@ -34429,7 +34429,7 @@
       <c r="A540" s="2" t="s">
         <v>3062</v>
       </c>
-      <c r="B540" s="2" t="s">
+      <c r="B540" s="3" t="s">
         <v>3063</v>
       </c>
       <c r="C540" s="2"/>
@@ -34461,7 +34461,7 @@
       <c r="A541" s="2" t="s">
         <v>3067</v>
       </c>
-      <c r="B541" s="2" t="s">
+      <c r="B541" s="3" t="s">
         <v>3068</v>
       </c>
       <c r="C541" s="2"/>
@@ -34493,7 +34493,7 @@
       <c r="A542" s="2" t="s">
         <v>3072</v>
       </c>
-      <c r="B542" s="2" t="s">
+      <c r="B542" s="3" t="s">
         <v>3073</v>
       </c>
       <c r="C542" s="2"/>
@@ -34525,7 +34525,7 @@
       <c r="A543" s="2" t="s">
         <v>3077</v>
       </c>
-      <c r="B543" s="2" t="s">
+      <c r="B543" s="3" t="s">
         <v>3078</v>
       </c>
       <c r="C543" s="2"/>
@@ -34557,7 +34557,7 @@
       <c r="A544" s="2" t="s">
         <v>3082</v>
       </c>
-      <c r="B544" s="2" t="s">
+      <c r="B544" s="3" t="s">
         <v>3083</v>
       </c>
       <c r="C544" s="2"/>
@@ -34589,7 +34589,7 @@
       <c r="A545" s="2" t="s">
         <v>3087</v>
       </c>
-      <c r="B545" s="2" t="s">
+      <c r="B545" s="3" t="s">
         <v>3088</v>
       </c>
       <c r="C545" s="2"/>
@@ -34621,7 +34621,7 @@
       <c r="A546" s="2" t="s">
         <v>3092</v>
       </c>
-      <c r="B546" s="2" t="s">
+      <c r="B546" s="3" t="s">
         <v>3093</v>
       </c>
       <c r="C546" s="2"/>
@@ -34653,7 +34653,7 @@
       <c r="A547" s="2" t="s">
         <v>3097</v>
       </c>
-      <c r="B547" s="2" t="s">
+      <c r="B547" s="3" t="s">
         <v>3098</v>
       </c>
       <c r="C547" s="2"/>
@@ -34685,7 +34685,7 @@
       <c r="A548" s="2" t="s">
         <v>3102</v>
       </c>
-      <c r="B548" s="2" t="s">
+      <c r="B548" s="3" t="s">
         <v>3103</v>
       </c>
       <c r="C548" s="2"/>
@@ -34717,7 +34717,7 @@
       <c r="A549" s="2" t="s">
         <v>3107</v>
       </c>
-      <c r="B549" s="2" t="s">
+      <c r="B549" s="3" t="s">
         <v>3108</v>
       </c>
       <c r="C549" s="2"/>
@@ -34749,7 +34749,7 @@
       <c r="A550" s="2" t="s">
         <v>3112</v>
       </c>
-      <c r="B550" s="2" t="s">
+      <c r="B550" s="3" t="s">
         <v>3113</v>
       </c>
       <c r="C550" s="2"/>
@@ -34781,7 +34781,7 @@
       <c r="A551" s="2" t="s">
         <v>3117</v>
       </c>
-      <c r="B551" s="2" t="s">
+      <c r="B551" s="3" t="s">
         <v>3118</v>
       </c>
       <c r="C551" s="2"/>
@@ -34813,7 +34813,7 @@
       <c r="A552" s="2" t="s">
         <v>3122</v>
       </c>
-      <c r="B552" s="2" t="s">
+      <c r="B552" s="3" t="s">
         <v>3123</v>
       </c>
       <c r="C552" s="2"/>
@@ -34877,7 +34877,7 @@
       <c r="A554" s="2" t="s">
         <v>3132</v>
       </c>
-      <c r="B554" s="2" t="s">
+      <c r="B554" s="3" t="s">
         <v>3133</v>
       </c>
       <c r="C554" s="2"/>
@@ -34909,7 +34909,7 @@
       <c r="A555" s="2" t="s">
         <v>3137</v>
       </c>
-      <c r="B555" s="2" t="s">
+      <c r="B555" s="3" t="s">
         <v>3138</v>
       </c>
       <c r="C555" s="2"/>
@@ -34941,7 +34941,7 @@
       <c r="A556" s="2" t="s">
         <v>3142</v>
       </c>
-      <c r="B556" s="2" t="s">
+      <c r="B556" s="3" t="s">
         <v>3143</v>
       </c>
       <c r="C556" s="2"/>
@@ -34973,7 +34973,7 @@
       <c r="A557" s="2" t="s">
         <v>3147</v>
       </c>
-      <c r="B557" s="2" t="s">
+      <c r="B557" s="3" t="s">
         <v>874</v>
       </c>
       <c r="C557" s="2"/>
@@ -35005,7 +35005,7 @@
       <c r="A558" s="2" t="s">
         <v>3151</v>
       </c>
-      <c r="B558" s="2" t="s">
+      <c r="B558" s="3" t="s">
         <v>3152</v>
       </c>
       <c r="C558" s="2"/>
@@ -35037,7 +35037,7 @@
       <c r="A559" s="2" t="s">
         <v>3156</v>
       </c>
-      <c r="B559" s="2" t="s">
+      <c r="B559" s="3" t="s">
         <v>3157</v>
       </c>
       <c r="C559" s="2"/>
@@ -35069,7 +35069,7 @@
       <c r="A560" s="2" t="s">
         <v>3161</v>
       </c>
-      <c r="B560" s="2" t="s">
+      <c r="B560" s="3" t="s">
         <v>3162</v>
       </c>
       <c r="C560" s="2"/>
@@ -35101,7 +35101,7 @@
       <c r="A561" s="2" t="s">
         <v>3166</v>
       </c>
-      <c r="B561" s="2" t="s">
+      <c r="B561" s="3" t="s">
         <v>3167</v>
       </c>
       <c r="C561" s="2"/>
@@ -35133,7 +35133,7 @@
       <c r="A562" s="2" t="s">
         <v>3171</v>
       </c>
-      <c r="B562" s="2" t="s">
+      <c r="B562" s="3" t="s">
         <v>3172</v>
       </c>
       <c r="C562" s="2"/>
@@ -35165,7 +35165,7 @@
       <c r="A563" s="2" t="s">
         <v>3176</v>
       </c>
-      <c r="B563" s="2" t="s">
+      <c r="B563" s="3" t="s">
         <v>3177</v>
       </c>
       <c r="C563" s="2"/>
@@ -35197,7 +35197,7 @@
       <c r="A564" s="2" t="s">
         <v>3181</v>
       </c>
-      <c r="B564" s="2" t="s">
+      <c r="B564" s="3" t="s">
         <v>3182</v>
       </c>
       <c r="C564" s="2"/>
@@ -35229,7 +35229,7 @@
       <c r="A565" s="2" t="s">
         <v>3186</v>
       </c>
-      <c r="B565" s="2" t="s">
+      <c r="B565" s="3" t="s">
         <v>3187</v>
       </c>
       <c r="C565" s="2"/>
@@ -35261,7 +35261,7 @@
       <c r="A566" s="2" t="s">
         <v>3191</v>
       </c>
-      <c r="B566" s="2" t="s">
+      <c r="B566" s="3" t="s">
         <v>3192</v>
       </c>
       <c r="C566" s="2"/>
@@ -35293,7 +35293,7 @@
       <c r="A567" s="2" t="s">
         <v>3196</v>
       </c>
-      <c r="B567" s="2" t="s">
+      <c r="B567" s="3" t="s">
         <v>3197</v>
       </c>
       <c r="C567" s="2"/>
@@ -35325,7 +35325,7 @@
       <c r="A568" s="2" t="s">
         <v>3201</v>
       </c>
-      <c r="B568" s="2" t="s">
+      <c r="B568" s="3" t="s">
         <v>3202</v>
       </c>
       <c r="C568" s="2"/>
@@ -35357,7 +35357,7 @@
       <c r="A569" s="2" t="s">
         <v>3206</v>
       </c>
-      <c r="B569" s="2" t="s">
+      <c r="B569" s="3" t="s">
         <v>3207</v>
       </c>
       <c r="C569" s="2"/>
@@ -35389,7 +35389,7 @@
       <c r="A570" s="2" t="s">
         <v>3211</v>
       </c>
-      <c r="B570" s="2" t="s">
+      <c r="B570" s="3" t="s">
         <v>3212</v>
       </c>
       <c r="C570" s="2"/>
@@ -35421,7 +35421,7 @@
       <c r="A571" s="2" t="s">
         <v>3216</v>
       </c>
-      <c r="B571" s="2" t="s">
+      <c r="B571" s="3" t="s">
         <v>3217</v>
       </c>
       <c r="C571" s="2"/>
@@ -35453,7 +35453,7 @@
       <c r="A572" s="2" t="s">
         <v>3221</v>
       </c>
-      <c r="B572" s="2" t="s">
+      <c r="B572" s="3" t="s">
         <v>3222</v>
       </c>
       <c r="C572" s="2"/>
@@ -35485,7 +35485,7 @@
       <c r="A573" s="2" t="s">
         <v>3226</v>
       </c>
-      <c r="B573" s="2" t="s">
+      <c r="B573" s="3" t="s">
         <v>3227</v>
       </c>
       <c r="C573" s="2"/>
@@ -35517,7 +35517,7 @@
       <c r="A574" s="2" t="s">
         <v>3231</v>
       </c>
-      <c r="B574" s="2" t="s">
+      <c r="B574" s="3" t="s">
         <v>3232</v>
       </c>
       <c r="C574" s="2"/>
@@ -35549,7 +35549,7 @@
       <c r="A575" s="2" t="s">
         <v>3236</v>
       </c>
-      <c r="B575" s="2" t="s">
+      <c r="B575" s="3" t="s">
         <v>3237</v>
       </c>
       <c r="C575" s="2"/>
@@ -35581,7 +35581,7 @@
       <c r="A576" s="2" t="s">
         <v>3241</v>
       </c>
-      <c r="B576" s="2" t="s">
+      <c r="B576" s="3" t="s">
         <v>3242</v>
       </c>
       <c r="C576" s="2"/>
@@ -35613,7 +35613,7 @@
       <c r="A577" s="2" t="s">
         <v>3246</v>
       </c>
-      <c r="B577" s="2" t="s">
+      <c r="B577" s="3" t="s">
         <v>3247</v>
       </c>
       <c r="C577" s="2"/>
@@ -35645,7 +35645,7 @@
       <c r="A578" s="2" t="s">
         <v>3251</v>
       </c>
-      <c r="B578" s="2" t="s">
+      <c r="B578" s="3" t="s">
         <v>3252</v>
       </c>
       <c r="C578" s="2"/>
@@ -35677,7 +35677,7 @@
       <c r="A579" s="2" t="s">
         <v>3256</v>
       </c>
-      <c r="B579" s="2" t="s">
+      <c r="B579" s="3" t="s">
         <v>3257</v>
       </c>
       <c r="C579" s="2"/>
@@ -35709,7 +35709,7 @@
       <c r="A580" s="2" t="s">
         <v>3261</v>
       </c>
-      <c r="B580" s="2" t="s">
+      <c r="B580" s="3" t="s">
         <v>3262</v>
       </c>
       <c r="C580" s="2"/>
@@ -35741,7 +35741,7 @@
       <c r="A581" s="2" t="s">
         <v>3266</v>
       </c>
-      <c r="B581" s="2" t="s">
+      <c r="B581" s="3" t="s">
         <v>3267</v>
       </c>
       <c r="C581" s="2"/>
@@ -35773,7 +35773,7 @@
       <c r="A582" s="2" t="s">
         <v>3271</v>
       </c>
-      <c r="B582" s="2" t="s">
+      <c r="B582" s="3" t="s">
         <v>3272</v>
       </c>
       <c r="C582" s="2"/>
@@ -35805,7 +35805,7 @@
       <c r="A583" s="2" t="s">
         <v>3276</v>
       </c>
-      <c r="B583" s="2" t="s">
+      <c r="B583" s="3" t="s">
         <v>3277</v>
       </c>
       <c r="C583" s="2"/>
@@ -35837,7 +35837,7 @@
       <c r="A584" s="2" t="s">
         <v>3281</v>
       </c>
-      <c r="B584" s="2" t="s">
+      <c r="B584" s="3" t="s">
         <v>3282</v>
       </c>
       <c r="C584" s="2"/>
@@ -35869,7 +35869,7 @@
       <c r="A585" s="2" t="s">
         <v>3286</v>
       </c>
-      <c r="B585" s="2" t="s">
+      <c r="B585" s="3" t="s">
         <v>3287</v>
       </c>
       <c r="C585" s="2"/>
@@ -35901,7 +35901,7 @@
       <c r="A586" s="2" t="s">
         <v>3291</v>
       </c>
-      <c r="B586" s="2" t="s">
+      <c r="B586" s="3" t="s">
         <v>3292</v>
       </c>
       <c r="C586" s="2"/>
@@ -35933,7 +35933,7 @@
       <c r="A587" s="2" t="s">
         <v>3296</v>
       </c>
-      <c r="B587" s="2" t="s">
+      <c r="B587" s="3" t="s">
         <v>3297</v>
       </c>
       <c r="C587" s="2"/>
@@ -35965,7 +35965,7 @@
       <c r="A588" s="2" t="s">
         <v>3301</v>
       </c>
-      <c r="B588" s="2" t="s">
+      <c r="B588" s="3" t="s">
         <v>3302</v>
       </c>
       <c r="C588" s="2"/>
@@ -35997,7 +35997,7 @@
       <c r="A589" s="2" t="s">
         <v>3306</v>
       </c>
-      <c r="B589" s="2" t="s">
+      <c r="B589" s="3" t="s">
         <v>3307</v>
       </c>
       <c r="C589" s="2"/>
@@ -36029,7 +36029,7 @@
       <c r="A590" s="2" t="s">
         <v>3311</v>
       </c>
-      <c r="B590" s="2" t="s">
+      <c r="B590" s="3" t="s">
         <v>3312</v>
       </c>
       <c r="C590" s="2"/>
@@ -36061,7 +36061,7 @@
       <c r="A591" s="2" t="s">
         <v>3316</v>
       </c>
-      <c r="B591" s="2" t="s">
+      <c r="B591" s="3" t="s">
         <v>3317</v>
       </c>
       <c r="C591" s="2"/>
@@ -36093,7 +36093,7 @@
       <c r="A592" s="2" t="s">
         <v>3321</v>
       </c>
-      <c r="B592" s="2" t="s">
+      <c r="B592" s="3" t="s">
         <v>3322</v>
       </c>
       <c r="C592" s="2"/>
@@ -36125,7 +36125,7 @@
       <c r="A593" s="2" t="s">
         <v>3326</v>
       </c>
-      <c r="B593" s="2" t="s">
+      <c r="B593" s="3" t="s">
         <v>3327</v>
       </c>
       <c r="C593" s="2"/>
@@ -36157,7 +36157,7 @@
       <c r="A594" s="2" t="s">
         <v>3331</v>
       </c>
-      <c r="B594" s="2" t="s">
+      <c r="B594" s="3" t="s">
         <v>3332</v>
       </c>
       <c r="C594" s="2"/>
@@ -36189,7 +36189,7 @@
       <c r="A595" s="2" t="s">
         <v>3336</v>
       </c>
-      <c r="B595" s="2" t="s">
+      <c r="B595" s="3" t="s">
         <v>3337</v>
       </c>
       <c r="C595" s="2"/>
@@ -36221,7 +36221,7 @@
       <c r="A596" s="2" t="s">
         <v>3341</v>
       </c>
-      <c r="B596" s="2" t="s">
+      <c r="B596" s="3" t="s">
         <v>3342</v>
       </c>
       <c r="C596" s="2"/>
@@ -36253,7 +36253,7 @@
       <c r="A597" s="2" t="s">
         <v>3346</v>
       </c>
-      <c r="B597" s="2" t="s">
+      <c r="B597" s="3" t="s">
         <v>3347</v>
       </c>
       <c r="C597" s="2"/>
@@ -36285,7 +36285,7 @@
       <c r="A598" s="2" t="s">
         <v>3351</v>
       </c>
-      <c r="B598" s="2" t="s">
+      <c r="B598" s="3" t="s">
         <v>3352</v>
       </c>
       <c r="C598" s="2"/>
@@ -36317,7 +36317,7 @@
       <c r="A599" s="2" t="s">
         <v>3356</v>
       </c>
-      <c r="B599" s="2" t="s">
+      <c r="B599" s="3" t="s">
         <v>3357</v>
       </c>
       <c r="C599" s="2"/>
@@ -36349,7 +36349,7 @@
       <c r="A600" s="2" t="s">
         <v>3360</v>
       </c>
-      <c r="B600" s="2" t="s">
+      <c r="B600" s="3" t="s">
         <v>3361</v>
       </c>
       <c r="C600" s="2"/>
@@ -36381,7 +36381,7 @@
       <c r="A601" s="2" t="s">
         <v>3365</v>
       </c>
-      <c r="B601" s="2" t="s">
+      <c r="B601" s="3" t="s">
         <v>3366</v>
       </c>
       <c r="C601" s="2"/>
@@ -36413,7 +36413,7 @@
       <c r="A602" s="2" t="s">
         <v>3370</v>
       </c>
-      <c r="B602" s="2" t="s">
+      <c r="B602" s="3" t="s">
         <v>3371</v>
       </c>
       <c r="C602" s="2"/>
@@ -36445,7 +36445,7 @@
       <c r="A603" s="2" t="s">
         <v>3375</v>
       </c>
-      <c r="B603" s="2" t="s">
+      <c r="B603" s="3" t="s">
         <v>3376</v>
       </c>
       <c r="C603" s="2"/>
@@ -36477,7 +36477,7 @@
       <c r="A604" s="2" t="s">
         <v>3380</v>
       </c>
-      <c r="B604" s="2" t="s">
+      <c r="B604" s="3" t="s">
         <v>3381</v>
       </c>
       <c r="C604" s="2"/>
@@ -36509,7 +36509,7 @@
       <c r="A605" s="2" t="s">
         <v>3384</v>
       </c>
-      <c r="B605" s="2" t="s">
+      <c r="B605" s="3" t="s">
         <v>3385</v>
       </c>
       <c r="C605" s="2"/>
@@ -36541,7 +36541,7 @@
       <c r="A606" s="2" t="s">
         <v>3389</v>
       </c>
-      <c r="B606" s="2" t="s">
+      <c r="B606" s="3" t="s">
         <v>3390</v>
       </c>
       <c r="C606" s="2"/>
@@ -36573,7 +36573,7 @@
       <c r="A607" s="2" t="s">
         <v>3394</v>
       </c>
-      <c r="B607" s="2" t="s">
+      <c r="B607" s="3" t="s">
         <v>3395</v>
       </c>
       <c r="C607" s="2"/>
@@ -36605,7 +36605,7 @@
       <c r="A608" s="2" t="s">
         <v>3399</v>
       </c>
-      <c r="B608" s="2" t="s">
+      <c r="B608" s="3" t="s">
         <v>3400</v>
       </c>
       <c r="C608" s="2"/>
@@ -36637,7 +36637,7 @@
       <c r="A609" s="2" t="s">
         <v>3404</v>
       </c>
-      <c r="B609" s="2" t="s">
+      <c r="B609" s="3" t="s">
         <v>3405</v>
       </c>
       <c r="C609" s="2"/>
@@ -36669,7 +36669,7 @@
       <c r="A610" s="2" t="s">
         <v>3409</v>
       </c>
-      <c r="B610" s="2" t="s">
+      <c r="B610" s="3" t="s">
         <v>3410</v>
       </c>
       <c r="C610" s="2"/>
@@ -36701,7 +36701,7 @@
       <c r="A611" s="2" t="s">
         <v>3414</v>
       </c>
-      <c r="B611" s="2" t="s">
+      <c r="B611" s="3" t="s">
         <v>3415</v>
       </c>
       <c r="C611" s="2"/>
@@ -36733,7 +36733,7 @@
       <c r="A612" s="2" t="s">
         <v>3419</v>
       </c>
-      <c r="B612" s="2" t="s">
+      <c r="B612" s="3" t="s">
         <v>3420</v>
       </c>
       <c r="C612" s="2"/>
@@ -36765,7 +36765,7 @@
       <c r="A613" s="2" t="s">
         <v>3424</v>
       </c>
-      <c r="B613" s="2" t="s">
+      <c r="B613" s="3" t="s">
         <v>3425</v>
       </c>
       <c r="C613" s="2"/>
@@ -36797,7 +36797,7 @@
       <c r="A614" s="2" t="s">
         <v>3429</v>
       </c>
-      <c r="B614" s="2" t="s">
+      <c r="B614" s="3" t="s">
         <v>3430</v>
       </c>
       <c r="C614" s="2"/>
@@ -36829,7 +36829,7 @@
       <c r="A615" s="2" t="s">
         <v>3434</v>
       </c>
-      <c r="B615" s="2" t="s">
+      <c r="B615" s="3" t="s">
         <v>3435</v>
       </c>
       <c r="C615" s="2"/>
@@ -36861,7 +36861,7 @@
       <c r="A616" s="2" t="s">
         <v>3439</v>
       </c>
-      <c r="B616" s="2" t="s">
+      <c r="B616" s="3" t="s">
         <v>3440</v>
       </c>
       <c r="C616" s="2"/>
@@ -36893,7 +36893,7 @@
       <c r="A617" s="2" t="s">
         <v>3444</v>
       </c>
-      <c r="B617" s="2" t="s">
+      <c r="B617" s="3" t="s">
         <v>3445</v>
       </c>
       <c r="C617" s="2"/>
@@ -36925,7 +36925,7 @@
       <c r="A618" s="2" t="s">
         <v>3449</v>
       </c>
-      <c r="B618" s="2" t="s">
+      <c r="B618" s="3" t="s">
         <v>3450</v>
       </c>
       <c r="C618" s="2"/>
@@ -36957,7 +36957,7 @@
       <c r="A619" s="2" t="s">
         <v>3454</v>
       </c>
-      <c r="B619" s="2" t="s">
+      <c r="B619" s="3" t="s">
         <v>3455</v>
       </c>
       <c r="C619" s="2"/>
@@ -36989,7 +36989,7 @@
       <c r="A620" s="2" t="s">
         <v>3459</v>
       </c>
-      <c r="B620" s="2" t="s">
+      <c r="B620" s="3" t="s">
         <v>3460</v>
       </c>
       <c r="C620" s="2"/>
@@ -37021,7 +37021,7 @@
       <c r="A621" s="2" t="s">
         <v>3464</v>
       </c>
-      <c r="B621" s="2" t="s">
+      <c r="B621" s="3" t="s">
         <v>3465</v>
       </c>
       <c r="C621" s="2"/>
@@ -37053,7 +37053,7 @@
       <c r="A622" s="2" t="s">
         <v>3469</v>
       </c>
-      <c r="B622" s="2" t="s">
+      <c r="B622" s="3" t="s">
         <v>3470</v>
       </c>
       <c r="C622" s="2"/>
@@ -37085,7 +37085,7 @@
       <c r="A623" s="2" t="s">
         <v>3474</v>
       </c>
-      <c r="B623" s="2" t="s">
+      <c r="B623" s="3" t="s">
         <v>3475</v>
       </c>
       <c r="C623" s="2"/>
@@ -37117,7 +37117,7 @@
       <c r="A624" s="2" t="s">
         <v>3479</v>
       </c>
-      <c r="B624" s="2" t="s">
+      <c r="B624" s="3" t="s">
         <v>3480</v>
       </c>
       <c r="C624" s="2"/>
@@ -37149,7 +37149,7 @@
       <c r="A625" s="2" t="s">
         <v>3484</v>
       </c>
-      <c r="B625" s="2" t="s">
+      <c r="B625" s="3" t="s">
         <v>3485</v>
       </c>
       <c r="C625" s="2"/>
@@ -37181,7 +37181,7 @@
       <c r="A626" s="2" t="s">
         <v>3489</v>
       </c>
-      <c r="B626" s="2" t="s">
+      <c r="B626" s="3" t="s">
         <v>3490</v>
       </c>
       <c r="C626" s="2"/>
@@ -37213,7 +37213,7 @@
       <c r="A627" s="2" t="s">
         <v>3494</v>
       </c>
-      <c r="B627" s="2" t="s">
+      <c r="B627" s="3" t="s">
         <v>3495</v>
       </c>
       <c r="C627" s="2"/>
@@ -37245,7 +37245,7 @@
       <c r="A628" s="2" t="s">
         <v>3499</v>
       </c>
-      <c r="B628" s="2" t="s">
+      <c r="B628" s="3" t="s">
         <v>3500</v>
       </c>
       <c r="C628" s="2"/>
@@ -37277,7 +37277,7 @@
       <c r="A629" s="2" t="s">
         <v>3504</v>
       </c>
-      <c r="B629" s="2" t="s">
+      <c r="B629" s="3" t="s">
         <v>3505</v>
       </c>
       <c r="C629" s="2"/>
@@ -37309,7 +37309,7 @@
       <c r="A630" s="2" t="s">
         <v>3509</v>
       </c>
-      <c r="B630" s="2" t="s">
+      <c r="B630" s="3" t="s">
         <v>3510</v>
       </c>
       <c r="C630" s="2"/>
@@ -37341,7 +37341,7 @@
       <c r="A631" s="2" t="s">
         <v>3514</v>
       </c>
-      <c r="B631" s="2" t="s">
+      <c r="B631" s="3" t="s">
         <v>3515</v>
       </c>
       <c r="C631" s="2"/>
@@ -37373,7 +37373,7 @@
       <c r="A632" s="2" t="s">
         <v>3519</v>
       </c>
-      <c r="B632" s="2" t="s">
+      <c r="B632" s="3" t="s">
         <v>3520</v>
       </c>
       <c r="C632" s="2"/>
@@ -37405,7 +37405,7 @@
       <c r="A633" s="2" t="s">
         <v>3524</v>
       </c>
-      <c r="B633" s="2" t="s">
+      <c r="B633" s="3" t="s">
         <v>3525</v>
       </c>
       <c r="C633" s="2"/>
@@ -37437,7 +37437,7 @@
       <c r="A634" s="2" t="s">
         <v>3529</v>
       </c>
-      <c r="B634" s="2" t="s">
+      <c r="B634" s="3" t="s">
         <v>3530</v>
       </c>
       <c r="C634" s="2"/>
@@ -37469,7 +37469,7 @@
       <c r="A635" s="2" t="s">
         <v>3534</v>
       </c>
-      <c r="B635" s="2" t="s">
+      <c r="B635" s="3" t="s">
         <v>3535</v>
       </c>
       <c r="C635" s="2"/>
@@ -37501,7 +37501,7 @@
       <c r="A636" s="2" t="s">
         <v>3539</v>
       </c>
-      <c r="B636" s="2" t="s">
+      <c r="B636" s="3" t="s">
         <v>3540</v>
       </c>
       <c r="C636" s="2"/>
@@ -37533,7 +37533,7 @@
       <c r="A637" s="2" t="s">
         <v>3544</v>
       </c>
-      <c r="B637" s="2" t="s">
+      <c r="B637" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="C637" s="2"/>
@@ -37565,7 +37565,7 @@
       <c r="A638" s="2" t="s">
         <v>3549</v>
       </c>
-      <c r="B638" s="2" t="s">
+      <c r="B638" s="3" t="s">
         <v>3550</v>
       </c>
       <c r="C638" s="2"/>
@@ -37597,7 +37597,7 @@
       <c r="A639" s="2" t="s">
         <v>3554</v>
       </c>
-      <c r="B639" s="2" t="s">
+      <c r="B639" s="3" t="s">
         <v>3555</v>
       </c>
       <c r="C639" s="2"/>
@@ -37629,7 +37629,7 @@
       <c r="A640" s="2" t="s">
         <v>3559</v>
       </c>
-      <c r="B640" s="2" t="s">
+      <c r="B640" s="3" t="s">
         <v>3560</v>
       </c>
       <c r="C640" s="2"/>
@@ -37661,7 +37661,7 @@
       <c r="A641" s="2" t="s">
         <v>3564</v>
       </c>
-      <c r="B641" s="2" t="s">
+      <c r="B641" s="3" t="s">
         <v>3565</v>
       </c>
       <c r="C641" s="2"/>
@@ -37693,7 +37693,7 @@
       <c r="A642" s="2" t="s">
         <v>3569</v>
       </c>
-      <c r="B642" s="2" t="s">
+      <c r="B642" s="3" t="s">
         <v>3570</v>
       </c>
       <c r="C642" s="2"/>
@@ -37725,7 +37725,7 @@
       <c r="A643" s="2" t="s">
         <v>3574</v>
       </c>
-      <c r="B643" s="2" t="s">
+      <c r="B643" s="3" t="s">
         <v>3575</v>
       </c>
       <c r="C643" s="2"/>
@@ -37757,7 +37757,7 @@
       <c r="A644" s="2" t="s">
         <v>3579</v>
       </c>
-      <c r="B644" s="2" t="s">
+      <c r="B644" s="3" t="s">
         <v>3580</v>
       </c>
       <c r="C644" s="2"/>
@@ -37821,7 +37821,7 @@
       <c r="A646" s="2" t="s">
         <v>3589</v>
       </c>
-      <c r="B646" s="2" t="s">
+      <c r="B646" s="3" t="s">
         <v>3590</v>
       </c>
       <c r="C646" s="2"/>
@@ -37853,7 +37853,7 @@
       <c r="A647" s="2" t="s">
         <v>3594</v>
       </c>
-      <c r="B647" s="2" t="s">
+      <c r="B647" s="3" t="s">
         <v>3595</v>
       </c>
       <c r="C647" s="2"/>
@@ -37917,7 +37917,7 @@
       <c r="A649" s="2" t="s">
         <v>3604</v>
       </c>
-      <c r="B649" s="2" t="s">
+      <c r="B649" s="3" t="s">
         <v>3605</v>
       </c>
       <c r="C649" s="2"/>
@@ -37949,7 +37949,7 @@
       <c r="A650" s="2" t="s">
         <v>3609</v>
       </c>
-      <c r="B650" s="2" t="s">
+      <c r="B650" s="3" t="s">
         <v>3610</v>
       </c>
       <c r="C650" s="2"/>
@@ -37981,7 +37981,7 @@
       <c r="A651" s="2" t="s">
         <v>3614</v>
       </c>
-      <c r="B651" s="2" t="s">
+      <c r="B651" s="3" t="s">
         <v>3615</v>
       </c>
       <c r="C651" s="2"/>
@@ -38013,7 +38013,7 @@
       <c r="A652" s="2" t="s">
         <v>3619</v>
       </c>
-      <c r="B652" s="2" t="s">
+      <c r="B652" s="3" t="s">
         <v>3620</v>
       </c>
       <c r="C652" s="2"/>
@@ -38045,7 +38045,7 @@
       <c r="A653" s="2" t="s">
         <v>3624</v>
       </c>
-      <c r="B653" s="2" t="s">
+      <c r="B653" s="3" t="s">
         <v>3625</v>
       </c>
       <c r="C653" s="2"/>
@@ -38077,7 +38077,7 @@
       <c r="A654" s="2" t="s">
         <v>3629</v>
       </c>
-      <c r="B654" s="2" t="s">
+      <c r="B654" s="3" t="s">
         <v>3630</v>
       </c>
       <c r="C654" s="2"/>
@@ -38109,7 +38109,7 @@
       <c r="A655" s="2" t="s">
         <v>3634</v>
       </c>
-      <c r="B655" s="2" t="s">
+      <c r="B655" s="3" t="s">
         <v>3635</v>
       </c>
       <c r="C655" s="2"/>
@@ -38141,7 +38141,7 @@
       <c r="A656" s="2" t="s">
         <v>3639</v>
       </c>
-      <c r="B656" s="2" t="s">
+      <c r="B656" s="3" t="s">
         <v>3640</v>
       </c>
       <c r="C656" s="2"/>
@@ -38173,7 +38173,7 @@
       <c r="A657" s="2" t="s">
         <v>3644</v>
       </c>
-      <c r="B657" s="2" t="s">
+      <c r="B657" s="3" t="s">
         <v>3645</v>
       </c>
       <c r="C657" s="2"/>
@@ -38205,7 +38205,7 @@
       <c r="A658" s="2" t="s">
         <v>3649</v>
       </c>
-      <c r="B658" s="2" t="s">
+      <c r="B658" s="3" t="s">
         <v>3650</v>
       </c>
       <c r="C658" s="2"/>
@@ -38237,7 +38237,7 @@
       <c r="A659" s="2" t="s">
         <v>3654</v>
       </c>
-      <c r="B659" s="2" t="s">
+      <c r="B659" s="3" t="s">
         <v>3655</v>
       </c>
       <c r="C659" s="2"/>
@@ -38269,7 +38269,7 @@
       <c r="A660" s="2" t="s">
         <v>3659</v>
       </c>
-      <c r="B660" s="2" t="s">
+      <c r="B660" s="3" t="s">
         <v>3660</v>
       </c>
       <c r="C660" s="2"/>
@@ -38301,7 +38301,7 @@
       <c r="A661" s="2" t="s">
         <v>3664</v>
       </c>
-      <c r="B661" s="2" t="s">
+      <c r="B661" s="3" t="s">
         <v>3665</v>
       </c>
       <c r="C661" s="2"/>
@@ -38333,7 +38333,7 @@
       <c r="A662" s="2" t="s">
         <v>3669</v>
       </c>
-      <c r="B662" s="2" t="s">
+      <c r="B662" s="3" t="s">
         <v>3670</v>
       </c>
       <c r="C662" s="2"/>
@@ -38397,7 +38397,7 @@
       <c r="A664" s="2" t="s">
         <v>3679</v>
       </c>
-      <c r="B664" s="2" t="s">
+      <c r="B664" s="3" t="s">
         <v>3680</v>
       </c>
       <c r="C664" s="2"/>
@@ -38429,7 +38429,7 @@
       <c r="A665" s="2" t="s">
         <v>3684</v>
       </c>
-      <c r="B665" s="2" t="s">
+      <c r="B665" s="3" t="s">
         <v>3685</v>
       </c>
       <c r="C665" s="2"/>
@@ -38461,7 +38461,7 @@
       <c r="A666" s="2" t="s">
         <v>3689</v>
       </c>
-      <c r="B666" s="2" t="s">
+      <c r="B666" s="3" t="s">
         <v>3690</v>
       </c>
       <c r="C666" s="2"/>
@@ -38493,7 +38493,7 @@
       <c r="A667" s="2" t="s">
         <v>3694</v>
       </c>
-      <c r="B667" s="2" t="s">
+      <c r="B667" s="3" t="s">
         <v>3695</v>
       </c>
       <c r="C667" s="2"/>
@@ -38525,7 +38525,7 @@
       <c r="A668" s="2" t="s">
         <v>3699</v>
       </c>
-      <c r="B668" s="2" t="s">
+      <c r="B668" s="3" t="s">
         <v>3700</v>
       </c>
       <c r="C668" s="2"/>
@@ -38557,7 +38557,7 @@
       <c r="A669" s="2" t="s">
         <v>3704</v>
       </c>
-      <c r="B669" s="2" t="s">
+      <c r="B669" s="3" t="s">
         <v>3705</v>
       </c>
       <c r="C669" s="2"/>
@@ -38589,7 +38589,7 @@
       <c r="A670" s="2" t="s">
         <v>3709</v>
       </c>
-      <c r="B670" s="2" t="s">
+      <c r="B670" s="3" t="s">
         <v>3710</v>
       </c>
       <c r="C670" s="2"/>
@@ -38621,7 +38621,7 @@
       <c r="A671" s="2" t="s">
         <v>3714</v>
       </c>
-      <c r="B671" s="2" t="s">
+      <c r="B671" s="3" t="s">
         <v>3715</v>
       </c>
       <c r="C671" s="2"/>
@@ -38653,7 +38653,7 @@
       <c r="A672" s="2" t="s">
         <v>3719</v>
       </c>
-      <c r="B672" s="2" t="s">
+      <c r="B672" s="3" t="s">
         <v>3720</v>
       </c>
       <c r="C672" s="2"/>
@@ -38685,7 +38685,7 @@
       <c r="A673" s="2" t="s">
         <v>3724</v>
       </c>
-      <c r="B673" s="2" t="s">
+      <c r="B673" s="3" t="s">
         <v>3725</v>
       </c>
       <c r="C673" s="2"/>
@@ -38717,7 +38717,7 @@
       <c r="A674" s="2" t="s">
         <v>3729</v>
       </c>
-      <c r="B674" s="2" t="s">
+      <c r="B674" s="3" t="s">
         <v>3730</v>
       </c>
       <c r="C674" s="2"/>
@@ -38749,7 +38749,7 @@
       <c r="A675" s="2" t="s">
         <v>3734</v>
       </c>
-      <c r="B675" s="2" t="s">
+      <c r="B675" s="3" t="s">
         <v>3730</v>
       </c>
       <c r="C675" s="2"/>
@@ -38781,7 +38781,7 @@
       <c r="A676" s="2" t="s">
         <v>3738</v>
       </c>
-      <c r="B676" s="2" t="s">
+      <c r="B676" s="3" t="s">
         <v>3739</v>
       </c>
       <c r="C676" s="2"/>
@@ -38845,7 +38845,7 @@
       <c r="A678" s="2" t="s">
         <v>3748</v>
       </c>
-      <c r="B678" s="2" t="s">
+      <c r="B678" s="3" t="s">
         <v>3749</v>
       </c>
       <c r="C678" s="2"/>
@@ -38877,7 +38877,7 @@
       <c r="A679" s="2" t="s">
         <v>3753</v>
       </c>
-      <c r="B679" s="2" t="s">
+      <c r="B679" s="3" t="s">
         <v>3754</v>
       </c>
       <c r="C679" s="2"/>
@@ -38909,7 +38909,7 @@
       <c r="A680" s="2" t="s">
         <v>3758</v>
       </c>
-      <c r="B680" s="2" t="s">
+      <c r="B680" s="3" t="s">
         <v>3759</v>
       </c>
       <c r="C680" s="2"/>
@@ -38941,7 +38941,7 @@
       <c r="A681" s="2" t="s">
         <v>3763</v>
       </c>
-      <c r="B681" s="2" t="s">
+      <c r="B681" s="3" t="s">
         <v>3764</v>
       </c>
       <c r="C681" s="2"/>
@@ -38973,7 +38973,7 @@
       <c r="A682" s="2" t="s">
         <v>3768</v>
       </c>
-      <c r="B682" s="2" t="s">
+      <c r="B682" s="3" t="s">
         <v>3769</v>
       </c>
       <c r="C682" s="2"/>
@@ -39005,7 +39005,7 @@
       <c r="A683" s="2" t="s">
         <v>3773</v>
       </c>
-      <c r="B683" s="2" t="s">
+      <c r="B683" s="3" t="s">
         <v>3774</v>
       </c>
       <c r="C683" s="2"/>
@@ -39037,7 +39037,7 @@
       <c r="A684" s="2" t="s">
         <v>3778</v>
       </c>
-      <c r="B684" s="2" t="s">
+      <c r="B684" s="3" t="s">
         <v>3779</v>
       </c>
       <c r="C684" s="2"/>
@@ -39069,7 +39069,7 @@
       <c r="A685" s="2" t="s">
         <v>3783</v>
       </c>
-      <c r="B685" s="2" t="s">
+      <c r="B685" s="3" t="s">
         <v>3784</v>
       </c>
       <c r="C685" s="2"/>
@@ -39101,7 +39101,7 @@
       <c r="A686" s="2" t="s">
         <v>3788</v>
       </c>
-      <c r="B686" s="2" t="s">
+      <c r="B686" s="3" t="s">
         <v>3789</v>
       </c>
       <c r="C686" s="2"/>
@@ -39133,7 +39133,7 @@
       <c r="A687" s="2" t="s">
         <v>3793</v>
       </c>
-      <c r="B687" s="2" t="s">
+      <c r="B687" s="3" t="s">
         <v>3794</v>
       </c>
       <c r="C687" s="2"/>
@@ -39165,7 +39165,7 @@
       <c r="A688" s="2" t="s">
         <v>3798</v>
       </c>
-      <c r="B688" s="2" t="s">
+      <c r="B688" s="3" t="s">
         <v>3799</v>
       </c>
       <c r="C688" s="2"/>
@@ -39197,7 +39197,7 @@
       <c r="A689" s="2" t="s">
         <v>3803</v>
       </c>
-      <c r="B689" s="2" t="s">
+      <c r="B689" s="3" t="s">
         <v>3804</v>
       </c>
       <c r="C689" s="2"/>
@@ -39229,7 +39229,7 @@
       <c r="A690" s="2" t="s">
         <v>3808</v>
       </c>
-      <c r="B690" s="2" t="s">
+      <c r="B690" s="3" t="s">
         <v>3809</v>
       </c>
       <c r="C690" s="2"/>
@@ -39261,7 +39261,7 @@
       <c r="A691" s="2" t="s">
         <v>3813</v>
       </c>
-      <c r="B691" s="2" t="s">
+      <c r="B691" s="3" t="s">
         <v>3814</v>
       </c>
       <c r="C691" s="2"/>
@@ -39293,7 +39293,7 @@
       <c r="A692" s="2" t="s">
         <v>3818</v>
       </c>
-      <c r="B692" s="2" t="s">
+      <c r="B692" s="3" t="s">
         <v>3819</v>
       </c>
       <c r="C692" s="2"/>
@@ -39325,7 +39325,7 @@
       <c r="A693" s="2" t="s">
         <v>3823</v>
       </c>
-      <c r="B693" s="2" t="s">
+      <c r="B693" s="3" t="s">
         <v>3824</v>
       </c>
       <c r="C693" s="2"/>
@@ -39357,7 +39357,7 @@
       <c r="A694" s="2" t="s">
         <v>3828</v>
       </c>
-      <c r="B694" s="2" t="s">
+      <c r="B694" s="3" t="s">
         <v>3829</v>
       </c>
       <c r="C694" s="2"/>
@@ -39389,7 +39389,7 @@
       <c r="A695" s="2" t="s">
         <v>3833</v>
       </c>
-      <c r="B695" s="2" t="s">
+      <c r="B695" s="3" t="s">
         <v>3834</v>
       </c>
       <c r="C695" s="2"/>
@@ -39421,7 +39421,7 @@
       <c r="A696" s="2" t="s">
         <v>3838</v>
       </c>
-      <c r="B696" s="2" t="s">
+      <c r="B696" s="3" t="s">
         <v>3839</v>
       </c>
       <c r="C696" s="2"/>
@@ -39453,7 +39453,7 @@
       <c r="A697" s="2" t="s">
         <v>3843</v>
       </c>
-      <c r="B697" s="2" t="s">
+      <c r="B697" s="3" t="s">
         <v>3844</v>
       </c>
       <c r="C697" s="2"/>
@@ -39485,7 +39485,7 @@
       <c r="A698" s="2" t="s">
         <v>3848</v>
       </c>
-      <c r="B698" s="2" t="s">
+      <c r="B698" s="3" t="s">
         <v>3849</v>
       </c>
       <c r="C698" s="2"/>
@@ -39517,7 +39517,7 @@
       <c r="A699" s="2" t="s">
         <v>3853</v>
       </c>
-      <c r="B699" s="2" t="s">
+      <c r="B699" s="3" t="s">
         <v>3854</v>
       </c>
       <c r="C699" s="2"/>
@@ -39549,7 +39549,7 @@
       <c r="A700" s="2" t="s">
         <v>3858</v>
       </c>
-      <c r="B700" s="2" t="s">
+      <c r="B700" s="3" t="s">
         <v>3859</v>
       </c>
       <c r="C700" s="2"/>
@@ -39581,7 +39581,7 @@
       <c r="A701" s="2" t="s">
         <v>3863</v>
       </c>
-      <c r="B701" s="2" t="s">
+      <c r="B701" s="3" t="s">
         <v>3864</v>
       </c>
       <c r="C701" s="2"/>
@@ -39613,7 +39613,7 @@
       <c r="A702" s="2" t="s">
         <v>3867</v>
       </c>
-      <c r="B702" s="2" t="s">
+      <c r="B702" s="3" t="s">
         <v>3868</v>
       </c>
       <c r="C702" s="2"/>
@@ -39645,7 +39645,7 @@
       <c r="A703" s="2" t="s">
         <v>3872</v>
       </c>
-      <c r="B703" s="2" t="s">
+      <c r="B703" s="3" t="s">
         <v>3873</v>
       </c>
       <c r="C703" s="2"/>
@@ -39677,7 +39677,7 @@
       <c r="A704" s="2" t="s">
         <v>3877</v>
       </c>
-      <c r="B704" s="2" t="s">
+      <c r="B704" s="3" t="s">
         <v>3878</v>
       </c>
       <c r="C704" s="2"/>
@@ -39709,7 +39709,7 @@
       <c r="A705" s="2" t="s">
         <v>3882</v>
       </c>
-      <c r="B705" s="2" t="s">
+      <c r="B705" s="3" t="s">
         <v>3883</v>
       </c>
       <c r="C705" s="2"/>
@@ -39741,7 +39741,7 @@
       <c r="A706" s="2" t="s">
         <v>3887</v>
       </c>
-      <c r="B706" s="2" t="s">
+      <c r="B706" s="3" t="s">
         <v>3888</v>
       </c>
       <c r="C706" s="2"/>
@@ -39773,7 +39773,7 @@
       <c r="A707" s="2" t="s">
         <v>3892</v>
       </c>
-      <c r="B707" s="2" t="s">
+      <c r="B707" s="3" t="s">
         <v>3893</v>
       </c>
       <c r="C707" s="2"/>
@@ -39805,7 +39805,7 @@
       <c r="A708" s="2" t="s">
         <v>3897</v>
       </c>
-      <c r="B708" s="2" t="s">
+      <c r="B708" s="3" t="s">
         <v>3898</v>
       </c>
       <c r="C708" s="2"/>
@@ -39837,7 +39837,7 @@
       <c r="A709" s="2" t="s">
         <v>3902</v>
       </c>
-      <c r="B709" s="2" t="s">
+      <c r="B709" s="3" t="s">
         <v>3903</v>
       </c>
       <c r="C709" s="2"/>
@@ -39869,7 +39869,7 @@
       <c r="A710" s="2" t="s">
         <v>3907</v>
       </c>
-      <c r="B710" s="2" t="s">
+      <c r="B710" s="3" t="s">
         <v>3908</v>
       </c>
       <c r="C710" s="2"/>
@@ -39901,7 +39901,7 @@
       <c r="A711" s="2" t="s">
         <v>3912</v>
       </c>
-      <c r="B711" s="2" t="s">
+      <c r="B711" s="3" t="s">
         <v>3913</v>
       </c>
       <c r="C711" s="2"/>
@@ -39933,7 +39933,7 @@
       <c r="A712" s="2" t="s">
         <v>3917</v>
       </c>
-      <c r="B712" s="2" t="s">
+      <c r="B712" s="3" t="s">
         <v>3918</v>
       </c>
       <c r="C712" s="2"/>
@@ -39965,7 +39965,7 @@
       <c r="A713" s="2" t="s">
         <v>3922</v>
       </c>
-      <c r="B713" s="2" t="s">
+      <c r="B713" s="3" t="s">
         <v>3923</v>
       </c>
       <c r="C713" s="2"/>
@@ -39997,7 +39997,7 @@
       <c r="A714" s="2" t="s">
         <v>3927</v>
       </c>
-      <c r="B714" s="2" t="s">
+      <c r="B714" s="3" t="s">
         <v>3928</v>
       </c>
       <c r="C714" s="2"/>
@@ -40029,7 +40029,7 @@
       <c r="A715" s="2" t="s">
         <v>3932</v>
       </c>
-      <c r="B715" s="2" t="s">
+      <c r="B715" s="3" t="s">
         <v>3933</v>
       </c>
       <c r="C715" s="2"/>
@@ -40061,7 +40061,7 @@
       <c r="A716" s="2" t="s">
         <v>3937</v>
       </c>
-      <c r="B716" s="2" t="s">
+      <c r="B716" s="3" t="s">
         <v>3938</v>
       </c>
       <c r="C716" s="2"/>
@@ -40093,7 +40093,7 @@
       <c r="A717" s="2" t="s">
         <v>3942</v>
       </c>
-      <c r="B717" s="2" t="s">
+      <c r="B717" s="3" t="s">
         <v>3943</v>
       </c>
       <c r="C717" s="2"/>
@@ -40157,7 +40157,7 @@
       <c r="A719" s="2" t="s">
         <v>3952</v>
       </c>
-      <c r="B719" s="2" t="s">
+      <c r="B719" s="3" t="s">
         <v>3953</v>
       </c>
       <c r="C719" s="2"/>
@@ -40189,7 +40189,7 @@
       <c r="A720" s="2" t="s">
         <v>3957</v>
       </c>
-      <c r="B720" s="2" t="s">
+      <c r="B720" s="3" t="s">
         <v>3958</v>
       </c>
       <c r="C720" s="2"/>
@@ -40221,7 +40221,7 @@
       <c r="A721" s="2" t="s">
         <v>3962</v>
       </c>
-      <c r="B721" s="2" t="s">
+      <c r="B721" s="3" t="s">
         <v>3963</v>
       </c>
       <c r="C721" s="2"/>
@@ -40253,7 +40253,7 @@
       <c r="A722" s="2" t="s">
         <v>3967</v>
       </c>
-      <c r="B722" s="2" t="s">
+      <c r="B722" s="3" t="s">
         <v>3968</v>
       </c>
       <c r="C722" s="2"/>
@@ -40285,7 +40285,7 @@
       <c r="A723" s="2" t="s">
         <v>3972</v>
       </c>
-      <c r="B723" s="2" t="s">
+      <c r="B723" s="3" t="s">
         <v>3973</v>
       </c>
       <c r="C723" s="2"/>
@@ -40317,7 +40317,7 @@
       <c r="A724" s="2" t="s">
         <v>3977</v>
       </c>
-      <c r="B724" s="2" t="s">
+      <c r="B724" s="3" t="s">
         <v>3978</v>
       </c>
       <c r="C724" s="2"/>
@@ -40349,7 +40349,7 @@
       <c r="A725" s="2" t="s">
         <v>3982</v>
       </c>
-      <c r="B725" s="2" t="s">
+      <c r="B725" s="3" t="s">
         <v>3983</v>
       </c>
       <c r="C725" s="2"/>
@@ -40381,7 +40381,7 @@
       <c r="A726" s="2" t="s">
         <v>3987</v>
       </c>
-      <c r="B726" s="2" t="s">
+      <c r="B726" s="3" t="s">
         <v>3988</v>
       </c>
       <c r="C726" s="2"/>
@@ -40413,7 +40413,7 @@
       <c r="A727" s="2" t="s">
         <v>3992</v>
       </c>
-      <c r="B727" s="2" t="s">
+      <c r="B727" s="3" t="s">
         <v>3993</v>
       </c>
       <c r="C727" s="2"/>
@@ -40445,7 +40445,7 @@
       <c r="A728" s="2" t="s">
         <v>3997</v>
       </c>
-      <c r="B728" s="2" t="s">
+      <c r="B728" s="3" t="s">
         <v>3998</v>
       </c>
       <c r="C728" s="2"/>
@@ -40477,7 +40477,7 @@
       <c r="A729" s="2" t="s">
         <v>4002</v>
       </c>
-      <c r="B729" s="2" t="s">
+      <c r="B729" s="3" t="s">
         <v>4003</v>
       </c>
       <c r="C729" s="2"/>
@@ -40509,7 +40509,7 @@
       <c r="A730" s="2" t="s">
         <v>4007</v>
       </c>
-      <c r="B730" s="2" t="s">
+      <c r="B730" s="3" t="s">
         <v>4008</v>
       </c>
       <c r="C730" s="2"/>
@@ -40541,7 +40541,7 @@
       <c r="A731" s="2" t="s">
         <v>4012</v>
       </c>
-      <c r="B731" s="2" t="s">
+      <c r="B731" s="3" t="s">
         <v>4013</v>
       </c>
       <c r="C731" s="2"/>
@@ -40573,7 +40573,7 @@
       <c r="A732" s="2" t="s">
         <v>4017</v>
       </c>
-      <c r="B732" s="2" t="s">
+      <c r="B732" s="3" t="s">
         <v>4018</v>
       </c>
       <c r="C732" s="2"/>
@@ -40605,7 +40605,7 @@
       <c r="A733" s="2" t="s">
         <v>4022</v>
       </c>
-      <c r="B733" s="2" t="s">
+      <c r="B733" s="3" t="s">
         <v>4023</v>
       </c>
       <c r="C733" s="2"/>
@@ -40637,7 +40637,7 @@
       <c r="A734" s="2" t="s">
         <v>4027</v>
       </c>
-      <c r="B734" s="2" t="s">
+      <c r="B734" s="3" t="s">
         <v>4028</v>
       </c>
       <c r="C734" s="2"/>
@@ -40669,7 +40669,7 @@
       <c r="A735" s="2" t="s">
         <v>4032</v>
       </c>
-      <c r="B735" s="2" t="s">
+      <c r="B735" s="3" t="s">
         <v>4033</v>
       </c>
       <c r="C735" s="2"/>
@@ -40701,7 +40701,7 @@
       <c r="A736" s="2" t="s">
         <v>4037</v>
       </c>
-      <c r="B736" s="2" t="s">
+      <c r="B736" s="3" t="s">
         <v>4038</v>
       </c>
       <c r="C736" s="2"/>
@@ -40733,7 +40733,7 @@
       <c r="A737" s="2" t="s">
         <v>4042</v>
       </c>
-      <c r="B737" s="2" t="s">
+      <c r="B737" s="3" t="s">
         <v>4043</v>
       </c>
       <c r="C737" s="2"/>
@@ -40765,7 +40765,7 @@
       <c r="A738" s="2" t="s">
         <v>4047</v>
       </c>
-      <c r="B738" s="2" t="s">
+      <c r="B738" s="3" t="s">
         <v>4048</v>
       </c>
       <c r="C738" s="2"/>
@@ -40797,7 +40797,7 @@
       <c r="A739" s="2" t="s">
         <v>4052</v>
       </c>
-      <c r="B739" s="2" t="s">
+      <c r="B739" s="3" t="s">
         <v>4053</v>
       </c>
       <c r="C739" s="2"/>
@@ -40829,7 +40829,7 @@
       <c r="A740" s="2" t="s">
         <v>4057</v>
       </c>
-      <c r="B740" s="2" t="s">
+      <c r="B740" s="3" t="s">
         <v>4058</v>
       </c>
       <c r="C740" s="2"/>
@@ -40861,7 +40861,7 @@
       <c r="A741" s="2" t="s">
         <v>4062</v>
       </c>
-      <c r="B741" s="2" t="s">
+      <c r="B741" s="3" t="s">
         <v>4063</v>
       </c>
       <c r="C741" s="2"/>
@@ -40893,7 +40893,7 @@
       <c r="A742" s="2" t="s">
         <v>4067</v>
       </c>
-      <c r="B742" s="2" t="s">
+      <c r="B742" s="3" t="s">
         <v>4068</v>
       </c>
       <c r="C742" s="2"/>
@@ -40925,7 +40925,7 @@
       <c r="A743" s="2" t="s">
         <v>4072</v>
       </c>
-      <c r="B743" s="2" t="s">
+      <c r="B743" s="3" t="s">
         <v>4073</v>
       </c>
       <c r="C743" s="2"/>
@@ -40957,7 +40957,7 @@
       <c r="A744" s="2" t="s">
         <v>4077</v>
       </c>
-      <c r="B744" s="2" t="s">
+      <c r="B744" s="3" t="s">
         <v>4078</v>
       </c>
       <c r="C744" s="2"/>
@@ -40989,7 +40989,7 @@
       <c r="A745" s="2" t="s">
         <v>4082</v>
       </c>
-      <c r="B745" s="2" t="s">
+      <c r="B745" s="3" t="s">
         <v>4083</v>
       </c>
       <c r="C745" s="2"/>
@@ -41021,7 +41021,7 @@
       <c r="A746" s="2" t="s">
         <v>4087</v>
       </c>
-      <c r="B746" s="2" t="s">
+      <c r="B746" s="3" t="s">
         <v>4088</v>
       </c>
       <c r="C746" s="2"/>
@@ -41053,7 +41053,7 @@
       <c r="A747" s="2" t="s">
         <v>4092</v>
       </c>
-      <c r="B747" s="2" t="s">
+      <c r="B747" s="3" t="s">
         <v>4093</v>
       </c>
       <c r="C747" s="2"/>
@@ -41085,7 +41085,7 @@
       <c r="A748" s="2" t="s">
         <v>4097</v>
       </c>
-      <c r="B748" s="2" t="s">
+      <c r="B748" s="3" t="s">
         <v>4098</v>
       </c>
       <c r="C748" s="2"/>
@@ -41117,7 +41117,7 @@
       <c r="A749" s="2" t="s">
         <v>4102</v>
       </c>
-      <c r="B749" s="2" t="s">
+      <c r="B749" s="3" t="s">
         <v>4103</v>
       </c>
       <c r="C749" s="2"/>
@@ -41213,7 +41213,7 @@
       <c r="A752" s="2" t="s">
         <v>4117</v>
       </c>
-      <c r="B752" s="2" t="s">
+      <c r="B752" s="3" t="s">
         <v>4118</v>
       </c>
       <c r="C752" s="2"/>
@@ -41245,7 +41245,7 @@
       <c r="A753" s="2" t="s">
         <v>4122</v>
       </c>
-      <c r="B753" s="2" t="s">
+      <c r="B753" s="3" t="s">
         <v>4123</v>
       </c>
       <c r="C753" s="2"/>
@@ -41277,7 +41277,7 @@
       <c r="A754" s="2" t="s">
         <v>4127</v>
       </c>
-      <c r="B754" s="2" t="s">
+      <c r="B754" s="3" t="s">
         <v>4128</v>
       </c>
       <c r="C754" s="2"/>
@@ -41309,7 +41309,7 @@
       <c r="A755" s="2" t="s">
         <v>4132</v>
       </c>
-      <c r="B755" s="2" t="s">
+      <c r="B755" s="3" t="s">
         <v>4133</v>
       </c>
       <c r="C755" s="2"/>
@@ -41341,7 +41341,7 @@
       <c r="A756" s="2" t="s">
         <v>4137</v>
       </c>
-      <c r="B756" s="2" t="s">
+      <c r="B756" s="3" t="s">
         <v>4138</v>
       </c>
       <c r="C756" s="2"/>
@@ -41405,7 +41405,7 @@
       <c r="A758" s="2" t="s">
         <v>4147</v>
       </c>
-      <c r="B758" s="2" t="s">
+      <c r="B758" s="3" t="s">
         <v>4148</v>
       </c>
       <c r="C758" s="2"/>
@@ -41437,7 +41437,7 @@
       <c r="A759" s="2" t="s">
         <v>4152</v>
       </c>
-      <c r="B759" s="2" t="s">
+      <c r="B759" s="3" t="s">
         <v>4153</v>
       </c>
       <c r="C759" s="2"/>
@@ -41469,7 +41469,7 @@
       <c r="A760" s="2" t="s">
         <v>4157</v>
       </c>
-      <c r="B760" s="2" t="s">
+      <c r="B760" s="3" t="s">
         <v>4158</v>
       </c>
       <c r="C760" s="2"/>
@@ -41501,7 +41501,7 @@
       <c r="A761" s="2" t="s">
         <v>4162</v>
       </c>
-      <c r="B761" s="2" t="s">
+      <c r="B761" s="3" t="s">
         <v>4163</v>
       </c>
       <c r="C761" s="2"/>
@@ -41533,7 +41533,7 @@
       <c r="A762" s="2" t="s">
         <v>4167</v>
       </c>
-      <c r="B762" s="2" t="s">
+      <c r="B762" s="3" t="s">
         <v>4168</v>
       </c>
       <c r="C762" s="2"/>
@@ -41565,7 +41565,7 @@
       <c r="A763" s="2" t="s">
         <v>4172</v>
       </c>
-      <c r="B763" s="2" t="s">
+      <c r="B763" s="3" t="s">
         <v>4173</v>
       </c>
       <c r="C763" s="2"/>
@@ -41597,7 +41597,7 @@
       <c r="A764" s="2" t="s">
         <v>4177</v>
       </c>
-      <c r="B764" s="2" t="s">
+      <c r="B764" s="3" t="s">
         <v>4178</v>
       </c>
       <c r="C764" s="2"/>
@@ -41629,7 +41629,7 @@
       <c r="A765" s="2" t="s">
         <v>4182</v>
       </c>
-      <c r="B765" s="2" t="s">
+      <c r="B765" s="3" t="s">
         <v>4183</v>
       </c>
       <c r="C765" s="2"/>
@@ -41661,7 +41661,7 @@
       <c r="A766" s="2" t="s">
         <v>4187</v>
       </c>
-      <c r="B766" s="2" t="s">
+      <c r="B766" s="3" t="s">
         <v>4188</v>
       </c>
       <c r="C766" s="2"/>
@@ -41693,7 +41693,7 @@
       <c r="A767" s="2" t="s">
         <v>4192</v>
       </c>
-      <c r="B767" s="2" t="s">
+      <c r="B767" s="3" t="s">
         <v>4193</v>
       </c>
       <c r="C767" s="2"/>
@@ -41725,7 +41725,7 @@
       <c r="A768" s="2" t="s">
         <v>4197</v>
       </c>
-      <c r="B768" s="2" t="s">
+      <c r="B768" s="3" t="s">
         <v>4198</v>
       </c>
       <c r="C768" s="2"/>
@@ -41757,7 +41757,7 @@
       <c r="A769" s="2" t="s">
         <v>4202</v>
       </c>
-      <c r="B769" s="2" t="s">
+      <c r="B769" s="3" t="s">
         <v>4203</v>
       </c>
       <c r="C769" s="2"/>
@@ -41789,7 +41789,7 @@
       <c r="A770" s="2" t="s">
         <v>4207</v>
       </c>
-      <c r="B770" s="2" t="s">
+      <c r="B770" s="3" t="s">
         <v>4208</v>
       </c>
       <c r="C770" s="2"/>
@@ -41821,7 +41821,7 @@
       <c r="A771" s="2" t="s">
         <v>4212</v>
       </c>
-      <c r="B771" s="2" t="s">
+      <c r="B771" s="3" t="s">
         <v>4213</v>
       </c>
       <c r="C771" s="2"/>
@@ -41885,7 +41885,7 @@
       <c r="A773" s="2" t="s">
         <v>4222</v>
       </c>
-      <c r="B773" s="2" t="s">
+      <c r="B773" s="3" t="s">
         <v>4223</v>
       </c>
       <c r="C773" s="2"/>
@@ -41917,7 +41917,7 @@
       <c r="A774" s="2" t="s">
         <v>4227</v>
       </c>
-      <c r="B774" s="2" t="s">
+      <c r="B774" s="3" t="s">
         <v>4228</v>
       </c>
       <c r="C774" s="2"/>
@@ -41949,7 +41949,7 @@
       <c r="A775" s="2" t="s">
         <v>4232</v>
       </c>
-      <c r="B775" s="2" t="s">
+      <c r="B775" s="3" t="s">
         <v>4233</v>
       </c>
       <c r="C775" s="2"/>
@@ -41981,7 +41981,7 @@
       <c r="A776" s="2" t="s">
         <v>4237</v>
       </c>
-      <c r="B776" s="2" t="s">
+      <c r="B776" s="3" t="s">
         <v>4238</v>
       </c>
       <c r="C776" s="2"/>
@@ -42013,7 +42013,7 @@
       <c r="A777" s="2" t="s">
         <v>4242</v>
       </c>
-      <c r="B777" s="2" t="s">
+      <c r="B777" s="3" t="s">
         <v>4243</v>
       </c>
       <c r="C777" s="2"/>
@@ -42045,7 +42045,7 @@
       <c r="A778" s="2" t="s">
         <v>4247</v>
       </c>
-      <c r="B778" s="2" t="s">
+      <c r="B778" s="3" t="s">
         <v>4248</v>
       </c>
       <c r="C778" s="2"/>
@@ -42077,7 +42077,7 @@
       <c r="A779" s="2" t="s">
         <v>4252</v>
       </c>
-      <c r="B779" s="2" t="s">
+      <c r="B779" s="3" t="s">
         <v>4253</v>
       </c>
       <c r="C779" s="2"/>
@@ -42109,7 +42109,7 @@
       <c r="A780" s="2" t="s">
         <v>4257</v>
       </c>
-      <c r="B780" s="2" t="s">
+      <c r="B780" s="3" t="s">
         <v>4258</v>
       </c>
       <c r="C780" s="2"/>
@@ -42141,7 +42141,7 @@
       <c r="A781" s="2" t="s">
         <v>4262</v>
       </c>
-      <c r="B781" s="2" t="s">
+      <c r="B781" s="3" t="s">
         <v>4263</v>
       </c>
       <c r="C781" s="2"/>
@@ -42173,7 +42173,7 @@
       <c r="A782" s="2" t="s">
         <v>4267</v>
       </c>
-      <c r="B782" s="2" t="s">
+      <c r="B782" s="3" t="s">
         <v>4268</v>
       </c>
       <c r="C782" s="2"/>
@@ -42205,7 +42205,7 @@
       <c r="A783" s="2" t="s">
         <v>4272</v>
       </c>
-      <c r="B783" s="2" t="s">
+      <c r="B783" s="3" t="s">
         <v>4273</v>
       </c>
       <c r="C783" s="2"/>
@@ -42269,7 +42269,7 @@
       <c r="A785" s="2" t="s">
         <v>4282</v>
       </c>
-      <c r="B785" s="2" t="s">
+      <c r="B785" s="3" t="s">
         <v>4283</v>
       </c>
       <c r="C785" s="2"/>
@@ -42301,7 +42301,7 @@
       <c r="A786" s="2" t="s">
         <v>4287</v>
       </c>
-      <c r="B786" s="2" t="s">
+      <c r="B786" s="3" t="s">
         <v>4288</v>
       </c>
       <c r="C786" s="2"/>
@@ -42333,7 +42333,7 @@
       <c r="A787" s="2" t="s">
         <v>4292</v>
       </c>
-      <c r="B787" s="2" t="s">
+      <c r="B787" s="3" t="s">
         <v>4293</v>
       </c>
       <c r="C787" s="2"/>
@@ -42397,7 +42397,7 @@
       <c r="A789" s="2" t="s">
         <v>4302</v>
       </c>
-      <c r="B789" s="2" t="s">
+      <c r="B789" s="3" t="s">
         <v>4303</v>
       </c>
       <c r="C789" s="2"/>
@@ -42429,7 +42429,7 @@
       <c r="A790" s="2" t="s">
         <v>4307</v>
       </c>
-      <c r="B790" s="2" t="s">
+      <c r="B790" s="3" t="s">
         <v>4308</v>
       </c>
       <c r="C790" s="2"/>
@@ -42461,7 +42461,7 @@
       <c r="A791" s="2" t="s">
         <v>4312</v>
       </c>
-      <c r="B791" s="2" t="s">
+      <c r="B791" s="3" t="s">
         <v>4313</v>
       </c>
       <c r="C791" s="2"/>
@@ -42493,7 +42493,7 @@
       <c r="A792" s="2" t="s">
         <v>4317</v>
       </c>
-      <c r="B792" s="2" t="s">
+      <c r="B792" s="3" t="s">
         <v>4318</v>
       </c>
       <c r="C792" s="2"/>
@@ -42525,7 +42525,7 @@
       <c r="A793" s="2" t="s">
         <v>4322</v>
       </c>
-      <c r="B793" s="2" t="s">
+      <c r="B793" s="3" t="s">
         <v>4323</v>
       </c>
       <c r="C793" s="2"/>
@@ -42557,7 +42557,7 @@
       <c r="A794" s="2" t="s">
         <v>4327</v>
       </c>
-      <c r="B794" s="2" t="s">
+      <c r="B794" s="3" t="s">
         <v>4328</v>
       </c>
       <c r="C794" s="2"/>
@@ -42589,7 +42589,7 @@
       <c r="A795" s="2" t="s">
         <v>4332</v>
       </c>
-      <c r="B795" s="2" t="s">
+      <c r="B795" s="3" t="s">
         <v>4333</v>
       </c>
       <c r="C795" s="2"/>
@@ -42621,7 +42621,7 @@
       <c r="A796" s="2" t="s">
         <v>4337</v>
       </c>
-      <c r="B796" s="2" t="s">
+      <c r="B796" s="3" t="s">
         <v>4338</v>
       </c>
       <c r="C796" s="2"/>
@@ -42653,7 +42653,7 @@
       <c r="A797" s="2" t="s">
         <v>4342</v>
       </c>
-      <c r="B797" s="2" t="s">
+      <c r="B797" s="3" t="s">
         <v>4343</v>
       </c>
       <c r="C797" s="2"/>
@@ -42685,7 +42685,7 @@
       <c r="A798" s="2" t="s">
         <v>4346</v>
       </c>
-      <c r="B798" s="2" t="s">
+      <c r="B798" s="3" t="s">
         <v>4347</v>
       </c>
       <c r="C798" s="2"/>
@@ -42717,7 +42717,7 @@
       <c r="A799" s="2" t="s">
         <v>4351</v>
       </c>
-      <c r="B799" s="2" t="s">
+      <c r="B799" s="3" t="s">
         <v>4352</v>
       </c>
       <c r="C799" s="2"/>
@@ -42749,7 +42749,7 @@
       <c r="A800" s="2" t="s">
         <v>4356</v>
       </c>
-      <c r="B800" s="2" t="s">
+      <c r="B800" s="3" t="s">
         <v>4357</v>
       </c>
       <c r="C800" s="2"/>
@@ -42781,7 +42781,7 @@
       <c r="A801" s="2" t="s">
         <v>4361</v>
       </c>
-      <c r="B801" s="2" t="s">
+      <c r="B801" s="3" t="s">
         <v>4362</v>
       </c>
       <c r="C801" s="2"/>
@@ -42813,7 +42813,7 @@
       <c r="A802" s="2" t="s">
         <v>4366</v>
       </c>
-      <c r="B802" s="2" t="s">
+      <c r="B802" s="3" t="s">
         <v>4367</v>
       </c>
       <c r="C802" s="2"/>
@@ -42845,7 +42845,7 @@
       <c r="A803" s="2" t="s">
         <v>4371</v>
       </c>
-      <c r="B803" s="2" t="s">
+      <c r="B803" s="3" t="s">
         <v>4372</v>
       </c>
       <c r="C803" s="2"/>
@@ -42877,7 +42877,7 @@
       <c r="A804" s="2" t="s">
         <v>4376</v>
       </c>
-      <c r="B804" s="2" t="s">
+      <c r="B804" s="3" t="s">
         <v>4377</v>
       </c>
       <c r="C804" s="2"/>
@@ -42909,7 +42909,7 @@
       <c r="A805" s="2" t="s">
         <v>4381</v>
       </c>
-      <c r="B805" s="2" t="s">
+      <c r="B805" s="3" t="s">
         <v>4382</v>
       </c>
       <c r="C805" s="2"/>
@@ -42941,7 +42941,7 @@
       <c r="A806" s="2" t="s">
         <v>4386</v>
       </c>
-      <c r="B806" s="2" t="s">
+      <c r="B806" s="3" t="s">
         <v>4387</v>
       </c>
       <c r="C806" s="2"/>
@@ -43005,7 +43005,7 @@
       <c r="A808" s="2" t="s">
         <v>4396</v>
       </c>
-      <c r="B808" s="2" t="s">
+      <c r="B808" s="3" t="s">
         <v>4397</v>
       </c>
       <c r="C808" s="2"/>
@@ -43037,7 +43037,7 @@
       <c r="A809" s="2" t="s">
         <v>4401</v>
       </c>
-      <c r="B809" s="2" t="s">
+      <c r="B809" s="3" t="s">
         <v>4402</v>
       </c>
       <c r="C809" s="2"/>
@@ -43069,7 +43069,7 @@
       <c r="A810" s="2" t="s">
         <v>4406</v>
       </c>
-      <c r="B810" s="2" t="s">
+      <c r="B810" s="3" t="s">
         <v>4407</v>
       </c>
       <c r="C810" s="2"/>
@@ -43101,7 +43101,7 @@
       <c r="A811" s="2" t="s">
         <v>4411</v>
       </c>
-      <c r="B811" s="2" t="s">
+      <c r="B811" s="3" t="s">
         <v>4412</v>
       </c>
       <c r="C811" s="2"/>
@@ -43133,7 +43133,7 @@
       <c r="A812" s="2" t="s">
         <v>4416</v>
       </c>
-      <c r="B812" s="2" t="s">
+      <c r="B812" s="3" t="s">
         <v>4417</v>
       </c>
       <c r="C812" s="2"/>
@@ -43165,7 +43165,7 @@
       <c r="A813" s="2" t="s">
         <v>4421</v>
       </c>
-      <c r="B813" s="2" t="s">
+      <c r="B813" s="3" t="s">
         <v>4422</v>
       </c>
       <c r="C813" s="2"/>
@@ -43197,7 +43197,7 @@
       <c r="A814" s="2" t="s">
         <v>4426</v>
       </c>
-      <c r="B814" s="2" t="s">
+      <c r="B814" s="3" t="s">
         <v>4427</v>
       </c>
       <c r="C814" s="2"/>
@@ -43229,7 +43229,7 @@
       <c r="A815" s="2" t="s">
         <v>4431</v>
       </c>
-      <c r="B815" s="2" t="s">
+      <c r="B815" s="3" t="s">
         <v>4432</v>
       </c>
       <c r="C815" s="2"/>
@@ -43261,7 +43261,7 @@
       <c r="A816" s="2" t="s">
         <v>4436</v>
       </c>
-      <c r="B816" s="2" t="s">
+      <c r="B816" s="3" t="s">
         <v>4437</v>
       </c>
       <c r="C816" s="2"/>
@@ -43293,7 +43293,7 @@
       <c r="A817" s="2" t="s">
         <v>4441</v>
       </c>
-      <c r="B817" s="2" t="s">
+      <c r="B817" s="3" t="s">
         <v>4442</v>
       </c>
       <c r="C817" s="2"/>
@@ -43325,7 +43325,7 @@
       <c r="A818" s="2" t="s">
         <v>4446</v>
       </c>
-      <c r="B818" s="2" t="s">
+      <c r="B818" s="3" t="s">
         <v>4447</v>
       </c>
       <c r="C818" s="2"/>
@@ -43357,7 +43357,7 @@
       <c r="A819" s="2" t="s">
         <v>4451</v>
       </c>
-      <c r="B819" s="2" t="s">
+      <c r="B819" s="3" t="s">
         <v>4452</v>
       </c>
       <c r="C819" s="2"/>
@@ -43389,7 +43389,7 @@
       <c r="A820" s="2" t="s">
         <v>4456</v>
       </c>
-      <c r="B820" s="2" t="s">
+      <c r="B820" s="3" t="s">
         <v>4457</v>
       </c>
       <c r="C820" s="2"/>
@@ -43421,7 +43421,7 @@
       <c r="A821" s="2" t="s">
         <v>4461</v>
       </c>
-      <c r="B821" s="2" t="s">
+      <c r="B821" s="3" t="s">
         <v>4462</v>
       </c>
       <c r="C821" s="2"/>
@@ -43453,7 +43453,7 @@
       <c r="A822" s="2" t="s">
         <v>4466</v>
       </c>
-      <c r="B822" s="2" t="s">
+      <c r="B822" s="3" t="s">
         <v>4467</v>
       </c>
       <c r="C822" s="2"/>
@@ -43485,7 +43485,7 @@
       <c r="A823" s="2" t="s">
         <v>4471</v>
       </c>
-      <c r="B823" s="2" t="s">
+      <c r="B823" s="3" t="s">
         <v>4472</v>
       </c>
       <c r="C823" s="2"/>
@@ -43549,7 +43549,7 @@
       <c r="A825" s="2" t="s">
         <v>4481</v>
       </c>
-      <c r="B825" s="2" t="s">
+      <c r="B825" s="3" t="s">
         <v>4482</v>
       </c>
       <c r="C825" s="2"/>
@@ -43581,7 +43581,7 @@
       <c r="A826" s="2" t="s">
         <v>4486</v>
       </c>
-      <c r="B826" s="2" t="s">
+      <c r="B826" s="3" t="s">
         <v>4487</v>
       </c>
       <c r="C826" s="2"/>
@@ -43613,7 +43613,7 @@
       <c r="A827" s="2" t="s">
         <v>4491</v>
       </c>
-      <c r="B827" s="2" t="s">
+      <c r="B827" s="3" t="s">
         <v>4492</v>
       </c>
       <c r="C827" s="2"/>
@@ -43645,7 +43645,7 @@
       <c r="A828" s="2" t="s">
         <v>4496</v>
       </c>
-      <c r="B828" s="2" t="s">
+      <c r="B828" s="3" t="s">
         <v>4497</v>
       </c>
       <c r="C828" s="2"/>
@@ -43677,7 +43677,7 @@
       <c r="A829" s="2" t="s">
         <v>4501</v>
       </c>
-      <c r="B829" s="2" t="s">
+      <c r="B829" s="3" t="s">
         <v>4502</v>
       </c>
       <c r="C829" s="2"/>
@@ -43709,7 +43709,7 @@
       <c r="A830" s="2" t="s">
         <v>4506</v>
       </c>
-      <c r="B830" s="2" t="s">
+      <c r="B830" s="3" t="s">
         <v>4507</v>
       </c>
       <c r="C830" s="2"/>
@@ -43741,7 +43741,7 @@
       <c r="A831" s="2" t="s">
         <v>4511</v>
       </c>
-      <c r="B831" s="2" t="s">
+      <c r="B831" s="3" t="s">
         <v>4512</v>
       </c>
       <c r="C831" s="2"/>
@@ -43773,7 +43773,7 @@
       <c r="A832" s="2" t="s">
         <v>4516</v>
       </c>
-      <c r="B832" s="2" t="s">
+      <c r="B832" s="3" t="s">
         <v>4517</v>
       </c>
       <c r="C832" s="2"/>
@@ -43805,7 +43805,7 @@
       <c r="A833" s="2" t="s">
         <v>4521</v>
       </c>
-      <c r="B833" s="2" t="s">
+      <c r="B833" s="3" t="s">
         <v>4522</v>
       </c>
       <c r="C833" s="2"/>
@@ -43837,7 +43837,7 @@
       <c r="A834" s="2" t="s">
         <v>4526</v>
       </c>
-      <c r="B834" s="2" t="s">
+      <c r="B834" s="3" t="s">
         <v>4527</v>
       </c>
       <c r="C834" s="2"/>
@@ -43869,7 +43869,7 @@
       <c r="A835" s="2" t="s">
         <v>4531</v>
       </c>
-      <c r="B835" s="2" t="s">
+      <c r="B835" s="3" t="s">
         <v>4532</v>
       </c>
       <c r="C835" s="2"/>
@@ -43901,7 +43901,7 @@
       <c r="A836" s="2" t="s">
         <v>4536</v>
       </c>
-      <c r="B836" s="2" t="s">
+      <c r="B836" s="3" t="s">
         <v>4537</v>
       </c>
       <c r="C836" s="2"/>
@@ -43933,7 +43933,7 @@
       <c r="A837" s="2" t="s">
         <v>4541</v>
       </c>
-      <c r="B837" s="2" t="s">
+      <c r="B837" s="3" t="s">
         <v>4542</v>
       </c>
       <c r="C837" s="2"/>
@@ -43965,7 +43965,7 @@
       <c r="A838" s="2" t="s">
         <v>4546</v>
       </c>
-      <c r="B838" s="2" t="s">
+      <c r="B838" s="3" t="s">
         <v>4547</v>
       </c>
       <c r="C838" s="2"/>
@@ -43997,7 +43997,7 @@
       <c r="A839" s="2" t="s">
         <v>4551</v>
       </c>
-      <c r="B839" s="2" t="s">
+      <c r="B839" s="3" t="s">
         <v>4552</v>
       </c>
       <c r="C839" s="2"/>
@@ -44029,7 +44029,7 @@
       <c r="A840" s="2" t="s">
         <v>4556</v>
       </c>
-      <c r="B840" s="2" t="s">
+      <c r="B840" s="3" t="s">
         <v>4557</v>
       </c>
       <c r="C840" s="2"/>
@@ -44061,7 +44061,7 @@
       <c r="A841" s="2" t="s">
         <v>4561</v>
       </c>
-      <c r="B841" s="2" t="s">
+      <c r="B841" s="3" t="s">
         <v>4562</v>
       </c>
       <c r="C841" s="2"/>
@@ -44093,7 +44093,7 @@
       <c r="A842" s="2" t="s">
         <v>4566</v>
       </c>
-      <c r="B842" s="2" t="s">
+      <c r="B842" s="3" t="s">
         <v>4567</v>
       </c>
       <c r="C842" s="2"/>
@@ -44125,7 +44125,7 @@
       <c r="A843" s="2" t="s">
         <v>4571</v>
       </c>
-      <c r="B843" s="2" t="s">
+      <c r="B843" s="3" t="s">
         <v>4572</v>
       </c>
       <c r="C843" s="2"/>
@@ -44157,7 +44157,7 @@
       <c r="A844" s="2" t="s">
         <v>4576</v>
       </c>
-      <c r="B844" s="2" t="s">
+      <c r="B844" s="3" t="s">
         <v>4577</v>
       </c>
       <c r="C844" s="2"/>
@@ -44189,7 +44189,7 @@
       <c r="A845" s="2" t="s">
         <v>4581</v>
       </c>
-      <c r="B845" s="2" t="s">
+      <c r="B845" s="3" t="s">
         <v>4582</v>
       </c>
       <c r="C845" s="2"/>
@@ -44221,7 +44221,7 @@
       <c r="A846" s="2" t="s">
         <v>4586</v>
       </c>
-      <c r="B846" s="2" t="s">
+      <c r="B846" s="3" t="s">
         <v>4587</v>
       </c>
       <c r="C846" s="2"/>
@@ -44253,7 +44253,7 @@
       <c r="A847" s="2" t="s">
         <v>4591</v>
       </c>
-      <c r="B847" s="2" t="s">
+      <c r="B847" s="3" t="s">
         <v>4592</v>
       </c>
       <c r="C847" s="2"/>
@@ -44285,7 +44285,7 @@
       <c r="A848" s="2" t="s">
         <v>4596</v>
       </c>
-      <c r="B848" s="2" t="s">
+      <c r="B848" s="3" t="s">
         <v>4597</v>
       </c>
       <c r="C848" s="2"/>
@@ -44317,7 +44317,7 @@
       <c r="A849" s="2" t="s">
         <v>4601</v>
       </c>
-      <c r="B849" s="2" t="s">
+      <c r="B849" s="3" t="s">
         <v>4602</v>
       </c>
       <c r="C849" s="2"/>
@@ -44349,7 +44349,7 @@
       <c r="A850" s="2" t="s">
         <v>4606</v>
       </c>
-      <c r="B850" s="2" t="s">
+      <c r="B850" s="3" t="s">
         <v>4607</v>
       </c>
       <c r="C850" s="2"/>
@@ -44381,7 +44381,7 @@
       <c r="A851" s="2" t="s">
         <v>4611</v>
       </c>
-      <c r="B851" s="2" t="s">
+      <c r="B851" s="3" t="s">
         <v>4612</v>
       </c>
       <c r="C851" s="2"/>
@@ -44413,7 +44413,7 @@
       <c r="A852" s="2" t="s">
         <v>4616</v>
       </c>
-      <c r="B852" s="2" t="s">
+      <c r="B852" s="3" t="s">
         <v>4617</v>
       </c>
       <c r="C852" s="2"/>
@@ -44445,7 +44445,7 @@
       <c r="A853" s="2" t="s">
         <v>4621</v>
       </c>
-      <c r="B853" s="2" t="s">
+      <c r="B853" s="3" t="s">
         <v>4622</v>
       </c>
       <c r="C853" s="2"/>
@@ -44477,7 +44477,7 @@
       <c r="A854" s="2" t="s">
         <v>4626</v>
       </c>
-      <c r="B854" s="2" t="s">
+      <c r="B854" s="3" t="s">
         <v>4627</v>
       </c>
       <c r="C854" s="2"/>
@@ -44541,7 +44541,7 @@
       <c r="A856" s="2" t="s">
         <v>4636</v>
       </c>
-      <c r="B856" s="2" t="s">
+      <c r="B856" s="3" t="s">
         <v>4637</v>
       </c>
       <c r="C856" s="2"/>
@@ -44573,7 +44573,7 @@
       <c r="A857" s="2" t="s">
         <v>4641</v>
       </c>
-      <c r="B857" s="2" t="s">
+      <c r="B857" s="3" t="s">
         <v>4642</v>
       </c>
       <c r="C857" s="2"/>
@@ -44605,7 +44605,7 @@
       <c r="A858" s="2" t="s">
         <v>4646</v>
       </c>
-      <c r="B858" s="2" t="s">
+      <c r="B858" s="3" t="s">
         <v>4647</v>
       </c>
       <c r="C858" s="2"/>
@@ -44637,7 +44637,7 @@
       <c r="A859" s="2" t="s">
         <v>4651</v>
       </c>
-      <c r="B859" s="2" t="s">
+      <c r="B859" s="3" t="s">
         <v>4652</v>
       </c>
       <c r="C859" s="2"/>
@@ -44669,7 +44669,7 @@
       <c r="A860" s="2" t="s">
         <v>4656</v>
       </c>
-      <c r="B860" s="2" t="s">
+      <c r="B860" s="3" t="s">
         <v>4657</v>
       </c>
       <c r="C860" s="2"/>
@@ -44701,7 +44701,7 @@
       <c r="A861" s="2" t="s">
         <v>4661</v>
       </c>
-      <c r="B861" s="2" t="s">
+      <c r="B861" s="3" t="s">
         <v>4662</v>
       </c>
       <c r="C861" s="2"/>
@@ -44733,7 +44733,7 @@
       <c r="A862" s="2" t="s">
         <v>4666</v>
       </c>
-      <c r="B862" s="2" t="s">
+      <c r="B862" s="3" t="s">
         <v>4667</v>
       </c>
       <c r="C862" s="2"/>
@@ -44829,7 +44829,7 @@
       <c r="A865" s="2" t="s">
         <v>4681</v>
       </c>
-      <c r="B865" s="2" t="s">
+      <c r="B865" s="3" t="s">
         <v>4682</v>
       </c>
       <c r="C865" s="2"/>
@@ -44861,7 +44861,7 @@
       <c r="A866" s="2" t="s">
         <v>4686</v>
       </c>
-      <c r="B866" s="2" t="s">
+      <c r="B866" s="3" t="s">
         <v>4687</v>
       </c>
       <c r="C866" s="2"/>
@@ -44893,7 +44893,7 @@
       <c r="A867" s="2" t="s">
         <v>4691</v>
       </c>
-      <c r="B867" s="2" t="s">
+      <c r="B867" s="3" t="s">
         <v>4692</v>
       </c>
       <c r="C867" s="2"/>
@@ -44925,7 +44925,7 @@
       <c r="A868" s="2" t="s">
         <v>4696</v>
       </c>
-      <c r="B868" s="2" t="s">
+      <c r="B868" s="3" t="s">
         <v>4697</v>
       </c>
       <c r="C868" s="2"/>
@@ -44957,7 +44957,7 @@
       <c r="A869" s="2" t="s">
         <v>4701</v>
       </c>
-      <c r="B869" s="2" t="s">
+      <c r="B869" s="3" t="s">
         <v>4702</v>
       </c>
       <c r="C869" s="2"/>
@@ -44989,7 +44989,7 @@
       <c r="A870" s="2" t="s">
         <v>4706</v>
       </c>
-      <c r="B870" s="2" t="s">
+      <c r="B870" s="3" t="s">
         <v>4707</v>
       </c>
       <c r="C870" s="2"/>
@@ -45021,7 +45021,7 @@
       <c r="A871" s="2" t="s">
         <v>4711</v>
       </c>
-      <c r="B871" s="2" t="s">
+      <c r="B871" s="3" t="s">
         <v>4712</v>
       </c>
       <c r="C871" s="2"/>
@@ -45053,7 +45053,7 @@
       <c r="A872" s="2" t="s">
         <v>4716</v>
       </c>
-      <c r="B872" s="2" t="s">
+      <c r="B872" s="3" t="s">
         <v>4717</v>
       </c>
       <c r="C872" s="2"/>
@@ -45085,7 +45085,7 @@
       <c r="A873" s="2" t="s">
         <v>4721</v>
       </c>
-      <c r="B873" s="2" t="s">
+      <c r="B873" s="3" t="s">
         <v>4722</v>
       </c>
       <c r="C873" s="2"/>
@@ -45117,7 +45117,7 @@
       <c r="A874" s="2" t="s">
         <v>4726</v>
       </c>
-      <c r="B874" s="2" t="s">
+      <c r="B874" s="3" t="s">
         <v>4727</v>
       </c>
       <c r="C874" s="2"/>
@@ -45149,7 +45149,7 @@
       <c r="A875" s="2" t="s">
         <v>4731</v>
       </c>
-      <c r="B875" s="2" t="s">
+      <c r="B875" s="3" t="s">
         <v>4732</v>
       </c>
       <c r="C875" s="2"/>
@@ -45181,7 +45181,7 @@
       <c r="A876" s="2" t="s">
         <v>4736</v>
       </c>
-      <c r="B876" s="2" t="s">
+      <c r="B876" s="3" t="s">
         <v>4737</v>
       </c>
       <c r="C876" s="2"/>
@@ -45213,7 +45213,7 @@
       <c r="A877" s="2" t="s">
         <v>4741</v>
       </c>
-      <c r="B877" s="2" t="s">
+      <c r="B877" s="3" t="s">
         <v>4742</v>
       </c>
       <c r="C877" s="2"/>
@@ -45245,7 +45245,7 @@
       <c r="A878" s="2" t="s">
         <v>4746</v>
       </c>
-      <c r="B878" s="2" t="s">
+      <c r="B878" s="3" t="s">
         <v>4747</v>
       </c>
       <c r="C878" s="2"/>
@@ -45277,7 +45277,7 @@
       <c r="A879" s="2" t="s">
         <v>4751</v>
       </c>
-      <c r="B879" s="2" t="s">
+      <c r="B879" s="3" t="s">
         <v>4752</v>
       </c>
       <c r="C879" s="2"/>
@@ -45309,7 +45309,7 @@
       <c r="A880" s="2" t="s">
         <v>4756</v>
       </c>
-      <c r="B880" s="2" t="s">
+      <c r="B880" s="3" t="s">
         <v>4757</v>
       </c>
       <c r="C880" s="2"/>
@@ -45341,7 +45341,7 @@
       <c r="A881" s="2" t="s">
         <v>4760</v>
       </c>
-      <c r="B881" s="2" t="s">
+      <c r="B881" s="3" t="s">
         <v>4761</v>
       </c>
       <c r="C881" s="2"/>
@@ -45373,7 +45373,7 @@
       <c r="A882" s="2" t="s">
         <v>4765</v>
       </c>
-      <c r="B882" s="2" t="s">
+      <c r="B882" s="3" t="s">
         <v>4766</v>
       </c>
       <c r="C882" s="2"/>
@@ -45405,7 +45405,7 @@
       <c r="A883" s="2" t="s">
         <v>4770</v>
       </c>
-      <c r="B883" s="2" t="s">
+      <c r="B883" s="3" t="s">
         <v>4771</v>
       </c>
       <c r="C883" s="2"/>
@@ -45437,7 +45437,7 @@
       <c r="A884" s="2" t="s">
         <v>4775</v>
       </c>
-      <c r="B884" s="2" t="s">
+      <c r="B884" s="3" t="s">
         <v>4776</v>
       </c>
       <c r="C884" s="2"/>
@@ -45469,7 +45469,7 @@
       <c r="A885" s="2" t="s">
         <v>4780</v>
       </c>
-      <c r="B885" s="2" t="s">
+      <c r="B885" s="3" t="s">
         <v>4781</v>
       </c>
       <c r="C885" s="2"/>
@@ -45501,7 +45501,7 @@
       <c r="A886" s="2" t="s">
         <v>4785</v>
       </c>
-      <c r="B886" s="2" t="s">
+      <c r="B886" s="3" t="s">
         <v>4786</v>
       </c>
       <c r="C886" s="2"/>
@@ -45533,7 +45533,7 @@
       <c r="A887" s="2" t="s">
         <v>4790</v>
       </c>
-      <c r="B887" s="2" t="s">
+      <c r="B887" s="3" t="s">
         <v>4791</v>
       </c>
       <c r="C887" s="2"/>
@@ -45565,7 +45565,7 @@
       <c r="A888" s="2" t="s">
         <v>4795</v>
       </c>
-      <c r="B888" s="2" t="s">
+      <c r="B888" s="3" t="s">
         <v>4796</v>
       </c>
       <c r="C888" s="2"/>
@@ -45597,7 +45597,7 @@
       <c r="A889" s="2" t="s">
         <v>4800</v>
       </c>
-      <c r="B889" s="2" t="s">
+      <c r="B889" s="3" t="s">
         <v>4801</v>
       </c>
       <c r="C889" s="2"/>
@@ -45629,7 +45629,7 @@
       <c r="A890" s="2" t="s">
         <v>4805</v>
       </c>
-      <c r="B890" s="2" t="s">
+      <c r="B890" s="3" t="s">
         <v>4806</v>
       </c>
       <c r="C890" s="2"/>
@@ -45661,7 +45661,7 @@
       <c r="A891" s="2" t="s">
         <v>4810</v>
       </c>
-      <c r="B891" s="2" t="s">
+      <c r="B891" s="3" t="s">
         <v>4811</v>
       </c>
       <c r="C891" s="2"/>
@@ -45693,7 +45693,7 @@
       <c r="A892" s="2" t="s">
         <v>4815</v>
       </c>
-      <c r="B892" s="2" t="s">
+      <c r="B892" s="3" t="s">
         <v>4816</v>
       </c>
       <c r="C892" s="2"/>
@@ -45725,7 +45725,7 @@
       <c r="A893" s="2" t="s">
         <v>4820</v>
       </c>
-      <c r="B893" s="2" t="s">
+      <c r="B893" s="3" t="s">
         <v>4821</v>
       </c>
       <c r="C893" s="2"/>
@@ -45757,7 +45757,7 @@
       <c r="A894" s="2" t="s">
         <v>4825</v>
       </c>
-      <c r="B894" s="2" t="s">
+      <c r="B894" s="3" t="s">
         <v>4826</v>
       </c>
       <c r="C894" s="2"/>
@@ -45789,7 +45789,7 @@
       <c r="A895" s="2" t="s">
         <v>4830</v>
       </c>
-      <c r="B895" s="2" t="s">
+      <c r="B895" s="3" t="s">
         <v>4831</v>
       </c>
       <c r="C895" s="2"/>
@@ -45821,7 +45821,7 @@
       <c r="A896" s="2" t="s">
         <v>4835</v>
       </c>
-      <c r="B896" s="2" t="s">
+      <c r="B896" s="3" t="s">
         <v>4836</v>
       </c>
       <c r="C896" s="2"/>
@@ -45853,7 +45853,7 @@
       <c r="A897" s="2" t="s">
         <v>4840</v>
       </c>
-      <c r="B897" s="2" t="s">
+      <c r="B897" s="3" t="s">
         <v>4841</v>
       </c>
       <c r="C897" s="2"/>
@@ -45885,7 +45885,7 @@
       <c r="A898" s="2" t="s">
         <v>4845</v>
       </c>
-      <c r="B898" s="2" t="s">
+      <c r="B898" s="3" t="s">
         <v>4846</v>
       </c>
       <c r="C898" s="2"/>
@@ -45917,7 +45917,7 @@
       <c r="A899" s="2" t="s">
         <v>4850</v>
       </c>
-      <c r="B899" s="2" t="s">
+      <c r="B899" s="3" t="s">
         <v>4851</v>
       </c>
       <c r="C899" s="2"/>
@@ -45949,7 +45949,7 @@
       <c r="A900" s="2" t="s">
         <v>4855</v>
       </c>
-      <c r="B900" s="2" t="s">
+      <c r="B900" s="3" t="s">
         <v>4856</v>
       </c>
       <c r="C900" s="2"/>
@@ -45981,7 +45981,7 @@
       <c r="A901" s="2" t="s">
         <v>4860</v>
       </c>
-      <c r="B901" s="2" t="s">
+      <c r="B901" s="3" t="s">
         <v>4861</v>
       </c>
       <c r="C901" s="2"/>
@@ -46013,7 +46013,7 @@
       <c r="A902" s="2" t="s">
         <v>4865</v>
       </c>
-      <c r="B902" s="2" t="s">
+      <c r="B902" s="3" t="s">
         <v>4866</v>
       </c>
       <c r="C902" s="2"/>
@@ -46045,7 +46045,7 @@
       <c r="A903" s="2" t="s">
         <v>4870</v>
       </c>
-      <c r="B903" s="2" t="s">
+      <c r="B903" s="3" t="s">
         <v>4871</v>
       </c>
       <c r="C903" s="2"/>
@@ -46077,7 +46077,7 @@
       <c r="A904" s="2" t="s">
         <v>4875</v>
       </c>
-      <c r="B904" s="2" t="s">
+      <c r="B904" s="3" t="s">
         <v>4876</v>
       </c>
       <c r="C904" s="2"/>
@@ -46109,7 +46109,7 @@
       <c r="A905" s="2" t="s">
         <v>4880</v>
       </c>
-      <c r="B905" s="2" t="s">
+      <c r="B905" s="3" t="s">
         <v>4881</v>
       </c>
       <c r="C905" s="2"/>
@@ -46141,7 +46141,7 @@
       <c r="A906" s="2" t="s">
         <v>4885</v>
       </c>
-      <c r="B906" s="2" t="s">
+      <c r="B906" s="3" t="s">
         <v>4886</v>
       </c>
       <c r="C906" s="2"/>
@@ -46173,7 +46173,7 @@
       <c r="A907" s="2" t="s">
         <v>4890</v>
       </c>
-      <c r="B907" s="2" t="s">
+      <c r="B907" s="3" t="s">
         <v>4891</v>
       </c>
       <c r="C907" s="2"/>
@@ -46205,7 +46205,7 @@
       <c r="A908" s="2" t="s">
         <v>4895</v>
       </c>
-      <c r="B908" s="2" t="s">
+      <c r="B908" s="3" t="s">
         <v>4896</v>
       </c>
       <c r="C908" s="2"/>
@@ -46237,7 +46237,7 @@
       <c r="A909" s="2" t="s">
         <v>4900</v>
       </c>
-      <c r="B909" s="2" t="s">
+      <c r="B909" s="3" t="s">
         <v>4901</v>
       </c>
       <c r="C909" s="2"/>
@@ -46269,7 +46269,7 @@
       <c r="A910" s="2" t="s">
         <v>4905</v>
       </c>
-      <c r="B910" s="2" t="s">
+      <c r="B910" s="3" t="s">
         <v>4906</v>
       </c>
       <c r="C910" s="2"/>
@@ -46301,7 +46301,7 @@
       <c r="A911" s="2" t="s">
         <v>4910</v>
       </c>
-      <c r="B911" s="2" t="s">
+      <c r="B911" s="3" t="s">
         <v>4911</v>
       </c>
       <c r="C911" s="2"/>
@@ -46333,7 +46333,7 @@
       <c r="A912" s="2" t="s">
         <v>4915</v>
       </c>
-      <c r="B912" s="2" t="s">
+      <c r="B912" s="3" t="s">
         <v>4916</v>
       </c>
       <c r="C912" s="2"/>
@@ -46365,7 +46365,7 @@
       <c r="A913" s="2" t="s">
         <v>4920</v>
       </c>
-      <c r="B913" s="2" t="s">
+      <c r="B913" s="3" t="s">
         <v>4921</v>
       </c>
       <c r="C913" s="2"/>
@@ -46397,7 +46397,7 @@
       <c r="A914" s="2" t="s">
         <v>4925</v>
       </c>
-      <c r="B914" s="2" t="s">
+      <c r="B914" s="3" t="s">
         <v>4926</v>
       </c>
       <c r="C914" s="2"/>
@@ -46429,7 +46429,7 @@
       <c r="A915" s="2" t="s">
         <v>4930</v>
       </c>
-      <c r="B915" s="2" t="s">
+      <c r="B915" s="3" t="s">
         <v>4931</v>
       </c>
       <c r="C915" s="2"/>
@@ -46461,7 +46461,7 @@
       <c r="A916" s="2" t="s">
         <v>4935</v>
       </c>
-      <c r="B916" s="2" t="s">
+      <c r="B916" s="3" t="s">
         <v>4936</v>
       </c>
       <c r="C916" s="2"/>
@@ -46493,7 +46493,7 @@
       <c r="A917" s="2" t="s">
         <v>4940</v>
       </c>
-      <c r="B917" s="2" t="s">
+      <c r="B917" s="3" t="s">
         <v>4941</v>
       </c>
       <c r="C917" s="2"/>
@@ -46525,7 +46525,7 @@
       <c r="A918" s="2" t="s">
         <v>4945</v>
       </c>
-      <c r="B918" s="2" t="s">
+      <c r="B918" s="3" t="s">
         <v>4946</v>
       </c>
       <c r="C918" s="2"/>
@@ -46557,7 +46557,7 @@
       <c r="A919" s="2" t="s">
         <v>4950</v>
       </c>
-      <c r="B919" s="2" t="s">
+      <c r="B919" s="3" t="s">
         <v>4951</v>
       </c>
       <c r="C919" s="2"/>
@@ -46589,7 +46589,7 @@
       <c r="A920" s="2" t="s">
         <v>4955</v>
       </c>
-      <c r="B920" s="2" t="s">
+      <c r="B920" s="3" t="s">
         <v>4956</v>
       </c>
       <c r="C920" s="2"/>
@@ -46621,7 +46621,7 @@
       <c r="A921" s="2" t="s">
         <v>4960</v>
       </c>
-      <c r="B921" s="2" t="s">
+      <c r="B921" s="3" t="s">
         <v>4961</v>
       </c>
       <c r="C921" s="2"/>
@@ -46653,7 +46653,7 @@
       <c r="A922" s="2" t="s">
         <v>4965</v>
       </c>
-      <c r="B922" s="2" t="s">
+      <c r="B922" s="3" t="s">
         <v>4966</v>
       </c>
       <c r="C922" s="2"/>
@@ -46685,7 +46685,7 @@
       <c r="A923" s="2" t="s">
         <v>4970</v>
       </c>
-      <c r="B923" s="2" t="s">
+      <c r="B923" s="3" t="s">
         <v>4971</v>
       </c>
       <c r="C923" s="2"/>
@@ -46717,7 +46717,7 @@
       <c r="A924" s="2" t="s">
         <v>4975</v>
       </c>
-      <c r="B924" s="2" t="s">
+      <c r="B924" s="3" t="s">
         <v>4976</v>
       </c>
       <c r="C924" s="2"/>
@@ -46749,7 +46749,7 @@
       <c r="A925" s="2" t="s">
         <v>4980</v>
       </c>
-      <c r="B925" s="2" t="s">
+      <c r="B925" s="3" t="s">
         <v>4981</v>
       </c>
       <c r="C925" s="2"/>
@@ -46781,7 +46781,7 @@
       <c r="A926" s="2" t="s">
         <v>4985</v>
       </c>
-      <c r="B926" s="2" t="s">
+      <c r="B926" s="3" t="s">
         <v>4986</v>
       </c>
       <c r="C926" s="2"/>
@@ -46813,7 +46813,7 @@
       <c r="A927" s="2" t="s">
         <v>4990</v>
       </c>
-      <c r="B927" s="2" t="s">
+      <c r="B927" s="3" t="s">
         <v>4991</v>
       </c>
       <c r="C927" s="2"/>
@@ -46845,7 +46845,7 @@
       <c r="A928" s="2" t="s">
         <v>4995</v>
       </c>
-      <c r="B928" s="2" t="s">
+      <c r="B928" s="3" t="s">
         <v>4996</v>
       </c>
       <c r="C928" s="2"/>
@@ -46877,7 +46877,7 @@
       <c r="A929" s="2" t="s">
         <v>5000</v>
       </c>
-      <c r="B929" s="2" t="s">
+      <c r="B929" s="3" t="s">
         <v>5001</v>
       </c>
       <c r="C929" s="2"/>
@@ -46909,7 +46909,7 @@
       <c r="A930" s="2" t="s">
         <v>5005</v>
       </c>
-      <c r="B930" s="2" t="s">
+      <c r="B930" s="3" t="s">
         <v>5006</v>
       </c>
       <c r="C930" s="2"/>
@@ -46941,7 +46941,7 @@
       <c r="A931" s="2" t="s">
         <v>5010</v>
       </c>
-      <c r="B931" s="2" t="s">
+      <c r="B931" s="3" t="s">
         <v>5011</v>
       </c>
       <c r="C931" s="2"/>
@@ -46973,7 +46973,7 @@
       <c r="A932" s="2" t="s">
         <v>5015</v>
       </c>
-      <c r="B932" s="2" t="s">
+      <c r="B932" s="3" t="s">
         <v>5016</v>
       </c>
       <c r="C932" s="2"/>
@@ -47005,7 +47005,7 @@
       <c r="A933" s="2" t="s">
         <v>5020</v>
       </c>
-      <c r="B933" s="2" t="s">
+      <c r="B933" s="3" t="s">
         <v>5021</v>
       </c>
       <c r="C933" s="2"/>
@@ -47037,7 +47037,7 @@
       <c r="A934" s="2" t="s">
         <v>5025</v>
       </c>
-      <c r="B934" s="2" t="s">
+      <c r="B934" s="3" t="s">
         <v>5026</v>
       </c>
       <c r="C934" s="2"/>
@@ -47069,7 +47069,7 @@
       <c r="A935" s="2" t="s">
         <v>5030</v>
       </c>
-      <c r="B935" s="2" t="s">
+      <c r="B935" s="3" t="s">
         <v>5031</v>
       </c>
       <c r="C935" s="2"/>
@@ -47101,7 +47101,7 @@
       <c r="A936" s="2" t="s">
         <v>5035</v>
       </c>
-      <c r="B936" s="2" t="s">
+      <c r="B936" s="3" t="s">
         <v>5036</v>
       </c>
       <c r="C936" s="2"/>
@@ -47133,7 +47133,7 @@
       <c r="A937" s="2" t="s">
         <v>5040</v>
       </c>
-      <c r="B937" s="2" t="s">
+      <c r="B937" s="3" t="s">
         <v>5041</v>
       </c>
       <c r="C937" s="2"/>
@@ -47165,7 +47165,7 @@
       <c r="A938" s="2" t="s">
         <v>5045</v>
       </c>
-      <c r="B938" s="2" t="s">
+      <c r="B938" s="3" t="s">
         <v>5046</v>
       </c>
       <c r="C938" s="2"/>
@@ -47197,7 +47197,7 @@
       <c r="A939" s="2" t="s">
         <v>5050</v>
       </c>
-      <c r="B939" s="2" t="s">
+      <c r="B939" s="3" t="s">
         <v>5051</v>
       </c>
       <c r="C939" s="2"/>
@@ -47229,7 +47229,7 @@
       <c r="A940" s="2" t="s">
         <v>5055</v>
       </c>
-      <c r="B940" s="2" t="s">
+      <c r="B940" s="3" t="s">
         <v>5056</v>
       </c>
       <c r="C940" s="2"/>
@@ -47261,7 +47261,7 @@
       <c r="A941" s="2" t="s">
         <v>5060</v>
       </c>
-      <c r="B941" s="2" t="s">
+      <c r="B941" s="3" t="s">
         <v>5061</v>
       </c>
       <c r="C941" s="2"/>
@@ -47293,7 +47293,7 @@
       <c r="A942" s="2" t="s">
         <v>5065</v>
       </c>
-      <c r="B942" s="2" t="s">
+      <c r="B942" s="3" t="s">
         <v>5066</v>
       </c>
       <c r="C942" s="2"/>
@@ -47325,7 +47325,7 @@
       <c r="A943" s="2" t="s">
         <v>5070</v>
       </c>
-      <c r="B943" s="2" t="s">
+      <c r="B943" s="3" t="s">
         <v>5071</v>
       </c>
       <c r="C943" s="2"/>
@@ -47357,7 +47357,7 @@
       <c r="A944" s="2" t="s">
         <v>5075</v>
       </c>
-      <c r="B944" s="2" t="s">
+      <c r="B944" s="3" t="s">
         <v>5076</v>
       </c>
       <c r="C944" s="2"/>
@@ -47389,7 +47389,7 @@
       <c r="A945" s="2" t="s">
         <v>5080</v>
       </c>
-      <c r="B945" s="2" t="s">
+      <c r="B945" s="3" t="s">
         <v>5081</v>
       </c>
       <c r="C945" s="2"/>
@@ -47421,7 +47421,7 @@
       <c r="A946" s="2" t="s">
         <v>5085</v>
       </c>
-      <c r="B946" s="2" t="s">
+      <c r="B946" s="3" t="s">
         <v>5086</v>
       </c>
       <c r="C946" s="2"/>
@@ -47453,7 +47453,7 @@
       <c r="A947" s="2" t="s">
         <v>5090</v>
       </c>
-      <c r="B947" s="2" t="s">
+      <c r="B947" s="3" t="s">
         <v>5091</v>
       </c>
       <c r="C947" s="2"/>
@@ -47485,7 +47485,7 @@
       <c r="A948" s="2" t="s">
         <v>5095</v>
       </c>
-      <c r="B948" s="2" t="s">
+      <c r="B948" s="3" t="s">
         <v>5096</v>
       </c>
       <c r="C948" s="2"/>
@@ -47517,7 +47517,7 @@
       <c r="A949" s="2" t="s">
         <v>5100</v>
       </c>
-      <c r="B949" s="2" t="s">
+      <c r="B949" s="3" t="s">
         <v>5101</v>
       </c>
       <c r="C949" s="2"/>
@@ -47549,7 +47549,7 @@
       <c r="A950" s="2" t="s">
         <v>5105</v>
       </c>
-      <c r="B950" s="2" t="s">
+      <c r="B950" s="3" t="s">
         <v>5106</v>
       </c>
       <c r="C950" s="2"/>
@@ -47581,7 +47581,7 @@
       <c r="A951" s="2" t="s">
         <v>5110</v>
       </c>
-      <c r="B951" s="2" t="s">
+      <c r="B951" s="3" t="s">
         <v>5111</v>
       </c>
       <c r="C951" s="2"/>
@@ -47613,7 +47613,7 @@
       <c r="A952" s="2" t="s">
         <v>5115</v>
       </c>
-      <c r="B952" s="2" t="s">
+      <c r="B952" s="3" t="s">
         <v>5116</v>
       </c>
       <c r="C952" s="2"/>
@@ -47645,7 +47645,7 @@
       <c r="A953" s="2" t="s">
         <v>5120</v>
       </c>
-      <c r="B953" s="2" t="s">
+      <c r="B953" s="3" t="s">
         <v>5121</v>
       </c>
       <c r="C953" s="2"/>
@@ -47677,7 +47677,7 @@
       <c r="A954" s="2" t="s">
         <v>5125</v>
       </c>
-      <c r="B954" s="2" t="s">
+      <c r="B954" s="3" t="s">
         <v>5126</v>
       </c>
       <c r="C954" s="2"/>
@@ -47709,7 +47709,7 @@
       <c r="A955" s="2" t="s">
         <v>5130</v>
       </c>
-      <c r="B955" s="2" t="s">
+      <c r="B955" s="3" t="s">
         <v>5131</v>
       </c>
       <c r="C955" s="2"/>
@@ -47741,7 +47741,7 @@
       <c r="A956" s="2" t="s">
         <v>5135</v>
       </c>
-      <c r="B956" s="2" t="s">
+      <c r="B956" s="3" t="s">
         <v>5136</v>
       </c>
       <c r="C956" s="2"/>
@@ -47773,7 +47773,7 @@
       <c r="A957" s="2" t="s">
         <v>5140</v>
       </c>
-      <c r="B957" s="2" t="s">
+      <c r="B957" s="3" t="s">
         <v>5141</v>
       </c>
       <c r="C957" s="2"/>
@@ -47805,7 +47805,7 @@
       <c r="A958" s="2" t="s">
         <v>5145</v>
       </c>
-      <c r="B958" s="2" t="s">
+      <c r="B958" s="3" t="s">
         <v>5146</v>
       </c>
       <c r="C958" s="2"/>
@@ -47837,7 +47837,7 @@
       <c r="A959" s="2" t="s">
         <v>5150</v>
       </c>
-      <c r="B959" s="2" t="s">
+      <c r="B959" s="3" t="s">
         <v>5151</v>
       </c>
       <c r="C959" s="2"/>
@@ -47869,7 +47869,7 @@
       <c r="A960" s="2" t="s">
         <v>5155</v>
       </c>
-      <c r="B960" s="2" t="s">
+      <c r="B960" s="3" t="s">
         <v>5156</v>
       </c>
       <c r="C960" s="2"/>
@@ -47901,7 +47901,7 @@
       <c r="A961" s="2" t="s">
         <v>5160</v>
       </c>
-      <c r="B961" s="2" t="s">
+      <c r="B961" s="3" t="s">
         <v>5161</v>
       </c>
       <c r="C961" s="2"/>
@@ -47933,7 +47933,7 @@
       <c r="A962" s="2" t="s">
         <v>5165</v>
       </c>
-      <c r="B962" s="2" t="s">
+      <c r="B962" s="3" t="s">
         <v>5166</v>
       </c>
       <c r="C962" s="2"/>
@@ -47965,7 +47965,7 @@
       <c r="A963" s="2" t="s">
         <v>5170</v>
       </c>
-      <c r="B963" s="2" t="s">
+      <c r="B963" s="3" t="s">
         <v>5171</v>
       </c>
       <c r="C963" s="2"/>
@@ -47997,7 +47997,7 @@
       <c r="A964" s="2" t="s">
         <v>5175</v>
       </c>
-      <c r="B964" s="2" t="s">
+      <c r="B964" s="3" t="s">
         <v>5176</v>
       </c>
       <c r="C964" s="2"/>
@@ -48029,7 +48029,7 @@
       <c r="A965" s="2" t="s">
         <v>5180</v>
       </c>
-      <c r="B965" s="2" t="s">
+      <c r="B965" s="3" t="s">
         <v>5181</v>
       </c>
       <c r="C965" s="2"/>
@@ -48061,7 +48061,7 @@
       <c r="A966" s="2" t="s">
         <v>5185</v>
       </c>
-      <c r="B966" s="2" t="s">
+      <c r="B966" s="3" t="s">
         <v>5186</v>
       </c>
       <c r="C966" s="2"/>
@@ -48093,7 +48093,7 @@
       <c r="A967" s="2" t="s">
         <v>5190</v>
       </c>
-      <c r="B967" s="2" t="s">
+      <c r="B967" s="3" t="s">
         <v>5191</v>
       </c>
       <c r="C967" s="2"/>
@@ -48125,7 +48125,7 @@
       <c r="A968" s="2" t="s">
         <v>5195</v>
       </c>
-      <c r="B968" s="2" t="s">
+      <c r="B968" s="3" t="s">
         <v>5196</v>
       </c>
       <c r="C968" s="2"/>
@@ -48157,7 +48157,7 @@
       <c r="A969" s="2" t="s">
         <v>5200</v>
       </c>
-      <c r="B969" s="2" t="s">
+      <c r="B969" s="3" t="s">
         <v>5201</v>
       </c>
       <c r="C969" s="2"/>
@@ -48189,7 +48189,7 @@
       <c r="A970" s="2" t="s">
         <v>5205</v>
       </c>
-      <c r="B970" s="2" t="s">
+      <c r="B970" s="3" t="s">
         <v>5206</v>
       </c>
       <c r="C970" s="2"/>
@@ -48221,7 +48221,7 @@
       <c r="A971" s="2" t="s">
         <v>5210</v>
       </c>
-      <c r="B971" s="2" t="s">
+      <c r="B971" s="3" t="s">
         <v>5211</v>
       </c>
       <c r="C971" s="2"/>
@@ -48253,7 +48253,7 @@
       <c r="A972" s="2" t="s">
         <v>5215</v>
       </c>
-      <c r="B972" s="2" t="s">
+      <c r="B972" s="3" t="s">
         <v>5216</v>
       </c>
       <c r="C972" s="2"/>
@@ -48285,7 +48285,7 @@
       <c r="A973" s="2" t="s">
         <v>5220</v>
       </c>
-      <c r="B973" s="2" t="s">
+      <c r="B973" s="3" t="s">
         <v>5221</v>
       </c>
       <c r="C973" s="2"/>
@@ -48317,7 +48317,7 @@
       <c r="A974" s="2" t="s">
         <v>5225</v>
       </c>
-      <c r="B974" s="2" t="s">
+      <c r="B974" s="3" t="s">
         <v>5226</v>
       </c>
       <c r="C974" s="2"/>
@@ -48349,7 +48349,7 @@
       <c r="A975" s="2" t="s">
         <v>5230</v>
       </c>
-      <c r="B975" s="2" t="s">
+      <c r="B975" s="3" t="s">
         <v>5231</v>
       </c>
       <c r="C975" s="2"/>
@@ -48381,7 +48381,7 @@
       <c r="A976" s="2" t="s">
         <v>5235</v>
       </c>
-      <c r="B976" s="2" t="s">
+      <c r="B976" s="3" t="s">
         <v>5236</v>
       </c>
       <c r="C976" s="2"/>
@@ -48413,7 +48413,7 @@
       <c r="A977" s="2" t="s">
         <v>5240</v>
       </c>
-      <c r="B977" s="2" t="s">
+      <c r="B977" s="3" t="s">
         <v>5241</v>
       </c>
       <c r="C977" s="2"/>
@@ -48445,7 +48445,7 @@
       <c r="A978" s="2" t="s">
         <v>5245</v>
       </c>
-      <c r="B978" s="2" t="s">
+      <c r="B978" s="3" t="s">
         <v>5246</v>
       </c>
       <c r="C978" s="2"/>
@@ -48477,7 +48477,7 @@
       <c r="A979" s="2" t="s">
         <v>5250</v>
       </c>
-      <c r="B979" s="2" t="s">
+      <c r="B979" s="3" t="s">
         <v>5251</v>
       </c>
       <c r="C979" s="2"/>
@@ -48509,7 +48509,7 @@
       <c r="A980" s="2" t="s">
         <v>5255</v>
       </c>
-      <c r="B980" s="2" t="s">
+      <c r="B980" s="3" t="s">
         <v>5256</v>
       </c>
       <c r="C980" s="2"/>
@@ -48541,7 +48541,7 @@
       <c r="A981" s="2" t="s">
         <v>5260</v>
       </c>
-      <c r="B981" s="2" t="s">
+      <c r="B981" s="3" t="s">
         <v>5261</v>
       </c>
       <c r="C981" s="2"/>
@@ -48573,7 +48573,7 @@
       <c r="A982" s="2" t="s">
         <v>5265</v>
       </c>
-      <c r="B982" s="2" t="s">
+      <c r="B982" s="3" t="s">
         <v>5266</v>
       </c>
       <c r="C982" s="2"/>
@@ -48605,7 +48605,7 @@
       <c r="A983" s="2" t="s">
         <v>5270</v>
       </c>
-      <c r="B983" s="2" t="s">
+      <c r="B983" s="3" t="s">
         <v>5271</v>
       </c>
       <c r="C983" s="2"/>
@@ -48637,7 +48637,7 @@
       <c r="A984" s="2" t="s">
         <v>5275</v>
       </c>
-      <c r="B984" s="2" t="s">
+      <c r="B984" s="3" t="s">
         <v>5276</v>
       </c>
       <c r="C984" s="2"/>
@@ -48669,7 +48669,7 @@
       <c r="A985" s="2" t="s">
         <v>5280</v>
       </c>
-      <c r="B985" s="2" t="s">
+      <c r="B985" s="3" t="s">
         <v>5281</v>
       </c>
       <c r="C985" s="2"/>
@@ -48701,7 +48701,7 @@
       <c r="A986" s="2" t="s">
         <v>5285</v>
       </c>
-      <c r="B986" s="2" t="s">
+      <c r="B986" s="3" t="s">
         <v>5286</v>
       </c>
       <c r="C986" s="2"/>
@@ -48733,7 +48733,7 @@
       <c r="A987" s="2" t="s">
         <v>5290</v>
       </c>
-      <c r="B987" s="2" t="s">
+      <c r="B987" s="3" t="s">
         <v>5291</v>
       </c>
       <c r="C987" s="2"/>
@@ -48765,7 +48765,7 @@
       <c r="A988" s="2" t="s">
         <v>5295</v>
       </c>
-      <c r="B988" s="2" t="s">
+      <c r="B988" s="3" t="s">
         <v>5296</v>
       </c>
       <c r="C988" s="2"/>
@@ -48797,7 +48797,7 @@
       <c r="A989" s="2" t="s">
         <v>5300</v>
       </c>
-      <c r="B989" s="2" t="s">
+      <c r="B989" s="3" t="s">
         <v>5301</v>
       </c>
       <c r="C989" s="2"/>
@@ -48829,7 +48829,7 @@
       <c r="A990" s="2" t="s">
         <v>5305</v>
       </c>
-      <c r="B990" s="2" t="s">
+      <c r="B990" s="3" t="s">
         <v>5306</v>
       </c>
       <c r="C990" s="2"/>
@@ -48861,7 +48861,7 @@
       <c r="A991" s="2" t="s">
         <v>5310</v>
       </c>
-      <c r="B991" s="2" t="s">
+      <c r="B991" s="3" t="s">
         <v>5311</v>
       </c>
       <c r="C991" s="2"/>
@@ -48893,7 +48893,7 @@
       <c r="A992" s="2" t="s">
         <v>5315</v>
       </c>
-      <c r="B992" s="2" t="s">
+      <c r="B992" s="3" t="s">
         <v>5316</v>
       </c>
       <c r="C992" s="2"/>
@@ -48925,7 +48925,7 @@
       <c r="A993" s="2" t="s">
         <v>5320</v>
       </c>
-      <c r="B993" s="2" t="s">
+      <c r="B993" s="3" t="s">
         <v>5321</v>
       </c>
       <c r="C993" s="2"/>
@@ -48957,7 +48957,7 @@
       <c r="A994" s="2" t="s">
         <v>5325</v>
       </c>
-      <c r="B994" s="2" t="s">
+      <c r="B994" s="3" t="s">
         <v>5326</v>
       </c>
       <c r="C994" s="2"/>
@@ -48989,7 +48989,7 @@
       <c r="A995" s="2" t="s">
         <v>5330</v>
       </c>
-      <c r="B995" s="2" t="s">
+      <c r="B995" s="3" t="s">
         <v>5331</v>
       </c>
       <c r="C995" s="2"/>
@@ -49021,7 +49021,7 @@
       <c r="A996" s="2" t="s">
         <v>5335</v>
       </c>
-      <c r="B996" s="2" t="s">
+      <c r="B996" s="3" t="s">
         <v>5336</v>
       </c>
       <c r="C996" s="2"/>
@@ -49053,7 +49053,7 @@
       <c r="A997" s="2" t="s">
         <v>5340</v>
       </c>
-      <c r="B997" s="2" t="s">
+      <c r="B997" s="3" t="s">
         <v>5341</v>
       </c>
       <c r="C997" s="2"/>
@@ -49085,7 +49085,7 @@
       <c r="A998" s="2" t="s">
         <v>5345</v>
       </c>
-      <c r="B998" s="2" t="s">
+      <c r="B998" s="3" t="s">
         <v>5346</v>
       </c>
       <c r="C998" s="2"/>
@@ -49117,7 +49117,7 @@
       <c r="A999" s="2" t="s">
         <v>5350</v>
       </c>
-      <c r="B999" s="2" t="s">
+      <c r="B999" s="3" t="s">
         <v>5351</v>
       </c>
       <c r="C999" s="2"/>
@@ -49149,7 +49149,7 @@
       <c r="A1000" s="2" t="s">
         <v>5355</v>
       </c>
-      <c r="B1000" s="2" t="s">
+      <c r="B1000" s="3" t="s">
         <v>5356</v>
       </c>
       <c r="C1000" s="2"/>
@@ -49181,7 +49181,7 @@
       <c r="A1001" s="2" t="s">
         <v>5360</v>
       </c>
-      <c r="B1001" s="2" t="s">
+      <c r="B1001" s="3" t="s">
         <v>5361</v>
       </c>
       <c r="C1001" s="2"/>
